--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5518,7 +5518,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004395</v>
+        <v>121004337</v>
       </c>
       <c r="B46" t="n">
         <v>78598</v>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550381</v>
+        <v>550319</v>
       </c>
       <c r="R46" t="n">
-        <v>6994155</v>
+        <v>6994143</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5597,6 +5597,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,7 +5629,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004337</v>
+        <v>121004395</v>
       </c>
       <c r="B47" t="n">
         <v>78598</v>
@@ -5667,10 +5672,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550319</v>
+        <v>550381</v>
       </c>
       <c r="R47" t="n">
-        <v>6994143</v>
+        <v>6994155</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5703,11 +5708,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004470</v>
+        <v>121004450</v>
       </c>
       <c r="B17" t="n">
-        <v>90613</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,21 +2431,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550383</v>
+        <v>550379</v>
       </c>
       <c r="R17" t="n">
-        <v>6993994</v>
+        <v>6994086</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2494,11 +2494,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121004521</v>
+        <v>121004547</v>
       </c>
       <c r="B18" t="n">
-        <v>79679</v>
+        <v>91973</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,25 +2533,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550494</v>
+        <v>550493</v>
       </c>
       <c r="R18" t="n">
-        <v>6993901</v>
+        <v>6994078</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2605,11 +2600,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004358</v>
+        <v>121004521</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,21 +2643,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2680,10 +2670,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550362</v>
+        <v>550494</v>
       </c>
       <c r="R19" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2716,6 +2706,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004536</v>
+        <v>121004500</v>
       </c>
       <c r="B20" t="n">
-        <v>80555</v>
+        <v>91973</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2755,25 +2750,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2786,10 +2781,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550477</v>
+        <v>550496</v>
       </c>
       <c r="R20" t="n">
-        <v>6994042</v>
+        <v>6993817</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2849,10 +2844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004409</v>
+        <v>121004525</v>
       </c>
       <c r="B21" t="n">
-        <v>91975</v>
+        <v>56563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,37 +2860,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550413</v>
+        <v>550502</v>
       </c>
       <c r="R21" t="n">
-        <v>6994137</v>
+        <v>6993935</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2936,7 +2936,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2955,10 +2954,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004514</v>
+        <v>121004430</v>
       </c>
       <c r="B22" t="n">
-        <v>90934</v>
+        <v>91973</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,25 +2966,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2998,10 +2997,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550464</v>
+        <v>550422</v>
       </c>
       <c r="R22" t="n">
-        <v>6993901</v>
+        <v>6994093</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3061,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004540</v>
+        <v>121004539</v>
       </c>
       <c r="B23" t="n">
-        <v>91963</v>
+        <v>89753</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3073,25 +3072,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3104,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550505</v>
+        <v>550486</v>
       </c>
       <c r="R23" t="n">
-        <v>6994074</v>
+        <v>6994062</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3167,10 +3166,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004537</v>
+        <v>121004337</v>
       </c>
       <c r="B24" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,25 +3178,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3210,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550477</v>
+        <v>550319</v>
       </c>
       <c r="R24" t="n">
-        <v>6994042</v>
+        <v>6994143</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3246,6 +3245,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,10 +3277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121004547</v>
+        <v>121004349</v>
       </c>
       <c r="B25" t="n">
-        <v>91963</v>
+        <v>79219</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,25 +3289,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,10 +3320,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550493</v>
+        <v>550358</v>
       </c>
       <c r="R25" t="n">
-        <v>6994078</v>
+        <v>6994160</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3379,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004362</v>
+        <v>121004399</v>
       </c>
       <c r="B26" t="n">
-        <v>89743</v>
+        <v>91973</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,25 +3395,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3422,10 +3426,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550364</v>
+        <v>550384</v>
       </c>
       <c r="R26" t="n">
-        <v>6994169</v>
+        <v>6994151</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3485,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004430</v>
+        <v>121004484</v>
       </c>
       <c r="B27" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3528,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550422</v>
+        <v>550427</v>
       </c>
       <c r="R27" t="n">
-        <v>6994093</v>
+        <v>6993867</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3591,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004475</v>
+        <v>121004395</v>
       </c>
       <c r="B28" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,25 +3607,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3634,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550385</v>
+        <v>550381</v>
       </c>
       <c r="R28" t="n">
-        <v>6993920</v>
+        <v>6994155</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3697,10 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004351</v>
+        <v>121004362</v>
       </c>
       <c r="B29" t="n">
-        <v>90613</v>
+        <v>89753</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3713,21 +3717,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550358</v>
+        <v>550364</v>
       </c>
       <c r="R29" t="n">
-        <v>6994160</v>
+        <v>6994169</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3803,10 +3807,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004525</v>
+        <v>121004470</v>
       </c>
       <c r="B30" t="n">
-        <v>56560</v>
+        <v>90623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3815,46 +3819,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550502</v>
+        <v>550383</v>
       </c>
       <c r="R30" t="n">
-        <v>6993935</v>
+        <v>6993994</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3889,12 +3888,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3913,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004394</v>
+        <v>121004524</v>
       </c>
       <c r="B31" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3956,10 +3961,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550381</v>
+        <v>550502</v>
       </c>
       <c r="R31" t="n">
-        <v>6994155</v>
+        <v>6993935</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4019,10 +4024,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004524</v>
+        <v>121004439</v>
       </c>
       <c r="B32" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4031,25 +4036,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4062,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550502</v>
+        <v>550405</v>
       </c>
       <c r="R32" t="n">
-        <v>6993935</v>
+        <v>6994090</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4098,6 +4103,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004500</v>
+        <v>121004515</v>
       </c>
       <c r="B33" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4137,25 +4147,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4168,10 +4178,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550496</v>
+        <v>550464</v>
       </c>
       <c r="R33" t="n">
-        <v>6993817</v>
+        <v>6993901</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4231,10 +4241,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004533</v>
+        <v>121004394</v>
       </c>
       <c r="B34" t="n">
-        <v>79216</v>
+        <v>91973</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4243,25 +4253,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4284,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550456</v>
+        <v>550381</v>
       </c>
       <c r="R34" t="n">
-        <v>6993982</v>
+        <v>6994155</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4310,11 +4320,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4342,10 +4347,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004550</v>
+        <v>121004368</v>
       </c>
       <c r="B35" t="n">
-        <v>80555</v>
+        <v>92001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4358,21 +4363,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4385,10 +4390,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550508</v>
+        <v>550364</v>
       </c>
       <c r="R35" t="n">
-        <v>6994113</v>
+        <v>6994169</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4448,10 +4453,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004399</v>
+        <v>121004541</v>
       </c>
       <c r="B36" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4491,10 +4496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550384</v>
+        <v>550528</v>
       </c>
       <c r="R36" t="n">
-        <v>6994151</v>
+        <v>6994067</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4554,10 +4559,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004446</v>
+        <v>121004341</v>
       </c>
       <c r="B37" t="n">
-        <v>91991</v>
+        <v>91973</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4566,25 +4571,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4597,10 +4602,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550416</v>
+        <v>550344</v>
       </c>
       <c r="R37" t="n">
-        <v>6994077</v>
+        <v>6994160</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4660,10 +4665,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004511</v>
+        <v>121004509</v>
       </c>
       <c r="B38" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4672,25 +4677,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4703,10 +4708,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550470</v>
+        <v>550476</v>
       </c>
       <c r="R38" t="n">
-        <v>6993852</v>
+        <v>6993841</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4739,11 +4744,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4771,10 +4771,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004484</v>
+        <v>121004514</v>
       </c>
       <c r="B39" t="n">
-        <v>91963</v>
+        <v>90944</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4783,25 +4783,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550427</v>
+        <v>550464</v>
       </c>
       <c r="R39" t="n">
-        <v>6993867</v>
+        <v>6993901</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004374</v>
+        <v>121004351</v>
       </c>
       <c r="B40" t="n">
-        <v>79216</v>
+        <v>90623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4893,21 +4893,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550369</v>
+        <v>550358</v>
       </c>
       <c r="R40" t="n">
-        <v>6994167</v>
+        <v>6994160</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004515</v>
+        <v>121004475</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550464</v>
+        <v>550385</v>
       </c>
       <c r="R41" t="n">
-        <v>6993901</v>
+        <v>6993920</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004368</v>
+        <v>121004409</v>
       </c>
       <c r="B42" t="n">
-        <v>91991</v>
+        <v>91985</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5101,25 +5101,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550364</v>
+        <v>550413</v>
       </c>
       <c r="R42" t="n">
-        <v>6994169</v>
+        <v>6994137</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004450</v>
+        <v>121004533</v>
       </c>
       <c r="B43" t="n">
-        <v>78598</v>
+        <v>79219</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550379</v>
+        <v>550456</v>
       </c>
       <c r="R43" t="n">
-        <v>6994086</v>
+        <v>6993982</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5274,6 +5274,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,10 +5306,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121004472</v>
+        <v>121004454</v>
       </c>
       <c r="B44" t="n">
-        <v>90841</v>
+        <v>95628</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5313,30 +5318,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5344,10 +5350,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550400</v>
+        <v>550389</v>
       </c>
       <c r="R44" t="n">
-        <v>6993983</v>
+        <v>6994068</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5407,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004439</v>
+        <v>121004537</v>
       </c>
       <c r="B45" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5419,25 +5425,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5450,10 +5456,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550405</v>
+        <v>550477</v>
       </c>
       <c r="R45" t="n">
-        <v>6994090</v>
+        <v>6994042</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5486,11 +5492,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5518,10 +5519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004337</v>
+        <v>121004446</v>
       </c>
       <c r="B46" t="n">
-        <v>78598</v>
+        <v>92001</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5534,21 +5535,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5561,10 +5562,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550319</v>
+        <v>550416</v>
       </c>
       <c r="R46" t="n">
-        <v>6994143</v>
+        <v>6994077</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5597,11 +5598,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5629,10 +5625,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004395</v>
+        <v>121004536</v>
       </c>
       <c r="B47" t="n">
-        <v>78598</v>
+        <v>80558</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5645,21 +5641,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5672,10 +5668,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550381</v>
+        <v>550477</v>
       </c>
       <c r="R47" t="n">
-        <v>6994155</v>
+        <v>6994042</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5735,10 +5731,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004341</v>
+        <v>121004511</v>
       </c>
       <c r="B48" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5747,25 +5743,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5778,10 +5774,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550344</v>
+        <v>550470</v>
       </c>
       <c r="R48" t="n">
-        <v>6994160</v>
+        <v>6993852</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5814,6 +5810,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5841,10 +5842,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004509</v>
+        <v>121004374</v>
       </c>
       <c r="B49" t="n">
-        <v>91963</v>
+        <v>79219</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5853,25 +5854,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5884,10 +5885,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550476</v>
+        <v>550369</v>
       </c>
       <c r="R49" t="n">
-        <v>6993841</v>
+        <v>6994167</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5947,10 +5948,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004454</v>
+        <v>121004472</v>
       </c>
       <c r="B50" t="n">
-        <v>95618</v>
+        <v>90851</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5959,31 +5960,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550389</v>
+        <v>550400</v>
       </c>
       <c r="R50" t="n">
-        <v>6994068</v>
+        <v>6993983</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6054,10 +6054,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004349</v>
+        <v>121004540</v>
       </c>
       <c r="B51" t="n">
-        <v>79216</v>
+        <v>91973</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6066,25 +6066,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550358</v>
+        <v>550505</v>
       </c>
       <c r="R51" t="n">
-        <v>6994160</v>
+        <v>6994074</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6160,10 +6160,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004541</v>
+        <v>121004550</v>
       </c>
       <c r="B52" t="n">
-        <v>91963</v>
+        <v>80558</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6172,25 +6172,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550528</v>
+        <v>550508</v>
       </c>
       <c r="R52" t="n">
-        <v>6994067</v>
+        <v>6994113</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004539</v>
+        <v>121004358</v>
       </c>
       <c r="B53" t="n">
-        <v>89743</v>
+        <v>78601</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550486</v>
+        <v>550362</v>
       </c>
       <c r="R53" t="n">
-        <v>6994062</v>
+        <v>6994156</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6375,7 +6375,7 @@
         <v>121004416</v>
       </c>
       <c r="B54" t="n">
-        <v>90841</v>
+        <v>90851</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121004565</v>
+        <v>121004558</v>
       </c>
       <c r="B55" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550469</v>
+        <v>550516</v>
       </c>
       <c r="R55" t="n">
-        <v>6994270</v>
+        <v>6994130</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6585,10 +6585,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004422</v>
+        <v>121004562</v>
       </c>
       <c r="B56" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550395</v>
+        <v>550520</v>
       </c>
       <c r="R56" t="n">
-        <v>6994127</v>
+        <v>6994154</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004519</v>
+        <v>121004405</v>
       </c>
       <c r="B57" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550494</v>
+        <v>550404</v>
       </c>
       <c r="R57" t="n">
-        <v>6993901</v>
+        <v>6994153</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6772,11 +6772,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6804,10 +6799,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004558</v>
+        <v>121004505</v>
       </c>
       <c r="B58" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6848,10 +6843,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550516</v>
+        <v>550496</v>
       </c>
       <c r="R58" t="n">
-        <v>6994130</v>
+        <v>6993835</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6911,10 +6906,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004477</v>
+        <v>121004422</v>
       </c>
       <c r="B59" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6955,10 +6950,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550370</v>
+        <v>550395</v>
       </c>
       <c r="R59" t="n">
-        <v>6993853</v>
+        <v>6994127</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7018,10 +7013,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004562</v>
+        <v>121004565</v>
       </c>
       <c r="B60" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7062,10 +7057,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550520</v>
+        <v>550469</v>
       </c>
       <c r="R60" t="n">
-        <v>6994154</v>
+        <v>6994270</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7125,10 +7120,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004405</v>
+        <v>121004519</v>
       </c>
       <c r="B61" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7169,10 +7164,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550404</v>
+        <v>550494</v>
       </c>
       <c r="R61" t="n">
-        <v>6994153</v>
+        <v>6993901</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7205,6 +7200,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7232,10 +7232,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121004505</v>
+        <v>121004477</v>
       </c>
       <c r="B62" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550496</v>
+        <v>550370</v>
       </c>
       <c r="R62" t="n">
-        <v>6993835</v>
+        <v>6993853</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004545</v>
+        <v>121004449</v>
       </c>
       <c r="B63" t="n">
-        <v>91967</v>
+        <v>88024</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>510</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550493</v>
+        <v>550379</v>
       </c>
       <c r="R63" t="n">
-        <v>6994078</v>
+        <v>6994086</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7445,10 +7445,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121004449</v>
+        <v>121004545</v>
       </c>
       <c r="B64" t="n">
-        <v>88018</v>
+        <v>91977</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7457,25 +7457,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>4365</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550379</v>
+        <v>550493</v>
       </c>
       <c r="R64" t="n">
-        <v>6994086</v>
+        <v>6994078</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7554,7 +7554,7 @@
         <v>121004494</v>
       </c>
       <c r="B65" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004450</v>
+        <v>121004541</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,25 +2427,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550379</v>
+        <v>550528</v>
       </c>
       <c r="R17" t="n">
-        <v>6994086</v>
+        <v>6994067</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121004547</v>
+        <v>121004537</v>
       </c>
       <c r="B18" t="n">
         <v>91973</v>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550493</v>
+        <v>550477</v>
       </c>
       <c r="R18" t="n">
-        <v>6994078</v>
+        <v>6994042</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2627,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004521</v>
+        <v>121004515</v>
       </c>
       <c r="B19" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550494</v>
+        <v>550464</v>
       </c>
       <c r="R19" t="n">
         <v>6993901</v>
@@ -2706,11 +2706,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2733,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004500</v>
+        <v>121004439</v>
       </c>
       <c r="B20" t="n">
-        <v>91973</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,25 +2745,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2781,10 +2776,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550496</v>
+        <v>550405</v>
       </c>
       <c r="R20" t="n">
-        <v>6993817</v>
+        <v>6994090</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2817,6 +2812,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,10 +2844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004525</v>
+        <v>121004399</v>
       </c>
       <c r="B21" t="n">
-        <v>56563</v>
+        <v>91973</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2860,42 +2860,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550502</v>
+        <v>550384</v>
       </c>
       <c r="R21" t="n">
-        <v>6993935</v>
+        <v>6994151</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2936,6 +2931,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2954,10 +2950,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004430</v>
+        <v>121004514</v>
       </c>
       <c r="B22" t="n">
-        <v>91973</v>
+        <v>90944</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,25 +2962,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2997,10 +2993,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550422</v>
+        <v>550464</v>
       </c>
       <c r="R22" t="n">
-        <v>6994093</v>
+        <v>6993901</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3060,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004539</v>
+        <v>121004472</v>
       </c>
       <c r="B23" t="n">
-        <v>89753</v>
+        <v>90851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,25 +3068,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550486</v>
+        <v>550400</v>
       </c>
       <c r="R23" t="n">
-        <v>6994062</v>
+        <v>6993983</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3166,7 +3162,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004337</v>
+        <v>121004395</v>
       </c>
       <c r="B24" t="n">
         <v>78601</v>
@@ -3209,10 +3205,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550319</v>
+        <v>550381</v>
       </c>
       <c r="R24" t="n">
-        <v>6994143</v>
+        <v>6994155</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3245,11 +3241,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,10 +3268,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121004349</v>
+        <v>121004394</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>91973</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,25 +3280,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3320,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550358</v>
+        <v>550381</v>
       </c>
       <c r="R25" t="n">
-        <v>6994160</v>
+        <v>6994155</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3383,7 +3374,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004399</v>
+        <v>121004484</v>
       </c>
       <c r="B26" t="n">
         <v>91973</v>
@@ -3426,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550384</v>
+        <v>550427</v>
       </c>
       <c r="R26" t="n">
-        <v>6994151</v>
+        <v>6993867</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3489,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004484</v>
+        <v>121004525</v>
       </c>
       <c r="B27" t="n">
-        <v>91973</v>
+        <v>56563</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,37 +3496,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550427</v>
+        <v>550502</v>
       </c>
       <c r="R27" t="n">
-        <v>6993867</v>
+        <v>6993935</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3576,7 +3572,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3595,7 +3590,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004395</v>
+        <v>121004337</v>
       </c>
       <c r="B28" t="n">
         <v>78601</v>
@@ -3638,10 +3633,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550381</v>
+        <v>550319</v>
       </c>
       <c r="R28" t="n">
-        <v>6994155</v>
+        <v>6994143</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3674,6 +3669,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3701,10 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004362</v>
+        <v>121004470</v>
       </c>
       <c r="B29" t="n">
-        <v>89753</v>
+        <v>90623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3717,21 +3717,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550364</v>
+        <v>550383</v>
       </c>
       <c r="R29" t="n">
-        <v>6994169</v>
+        <v>6993994</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3780,6 +3780,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3807,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004470</v>
+        <v>121004409</v>
       </c>
       <c r="B30" t="n">
-        <v>90623</v>
+        <v>91985</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3819,25 +3824,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3242</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3850,10 +3855,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550383</v>
+        <v>550413</v>
       </c>
       <c r="R30" t="n">
-        <v>6993994</v>
+        <v>6994137</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3886,11 +3891,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004524</v>
+        <v>121004550</v>
       </c>
       <c r="B31" t="n">
-        <v>91973</v>
+        <v>80558</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3930,25 +3930,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550502</v>
+        <v>550508</v>
       </c>
       <c r="R31" t="n">
-        <v>6993935</v>
+        <v>6994113</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004439</v>
+        <v>121004475</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4036,25 +4036,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550405</v>
+        <v>550385</v>
       </c>
       <c r="R32" t="n">
-        <v>6994090</v>
+        <v>6993920</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4103,11 +4103,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,10 +4130,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004515</v>
+        <v>121004368</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>92001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4151,21 +4146,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4178,10 +4173,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550464</v>
+        <v>550364</v>
       </c>
       <c r="R33" t="n">
-        <v>6993901</v>
+        <v>6994169</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4241,7 +4236,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004394</v>
+        <v>121004500</v>
       </c>
       <c r="B34" t="n">
         <v>91973</v>
@@ -4284,10 +4279,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550381</v>
+        <v>550496</v>
       </c>
       <c r="R34" t="n">
-        <v>6994155</v>
+        <v>6993817</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4347,10 +4342,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004368</v>
+        <v>121004539</v>
       </c>
       <c r="B35" t="n">
-        <v>92001</v>
+        <v>89753</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4363,21 +4358,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4390,10 +4385,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550364</v>
+        <v>550486</v>
       </c>
       <c r="R35" t="n">
-        <v>6994169</v>
+        <v>6994062</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4453,10 +4448,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004541</v>
+        <v>121004511</v>
       </c>
       <c r="B36" t="n">
-        <v>91973</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4465,25 +4460,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4496,10 +4491,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550528</v>
+        <v>550470</v>
       </c>
       <c r="R36" t="n">
-        <v>6994067</v>
+        <v>6993852</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4532,6 +4527,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4559,7 +4559,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004341</v>
+        <v>121004509</v>
       </c>
       <c r="B37" t="n">
         <v>91973</v>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550344</v>
+        <v>550476</v>
       </c>
       <c r="R37" t="n">
-        <v>6994160</v>
+        <v>6993841</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004509</v>
+        <v>121004454</v>
       </c>
       <c r="B38" t="n">
-        <v>91973</v>
+        <v>95628</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4677,30 +4677,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4708,10 +4709,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550476</v>
+        <v>550389</v>
       </c>
       <c r="R38" t="n">
-        <v>6993841</v>
+        <v>6994068</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4771,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004514</v>
+        <v>121004341</v>
       </c>
       <c r="B39" t="n">
-        <v>90944</v>
+        <v>91973</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4783,25 +4784,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4815,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550464</v>
+        <v>550344</v>
       </c>
       <c r="R39" t="n">
-        <v>6993901</v>
+        <v>6994160</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4877,10 +4878,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004351</v>
+        <v>121004547</v>
       </c>
       <c r="B40" t="n">
-        <v>90623</v>
+        <v>91973</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4889,25 +4890,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4920,10 +4921,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550358</v>
+        <v>550493</v>
       </c>
       <c r="R40" t="n">
-        <v>6994160</v>
+        <v>6994078</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4983,10 +4984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004475</v>
+        <v>121004362</v>
       </c>
       <c r="B41" t="n">
-        <v>91973</v>
+        <v>89753</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4995,25 +4996,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550385</v>
+        <v>550364</v>
       </c>
       <c r="R41" t="n">
-        <v>6993920</v>
+        <v>6994169</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5089,10 +5090,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004409</v>
+        <v>121004540</v>
       </c>
       <c r="B42" t="n">
-        <v>91985</v>
+        <v>91973</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5105,21 +5106,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5132,10 +5133,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550413</v>
+        <v>550505</v>
       </c>
       <c r="R42" t="n">
-        <v>6994137</v>
+        <v>6994074</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5195,10 +5196,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004533</v>
+        <v>121004351</v>
       </c>
       <c r="B43" t="n">
-        <v>79219</v>
+        <v>90623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5211,21 +5212,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5238,10 +5239,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550456</v>
+        <v>550358</v>
       </c>
       <c r="R43" t="n">
-        <v>6993982</v>
+        <v>6994160</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5274,11 +5275,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,10 +5302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121004454</v>
+        <v>121004374</v>
       </c>
       <c r="B44" t="n">
-        <v>95628</v>
+        <v>79219</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5322,27 +5318,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5350,10 +5345,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550389</v>
+        <v>550369</v>
       </c>
       <c r="R44" t="n">
-        <v>6994068</v>
+        <v>6994167</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5413,10 +5408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004537</v>
+        <v>121004536</v>
       </c>
       <c r="B45" t="n">
-        <v>91973</v>
+        <v>80558</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5425,25 +5420,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5519,10 +5514,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004446</v>
+        <v>121004430</v>
       </c>
       <c r="B46" t="n">
-        <v>92001</v>
+        <v>91973</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5531,25 +5526,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5562,10 +5557,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550416</v>
+        <v>550422</v>
       </c>
       <c r="R46" t="n">
-        <v>6994077</v>
+        <v>6994093</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5625,10 +5620,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004536</v>
+        <v>121004450</v>
       </c>
       <c r="B47" t="n">
-        <v>80558</v>
+        <v>78601</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5641,21 +5636,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5668,10 +5663,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550477</v>
+        <v>550379</v>
       </c>
       <c r="R47" t="n">
-        <v>6994042</v>
+        <v>6994086</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5731,10 +5726,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004511</v>
+        <v>121004533</v>
       </c>
       <c r="B48" t="n">
-        <v>78601</v>
+        <v>79219</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5747,21 +5742,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5774,10 +5769,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550470</v>
+        <v>550456</v>
       </c>
       <c r="R48" t="n">
-        <v>6993852</v>
+        <v>6993982</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5814,7 +5809,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5842,10 +5837,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004374</v>
+        <v>121004521</v>
       </c>
       <c r="B49" t="n">
-        <v>79219</v>
+        <v>79682</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5858,21 +5853,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5885,10 +5880,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550369</v>
+        <v>550494</v>
       </c>
       <c r="R49" t="n">
-        <v>6994167</v>
+        <v>6993901</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5921,6 +5916,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,10 +5948,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004472</v>
+        <v>121004446</v>
       </c>
       <c r="B50" t="n">
-        <v>90851</v>
+        <v>92001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5960,25 +5960,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550400</v>
+        <v>550416</v>
       </c>
       <c r="R50" t="n">
-        <v>6993983</v>
+        <v>6994077</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6054,10 +6054,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004540</v>
+        <v>121004358</v>
       </c>
       <c r="B51" t="n">
-        <v>91973</v>
+        <v>78601</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6066,25 +6066,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550505</v>
+        <v>550362</v>
       </c>
       <c r="R51" t="n">
-        <v>6994074</v>
+        <v>6994156</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6160,10 +6160,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004550</v>
+        <v>121004524</v>
       </c>
       <c r="B52" t="n">
-        <v>80558</v>
+        <v>91973</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6172,25 +6172,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550508</v>
+        <v>550502</v>
       </c>
       <c r="R52" t="n">
-        <v>6994113</v>
+        <v>6993935</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004358</v>
+        <v>121004349</v>
       </c>
       <c r="B53" t="n">
-        <v>78601</v>
+        <v>79219</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550362</v>
+        <v>550358</v>
       </c>
       <c r="R53" t="n">
-        <v>6994156</v>
+        <v>6994160</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121004558</v>
+        <v>121004505</v>
       </c>
       <c r="B55" t="n">
         <v>98081</v>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550516</v>
+        <v>550496</v>
       </c>
       <c r="R55" t="n">
-        <v>6994130</v>
+        <v>6993835</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6585,7 +6585,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004562</v>
+        <v>121004558</v>
       </c>
       <c r="B56" t="n">
         <v>98081</v>
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550520</v>
+        <v>550516</v>
       </c>
       <c r="R56" t="n">
-        <v>6994154</v>
+        <v>6994130</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6692,7 +6692,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004405</v>
+        <v>121004519</v>
       </c>
       <c r="B57" t="n">
         <v>98081</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550404</v>
+        <v>550494</v>
       </c>
       <c r="R57" t="n">
-        <v>6994153</v>
+        <v>6993901</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6772,6 +6772,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6799,7 +6804,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004505</v>
+        <v>121004562</v>
       </c>
       <c r="B58" t="n">
         <v>98081</v>
@@ -6843,10 +6848,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550496</v>
+        <v>550520</v>
       </c>
       <c r="R58" t="n">
-        <v>6993835</v>
+        <v>6994154</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6906,7 +6911,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004422</v>
+        <v>121004405</v>
       </c>
       <c r="B59" t="n">
         <v>98081</v>
@@ -6950,10 +6955,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550395</v>
+        <v>550404</v>
       </c>
       <c r="R59" t="n">
-        <v>6994127</v>
+        <v>6994153</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7120,7 +7125,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004519</v>
+        <v>121004422</v>
       </c>
       <c r="B61" t="n">
         <v>98081</v>
@@ -7164,10 +7169,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550494</v>
+        <v>550395</v>
       </c>
       <c r="R61" t="n">
-        <v>6993901</v>
+        <v>6994127</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7200,11 +7205,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7339,10 +7339,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004449</v>
+        <v>121004494</v>
       </c>
       <c r="B63" t="n">
-        <v>88024</v>
+        <v>91977</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550379</v>
+        <v>550515</v>
       </c>
       <c r="R63" t="n">
-        <v>6994086</v>
+        <v>6993816</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121004494</v>
+        <v>121004449</v>
       </c>
       <c r="B65" t="n">
-        <v>91977</v>
+        <v>88024</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7563,25 +7563,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550515</v>
+        <v>550379</v>
       </c>
       <c r="R65" t="n">
-        <v>6993816</v>
+        <v>6994086</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004541</v>
+        <v>121004475</v>
       </c>
       <c r="B17" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550528</v>
+        <v>550385</v>
       </c>
       <c r="R17" t="n">
-        <v>6994067</v>
+        <v>6993920</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121004537</v>
+        <v>121004521</v>
       </c>
       <c r="B18" t="n">
-        <v>91973</v>
+        <v>79685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,25 +2533,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550477</v>
+        <v>550494</v>
       </c>
       <c r="R18" t="n">
-        <v>6994042</v>
+        <v>6993901</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2600,6 +2600,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004515</v>
+        <v>121004509</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,25 +2644,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2670,10 +2675,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550464</v>
+        <v>550476</v>
       </c>
       <c r="R19" t="n">
-        <v>6993901</v>
+        <v>6993841</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2733,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004439</v>
+        <v>121004515</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2776,10 +2781,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550405</v>
+        <v>550464</v>
       </c>
       <c r="R20" t="n">
-        <v>6994090</v>
+        <v>6993901</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2812,11 +2817,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,10 +2844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004399</v>
+        <v>121004358</v>
       </c>
       <c r="B21" t="n">
-        <v>91973</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,25 +2856,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550384</v>
+        <v>550362</v>
       </c>
       <c r="R21" t="n">
-        <v>6994151</v>
+        <v>6994156</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004514</v>
+        <v>121004351</v>
       </c>
       <c r="B22" t="n">
-        <v>90944</v>
+        <v>90635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,25 +2962,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550464</v>
+        <v>550358</v>
       </c>
       <c r="R22" t="n">
-        <v>6993901</v>
+        <v>6994160</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004472</v>
+        <v>121004541</v>
       </c>
       <c r="B23" t="n">
-        <v>90851</v>
+        <v>91985</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,25 +3068,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550400</v>
+        <v>550528</v>
       </c>
       <c r="R23" t="n">
-        <v>6993983</v>
+        <v>6994067</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004395</v>
+        <v>121004394</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,25 +3174,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121004394</v>
+        <v>121004536</v>
       </c>
       <c r="B25" t="n">
-        <v>91973</v>
+        <v>80561</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3280,25 +3280,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550381</v>
+        <v>550477</v>
       </c>
       <c r="R25" t="n">
-        <v>6994155</v>
+        <v>6994042</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3374,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004484</v>
+        <v>121004362</v>
       </c>
       <c r="B26" t="n">
-        <v>91973</v>
+        <v>89760</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,25 +3386,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550427</v>
+        <v>550364</v>
       </c>
       <c r="R26" t="n">
-        <v>6993867</v>
+        <v>6994169</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004525</v>
+        <v>121004547</v>
       </c>
       <c r="B27" t="n">
-        <v>56563</v>
+        <v>91985</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,42 +3496,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550502</v>
+        <v>550493</v>
       </c>
       <c r="R27" t="n">
-        <v>6993935</v>
+        <v>6994078</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3572,6 +3567,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3590,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004337</v>
+        <v>121004439</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3633,10 +3629,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550319</v>
+        <v>550405</v>
       </c>
       <c r="R28" t="n">
-        <v>6994143</v>
+        <v>6994090</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3673,7 +3669,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3701,10 +3697,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004470</v>
+        <v>121004399</v>
       </c>
       <c r="B29" t="n">
-        <v>90623</v>
+        <v>91985</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3713,25 +3709,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3740,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550383</v>
+        <v>550384</v>
       </c>
       <c r="R29" t="n">
-        <v>6993994</v>
+        <v>6994151</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3780,11 +3776,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3812,7 +3803,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004409</v>
+        <v>121004484</v>
       </c>
       <c r="B30" t="n">
         <v>91985</v>
@@ -3828,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3855,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550413</v>
+        <v>550427</v>
       </c>
       <c r="R30" t="n">
-        <v>6994137</v>
+        <v>6993867</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3918,10 +3909,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004550</v>
+        <v>121004450</v>
       </c>
       <c r="B31" t="n">
-        <v>80558</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3934,21 +3925,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3961,10 +3952,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550508</v>
+        <v>550379</v>
       </c>
       <c r="R31" t="n">
-        <v>6994113</v>
+        <v>6994086</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4024,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004475</v>
+        <v>121004533</v>
       </c>
       <c r="B32" t="n">
-        <v>91973</v>
+        <v>79222</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4036,25 +4027,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4067,10 +4058,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550385</v>
+        <v>550456</v>
       </c>
       <c r="R32" t="n">
-        <v>6993920</v>
+        <v>6993982</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4103,6 +4094,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4130,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004368</v>
+        <v>121004524</v>
       </c>
       <c r="B33" t="n">
-        <v>92001</v>
+        <v>91985</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4142,25 +4138,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4173,10 +4169,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550364</v>
+        <v>550502</v>
       </c>
       <c r="R33" t="n">
-        <v>6994169</v>
+        <v>6993935</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4236,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004500</v>
+        <v>121004430</v>
       </c>
       <c r="B34" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4279,10 +4275,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550496</v>
+        <v>550422</v>
       </c>
       <c r="R34" t="n">
-        <v>6993817</v>
+        <v>6994093</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4342,10 +4338,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004539</v>
+        <v>121004337</v>
       </c>
       <c r="B35" t="n">
-        <v>89753</v>
+        <v>78604</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4358,21 +4354,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4385,10 +4381,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550486</v>
+        <v>550319</v>
       </c>
       <c r="R35" t="n">
-        <v>6994062</v>
+        <v>6994143</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4421,6 +4417,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4451,7 +4452,7 @@
         <v>121004511</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4559,10 +4560,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004509</v>
+        <v>121004470</v>
       </c>
       <c r="B37" t="n">
-        <v>91973</v>
+        <v>90635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4571,25 +4572,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4602,10 +4603,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550476</v>
+        <v>550383</v>
       </c>
       <c r="R37" t="n">
-        <v>6993841</v>
+        <v>6993994</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4638,6 +4639,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,10 +4671,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004454</v>
+        <v>121004446</v>
       </c>
       <c r="B38" t="n">
-        <v>95628</v>
+        <v>92013</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4681,27 +4687,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4709,10 +4714,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550389</v>
+        <v>550416</v>
       </c>
       <c r="R38" t="n">
-        <v>6994068</v>
+        <v>6994077</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4772,10 +4777,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004341</v>
+        <v>121004525</v>
       </c>
       <c r="B39" t="n">
-        <v>91973</v>
+        <v>56563</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4788,37 +4793,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550344</v>
+        <v>550502</v>
       </c>
       <c r="R39" t="n">
-        <v>6994160</v>
+        <v>6993935</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4859,7 +4869,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4878,10 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004547</v>
+        <v>121004395</v>
       </c>
       <c r="B40" t="n">
-        <v>91973</v>
+        <v>78604</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4890,25 +4899,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4921,10 +4930,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550493</v>
+        <v>550381</v>
       </c>
       <c r="R40" t="n">
-        <v>6994078</v>
+        <v>6994155</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4984,10 +4993,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004362</v>
+        <v>121004409</v>
       </c>
       <c r="B41" t="n">
-        <v>89753</v>
+        <v>91997</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4996,25 +5005,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5027,10 +5036,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550364</v>
+        <v>550413</v>
       </c>
       <c r="R41" t="n">
-        <v>6994169</v>
+        <v>6994137</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5090,10 +5099,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004540</v>
+        <v>121004539</v>
       </c>
       <c r="B42" t="n">
-        <v>91973</v>
+        <v>89760</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5102,25 +5111,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5133,10 +5142,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550505</v>
+        <v>550486</v>
       </c>
       <c r="R42" t="n">
-        <v>6994074</v>
+        <v>6994062</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5196,10 +5205,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004351</v>
+        <v>121004540</v>
       </c>
       <c r="B43" t="n">
-        <v>90623</v>
+        <v>91985</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5208,25 +5217,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5239,10 +5248,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550358</v>
+        <v>550505</v>
       </c>
       <c r="R43" t="n">
-        <v>6994160</v>
+        <v>6994074</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5302,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121004374</v>
+        <v>121004368</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>92013</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5318,21 +5327,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5345,10 +5354,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550369</v>
+        <v>550364</v>
       </c>
       <c r="R44" t="n">
-        <v>6994167</v>
+        <v>6994169</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5408,10 +5417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004536</v>
+        <v>121004550</v>
       </c>
       <c r="B45" t="n">
-        <v>80558</v>
+        <v>80561</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5451,10 +5460,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550477</v>
+        <v>550508</v>
       </c>
       <c r="R45" t="n">
-        <v>6994042</v>
+        <v>6994113</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5514,10 +5523,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004430</v>
+        <v>121004374</v>
       </c>
       <c r="B46" t="n">
-        <v>91973</v>
+        <v>79222</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5526,25 +5535,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5557,10 +5566,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550422</v>
+        <v>550369</v>
       </c>
       <c r="R46" t="n">
-        <v>6994093</v>
+        <v>6994167</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5620,10 +5629,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004450</v>
+        <v>121004341</v>
       </c>
       <c r="B47" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5632,25 +5641,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5663,10 +5672,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550379</v>
+        <v>550344</v>
       </c>
       <c r="R47" t="n">
-        <v>6994086</v>
+        <v>6994160</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5726,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004533</v>
+        <v>121004537</v>
       </c>
       <c r="B48" t="n">
-        <v>79219</v>
+        <v>91985</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5738,25 +5747,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5769,10 +5778,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550456</v>
+        <v>550477</v>
       </c>
       <c r="R48" t="n">
-        <v>6993982</v>
+        <v>6994042</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5805,11 +5814,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5837,10 +5841,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004521</v>
+        <v>121004472</v>
       </c>
       <c r="B49" t="n">
-        <v>79682</v>
+        <v>90863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5849,25 +5853,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5880,10 +5884,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550494</v>
+        <v>550400</v>
       </c>
       <c r="R49" t="n">
-        <v>6993901</v>
+        <v>6993983</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5916,11 +5920,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5948,10 +5947,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004446</v>
+        <v>121004514</v>
       </c>
       <c r="B50" t="n">
-        <v>92001</v>
+        <v>90956</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5960,25 +5959,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>65</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5991,10 +5990,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550416</v>
+        <v>550464</v>
       </c>
       <c r="R50" t="n">
-        <v>6994077</v>
+        <v>6993901</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6054,10 +6053,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004358</v>
+        <v>121004349</v>
       </c>
       <c r="B51" t="n">
-        <v>78601</v>
+        <v>79222</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6070,21 +6069,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6097,10 +6096,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550362</v>
+        <v>550358</v>
       </c>
       <c r="R51" t="n">
-        <v>6994156</v>
+        <v>6994160</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6160,10 +6159,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004524</v>
+        <v>121004500</v>
       </c>
       <c r="B52" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6203,10 +6202,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550502</v>
+        <v>550496</v>
       </c>
       <c r="R52" t="n">
-        <v>6993935</v>
+        <v>6993817</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6266,10 +6265,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004349</v>
+        <v>121004454</v>
       </c>
       <c r="B53" t="n">
-        <v>79219</v>
+        <v>95641</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6282,26 +6281,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550358</v>
+        <v>550389</v>
       </c>
       <c r="R53" t="n">
-        <v>6994160</v>
+        <v>6994068</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6375,7 +6375,7 @@
         <v>121004416</v>
       </c>
       <c r="B54" t="n">
-        <v>90851</v>
+        <v>90863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121004505</v>
+        <v>121004565</v>
       </c>
       <c r="B55" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550496</v>
+        <v>550469</v>
       </c>
       <c r="R55" t="n">
-        <v>6993835</v>
+        <v>6994270</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6588,7 +6588,7 @@
         <v>121004558</v>
       </c>
       <c r="B56" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004519</v>
+        <v>121004477</v>
       </c>
       <c r="B57" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550494</v>
+        <v>550370</v>
       </c>
       <c r="R57" t="n">
-        <v>6993901</v>
+        <v>6993853</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6772,11 +6772,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6804,10 +6799,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004562</v>
+        <v>121004505</v>
       </c>
       <c r="B58" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6848,10 +6843,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550520</v>
+        <v>550496</v>
       </c>
       <c r="R58" t="n">
-        <v>6994154</v>
+        <v>6993835</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6911,10 +6906,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004405</v>
+        <v>121004519</v>
       </c>
       <c r="B59" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6955,10 +6950,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550404</v>
+        <v>550494</v>
       </c>
       <c r="R59" t="n">
-        <v>6994153</v>
+        <v>6993901</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6991,6 +6986,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7018,10 +7018,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004565</v>
+        <v>121004422</v>
       </c>
       <c r="B60" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550469</v>
+        <v>550395</v>
       </c>
       <c r="R60" t="n">
-        <v>6994270</v>
+        <v>6994127</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7125,10 +7125,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004422</v>
+        <v>121004562</v>
       </c>
       <c r="B61" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7169,10 +7169,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550395</v>
+        <v>550520</v>
       </c>
       <c r="R61" t="n">
-        <v>6994127</v>
+        <v>6994154</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121004477</v>
+        <v>121004405</v>
       </c>
       <c r="B62" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550370</v>
+        <v>550404</v>
       </c>
       <c r="R62" t="n">
-        <v>6993853</v>
+        <v>6994153</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7342,7 +7342,7 @@
         <v>121004494</v>
       </c>
       <c r="B63" t="n">
-        <v>91977</v>
+        <v>91989</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7445,10 +7445,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121004545</v>
+        <v>121004449</v>
       </c>
       <c r="B64" t="n">
-        <v>91977</v>
+        <v>88031</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7457,25 +7457,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4365</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550493</v>
+        <v>550379</v>
       </c>
       <c r="R64" t="n">
-        <v>6994078</v>
+        <v>6994086</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121004449</v>
+        <v>121004545</v>
       </c>
       <c r="B65" t="n">
-        <v>88024</v>
+        <v>91989</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7563,25 +7563,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>510</v>
+        <v>4365</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550379</v>
+        <v>550493</v>
       </c>
       <c r="R65" t="n">
-        <v>6994086</v>
+        <v>6994078</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -6481,7 +6481,7 @@
         <v>121004565</v>
       </c>
       <c r="B55" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6585,10 +6585,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004558</v>
+        <v>121004422</v>
       </c>
       <c r="B56" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550516</v>
+        <v>550395</v>
       </c>
       <c r="R56" t="n">
-        <v>6994130</v>
+        <v>6994127</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004477</v>
+        <v>121004558</v>
       </c>
       <c r="B57" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550370</v>
+        <v>550516</v>
       </c>
       <c r="R57" t="n">
-        <v>6993853</v>
+        <v>6994130</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6799,10 +6799,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004505</v>
+        <v>121004562</v>
       </c>
       <c r="B58" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550496</v>
+        <v>550520</v>
       </c>
       <c r="R58" t="n">
-        <v>6993835</v>
+        <v>6994154</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6906,10 +6906,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004519</v>
+        <v>121004477</v>
       </c>
       <c r="B59" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550494</v>
+        <v>550370</v>
       </c>
       <c r="R59" t="n">
-        <v>6993901</v>
+        <v>6993853</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6986,11 +6986,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7018,10 +7013,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004422</v>
+        <v>121004405</v>
       </c>
       <c r="B60" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7062,10 +7057,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550395</v>
+        <v>550404</v>
       </c>
       <c r="R60" t="n">
-        <v>6994127</v>
+        <v>6994153</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7125,10 +7120,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004562</v>
+        <v>121004519</v>
       </c>
       <c r="B61" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7169,10 +7164,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550520</v>
+        <v>550494</v>
       </c>
       <c r="R61" t="n">
-        <v>6994154</v>
+        <v>6993901</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7205,6 +7200,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7232,10 +7232,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121004405</v>
+        <v>121004505</v>
       </c>
       <c r="B62" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550404</v>
+        <v>550496</v>
       </c>
       <c r="R62" t="n">
-        <v>6994153</v>
+        <v>6993835</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004494</v>
+        <v>121004545</v>
       </c>
       <c r="B63" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550515</v>
+        <v>550493</v>
       </c>
       <c r="R63" t="n">
-        <v>6993816</v>
+        <v>6994078</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121004545</v>
+        <v>121004494</v>
       </c>
       <c r="B65" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550493</v>
+        <v>550515</v>
       </c>
       <c r="R65" t="n">
-        <v>6994078</v>
+        <v>6993816</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7339,10 +7339,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004545</v>
+        <v>121004449</v>
       </c>
       <c r="B63" t="n">
-        <v>91990</v>
+        <v>88034</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>510</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550493</v>
+        <v>550379</v>
       </c>
       <c r="R63" t="n">
-        <v>6994078</v>
+        <v>6994086</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7445,10 +7445,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121004449</v>
+        <v>121004494</v>
       </c>
       <c r="B64" t="n">
-        <v>88031</v>
+        <v>91993</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7457,25 +7457,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>4365</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550379</v>
+        <v>550515</v>
       </c>
       <c r="R64" t="n">
-        <v>6994086</v>
+        <v>6993816</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7551,10 +7551,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121004494</v>
+        <v>121004545</v>
       </c>
       <c r="B65" t="n">
-        <v>91990</v>
+        <v>91993</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550515</v>
+        <v>550493</v>
       </c>
       <c r="R65" t="n">
-        <v>6993816</v>
+        <v>6994078</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7655,6 +7655,724 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126099630</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>550494</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6994148</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126099520</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80947</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>550419</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6994207</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126099534</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>550463</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6994172</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126099553</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79979</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>550465</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6994163</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126099588</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78639</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>353</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>550464</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6994104</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126099591</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79590</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>550464</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6994104</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,38 +7965,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B69" t="n">
-        <v>98339</v>
+        <v>79979</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8004,10 +8003,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R69" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8040,6 +8039,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8067,37 +8071,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>79979</v>
+        <v>98339</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R70" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8141,11 +8146,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,37 +7965,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B69" t="n">
-        <v>79979</v>
+        <v>98339</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8003,10 +8004,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R69" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8039,11 +8040,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,38 +8067,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B70" t="n">
-        <v>98339</v>
+        <v>79979</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R70" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8146,6 +8141,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>126099630</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>126099623</v>
       </c>
       <c r="B67" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>126099520</v>
       </c>
       <c r="B68" t="n">
-        <v>80947</v>
+        <v>80948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7965,38 +7965,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B69" t="n">
-        <v>98339</v>
+        <v>79980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8004,10 +8003,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R69" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8040,6 +8039,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8067,37 +8071,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>79979</v>
+        <v>98341</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R70" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8141,11 +8146,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8176,7 +8176,7 @@
         <v>126099588</v>
       </c>
       <c r="B71" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>126099591</v>
       </c>
       <c r="B72" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,37 +7965,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B69" t="n">
-        <v>79980</v>
+        <v>98343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8003,10 +8004,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R69" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8039,11 +8040,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,38 +8067,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B70" t="n">
-        <v>98341</v>
+        <v>79980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R70" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8146,6 +8141,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,38 +7965,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B69" t="n">
-        <v>98343</v>
+        <v>79980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8004,10 +8003,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R69" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8040,6 +8039,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8067,37 +8071,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>79980</v>
+        <v>98343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R70" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8141,11 +8146,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -8074,7 +8074,7 @@
         <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,37 +7965,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B69" t="n">
-        <v>79980</v>
+        <v>98345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8003,10 +8004,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R69" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8039,11 +8040,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,38 +8067,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B70" t="n">
-        <v>98345</v>
+        <v>79980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R70" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8146,6 +8141,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>126099630</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>126099623</v>
       </c>
       <c r="B67" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>126099520</v>
       </c>
       <c r="B68" t="n">
-        <v>80948</v>
+        <v>80952</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7965,38 +7965,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B69" t="n">
-        <v>98345</v>
+        <v>79984</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8004,10 +8003,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R69" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8040,6 +8039,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8067,37 +8071,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>79980</v>
+        <v>98349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R70" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8141,11 +8146,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8176,7 +8176,7 @@
         <v>126099588</v>
       </c>
       <c r="B71" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>126099591</v>
       </c>
       <c r="B72" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,37 +7965,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B69" t="n">
-        <v>79984</v>
+        <v>98352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8003,10 +8004,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R69" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8039,11 +8040,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,38 +8067,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B70" t="n">
-        <v>98349</v>
+        <v>79984</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R70" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8146,6 +8141,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,38 +7965,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B69" t="n">
-        <v>98352</v>
+        <v>79984</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8004,10 +8003,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R69" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8040,6 +8039,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8067,37 +8071,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>79984</v>
+        <v>98352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R70" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8141,11 +8146,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>126099630</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>126099623</v>
       </c>
       <c r="B67" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>126099520</v>
       </c>
       <c r="B68" t="n">
-        <v>80952</v>
+        <v>80955</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>126099553</v>
       </c>
       <c r="B69" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>126099588</v>
       </c>
       <c r="B71" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>126099591</v>
       </c>
       <c r="B72" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,37 +7965,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B69" t="n">
-        <v>79987</v>
+        <v>98361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8003,10 +8004,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R69" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8039,11 +8040,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8071,38 +8067,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B70" t="n">
-        <v>98361</v>
+        <v>79987</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R70" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8146,6 +8141,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -7965,38 +7965,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099534</v>
+        <v>126099553</v>
       </c>
       <c r="B69" t="n">
-        <v>98361</v>
+        <v>79987</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8004,10 +8003,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550463</v>
+        <v>550465</v>
       </c>
       <c r="R69" t="n">
-        <v>6994172</v>
+        <v>6994163</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8040,6 +8039,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8067,37 +8071,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099553</v>
+        <v>126099534</v>
       </c>
       <c r="B70" t="n">
-        <v>79987</v>
+        <v>98361</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8105,10 +8110,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550465</v>
+        <v>550463</v>
       </c>
       <c r="R70" t="n">
-        <v>6994163</v>
+        <v>6994172</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8141,11 +8146,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -6032,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8373,6 +8373,394 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134246393</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>550548</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6994192</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134246394</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>550512</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6994236</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134246388</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99178</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>550414</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6994084</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -8378,7 +8378,7 @@
         <v>134246393</v>
       </c>
       <c r="B73" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>134246394</v>
       </c>
       <c r="B74" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>134246388</v>
       </c>
       <c r="B75" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>134246390</v>
       </c>
       <c r="B76" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -8378,7 +8378,7 @@
         <v>134246393</v>
       </c>
       <c r="B73" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>134246394</v>
       </c>
       <c r="B74" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>134246388</v>
       </c>
       <c r="B75" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>134246390</v>
       </c>
       <c r="B76" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62025591</v>
+        <v>102089262</v>
       </c>
       <c r="B2" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550408.5211163756</v>
+        <v>550543</v>
       </c>
       <c r="R2" t="n">
-        <v>6994047.796887696</v>
+        <v>6994131</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,79 +758,68 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62025592</v>
+        <v>121004454</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550408.5211163756</v>
+        <v>550389</v>
       </c>
       <c r="R3" t="n">
-        <v>6994047.796887696</v>
+        <v>6994068</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,80 +857,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102089262</v>
+        <v>121004514</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550543.4065316274</v>
+        <v>550464</v>
       </c>
       <c r="R4" t="n">
-        <v>6994131.493256809</v>
+        <v>6993901</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,30 +944,21 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1033,52 +977,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102089819</v>
+        <v>126099588</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550446.0249367467</v>
+        <v>550464</v>
       </c>
       <c r="R5" t="n">
-        <v>6994088.272614149</v>
+        <v>6994104</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,22 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,6 +1059,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1147,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102089929</v>
+        <v>121004449</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,35 +1089,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550373.0330584078</v>
+        <v>550379</v>
       </c>
       <c r="R6" t="n">
-        <v>6994082.152641956</v>
+        <v>6994086</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,22 +1146,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,6 +1160,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,54 +1179,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102089806</v>
+        <v>62025590</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550469.0935862692</v>
+        <v>550309</v>
       </c>
       <c r="R7" t="n">
-        <v>6994093.617761243</v>
+        <v>6994262</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,22 +1244,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,67 +1260,74 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Klen, gammal sälg</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102089933</v>
+        <v>121004536</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550373.0330584078</v>
+        <v>550477</v>
       </c>
       <c r="R8" t="n">
-        <v>6994082.152641956</v>
+        <v>6994042</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,22 +1354,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,6 +1368,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1486,51 +1387,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102089938</v>
+        <v>121004550</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550373.0330584078</v>
+        <v>550508</v>
       </c>
       <c r="R9" t="n">
-        <v>6994082.152641956</v>
+        <v>6994113</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,22 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,6 +1469,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1599,15 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102089839</v>
+        <v>126099520</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,35 +1499,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550410.8747009736</v>
+        <v>550419</v>
       </c>
       <c r="R10" t="n">
-        <v>6994100.873143715</v>
+        <v>6994207</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,22 +1556,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,6 +1570,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1712,37 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102089700</v>
+        <v>102089224</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550476.456629602</v>
+        <v>550562</v>
       </c>
       <c r="R11" t="n">
-        <v>6994116.398577471</v>
+        <v>6994152</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,19 +1658,9 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,51 +1687,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102089935</v>
+        <v>121004416</v>
       </c>
       <c r="B12" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550373.0330584078</v>
+        <v>550398</v>
       </c>
       <c r="R12" t="n">
-        <v>6994082.152641956</v>
+        <v>6994131</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1896,22 +1755,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,6 +1769,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1938,15 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102089419</v>
+        <v>121004472</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,36 +1799,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550554.2845792349</v>
+        <v>550400</v>
       </c>
       <c r="R13" t="n">
-        <v>6994132.569277804</v>
+        <v>6993983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2010,22 +1856,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,6 +1870,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2052,53 +1889,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103996080</v>
+        <v>121004362</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550484.8090286197</v>
+        <v>550364</v>
       </c>
       <c r="R14" t="n">
-        <v>6994104.741969333</v>
+        <v>6994169</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2122,22 +1957,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,13 +1971,9 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2162,64 +1983,58 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103996059</v>
+        <v>121004490</v>
       </c>
       <c r="B15" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550309.7225877922</v>
+        <v>550508</v>
       </c>
       <c r="R15" t="n">
-        <v>6994183.621786926</v>
+        <v>6993803</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,22 +2058,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,13 +2072,9 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2283,64 +2084,58 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103996072</v>
+        <v>121004539</v>
       </c>
       <c r="B16" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550481.3023009888</v>
+        <v>550486</v>
       </c>
       <c r="R16" t="n">
-        <v>6994067.51441453</v>
+        <v>6994062</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,22 +2159,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,13 +2173,9 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2404,67 +2185,55 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004475</v>
+        <v>62025591</v>
       </c>
       <c r="B17" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550385</v>
+        <v>550409</v>
       </c>
       <c r="R17" t="n">
-        <v>6993920</v>
+        <v>6994048</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2488,12 +2257,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,34 +2271,38 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121004521</v>
+        <v>102089002</v>
       </c>
       <c r="B18" t="n">
-        <v>79685</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,37 +2310,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550494</v>
+        <v>550570</v>
       </c>
       <c r="R18" t="n">
-        <v>6993901</v>
+        <v>6994156</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2594,12 +2365,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2613,7 +2384,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2632,15 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004509</v>
+        <v>103996059</v>
       </c>
       <c r="B19" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2648,40 +2413,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550476</v>
+        <v>550310</v>
       </c>
       <c r="R19" t="n">
-        <v>6993841</v>
+        <v>6994183</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2705,12 +2467,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,9 +2491,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2731,22 +2507,21 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004515</v>
+        <v>121004351</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2781,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550464</v>
+        <v>550358</v>
       </c>
       <c r="R20" t="n">
-        <v>6993901</v>
+        <v>6994160</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2844,15 +2619,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004358</v>
+        <v>121004470</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,21 +2630,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550362</v>
+        <v>550383</v>
       </c>
       <c r="R21" t="n">
-        <v>6994156</v>
+        <v>6993994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2923,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,15 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004351</v>
+        <v>62025592</v>
       </c>
       <c r="B22" t="n">
-        <v>90635</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,40 +2736,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550358</v>
+        <v>550409</v>
       </c>
       <c r="R22" t="n">
-        <v>6994160</v>
+        <v>6994048</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3023,12 +2790,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,38 +2804,42 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004541</v>
+        <v>102089700</v>
       </c>
       <c r="B23" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3090,19 +2861,17 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550528</v>
+        <v>550476</v>
       </c>
       <c r="R23" t="n">
-        <v>6994067</v>
+        <v>6994117</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3129,12 +2898,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3162,19 +2930,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004394</v>
+        <v>103996072</v>
       </c>
       <c r="B24" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3196,22 +2959,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550381</v>
+        <v>550481</v>
       </c>
       <c r="R24" t="n">
-        <v>6994155</v>
+        <v>6994068</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3235,12 +2995,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,9 +3019,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3261,22 +3035,21 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121004536</v>
+        <v>103996080</v>
       </c>
       <c r="B25" t="n">
-        <v>80561</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,40 +3057,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550477</v>
+        <v>550485</v>
       </c>
       <c r="R25" t="n">
-        <v>6994042</v>
+        <v>6994105</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,12 +3111,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3355,9 +3135,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3367,22 +3151,21 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004362</v>
+        <v>121004341</v>
       </c>
       <c r="B26" t="n">
-        <v>89760</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,21 +3173,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550364</v>
+        <v>550344</v>
       </c>
       <c r="R26" t="n">
-        <v>6994169</v>
+        <v>6994160</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3480,19 +3263,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004547</v>
+        <v>121004394</v>
       </c>
       <c r="B27" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3523,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550493</v>
+        <v>550381</v>
       </c>
       <c r="R27" t="n">
-        <v>6994078</v>
+        <v>6994155</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3586,15 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004439</v>
+        <v>121004399</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,21 +3375,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3629,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550405</v>
+        <v>550384</v>
       </c>
       <c r="R28" t="n">
-        <v>6994090</v>
+        <v>6994151</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3665,11 +3438,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3697,19 +3465,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004399</v>
+        <v>121004430</v>
       </c>
       <c r="B29" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3740,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550384</v>
+        <v>550422</v>
       </c>
       <c r="R29" t="n">
-        <v>6994151</v>
+        <v>6994093</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3803,19 +3566,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004484</v>
+        <v>121004475</v>
       </c>
       <c r="B30" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3846,10 +3604,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550427</v>
+        <v>550385</v>
       </c>
       <c r="R30" t="n">
-        <v>6993867</v>
+        <v>6993920</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3909,15 +3667,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004450</v>
+        <v>121004484</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3925,21 +3678,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3952,10 +3705,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550379</v>
+        <v>550427</v>
       </c>
       <c r="R31" t="n">
-        <v>6994086</v>
+        <v>6993867</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4015,15 +3768,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004533</v>
+        <v>121004500</v>
       </c>
       <c r="B32" t="n">
-        <v>79222</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4031,21 +3779,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4058,10 +3806,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550456</v>
+        <v>550496</v>
       </c>
       <c r="R32" t="n">
-        <v>6993982</v>
+        <v>6993817</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4094,11 +3842,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4126,19 +3869,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004524</v>
+        <v>121004509</v>
       </c>
       <c r="B33" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4169,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550502</v>
+        <v>550476</v>
       </c>
       <c r="R33" t="n">
-        <v>6993935</v>
+        <v>6993841</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4232,19 +3970,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004430</v>
+        <v>121004524</v>
       </c>
       <c r="B34" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4275,10 +4008,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550422</v>
+        <v>550502</v>
       </c>
       <c r="R34" t="n">
-        <v>6994093</v>
+        <v>6993935</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4338,15 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004337</v>
+        <v>121004537</v>
       </c>
       <c r="B35" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,21 +4082,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4381,10 +4109,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550319</v>
+        <v>550477</v>
       </c>
       <c r="R35" t="n">
-        <v>6994143</v>
+        <v>6994042</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4417,11 +4145,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4449,15 +4172,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004511</v>
+        <v>121004540</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,21 +4183,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4492,10 +4210,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550470</v>
+        <v>550505</v>
       </c>
       <c r="R36" t="n">
-        <v>6993852</v>
+        <v>6994074</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4528,11 +4246,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4560,15 +4273,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004470</v>
+        <v>121004541</v>
       </c>
       <c r="B37" t="n">
-        <v>90635</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,21 +4284,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4603,10 +4311,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550383</v>
+        <v>550528</v>
       </c>
       <c r="R37" t="n">
-        <v>6993994</v>
+        <v>6994067</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4639,11 +4347,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4671,15 +4374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004446</v>
+        <v>121004547</v>
       </c>
       <c r="B38" t="n">
-        <v>92013</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,21 +4385,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4714,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550416</v>
+        <v>550493</v>
       </c>
       <c r="R38" t="n">
-        <v>6994077</v>
+        <v>6994078</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4777,61 +4475,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004525</v>
+        <v>134246391</v>
       </c>
       <c r="B39" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550502</v>
+        <v>550317</v>
       </c>
       <c r="R39" t="n">
-        <v>6993935</v>
+        <v>6994117</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4855,12 +4540,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4875,49 +4560,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004395</v>
+        <v>121004494</v>
       </c>
       <c r="B40" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4930,10 +4610,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550381</v>
+        <v>550515</v>
       </c>
       <c r="R40" t="n">
-        <v>6994155</v>
+        <v>6993816</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4993,37 +4673,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004409</v>
+        <v>121004545</v>
       </c>
       <c r="B41" t="n">
-        <v>91997</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5036,10 +4711,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550413</v>
+        <v>550493</v>
       </c>
       <c r="R41" t="n">
-        <v>6994137</v>
+        <v>6994078</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5099,15 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004539</v>
+        <v>121004409</v>
       </c>
       <c r="B42" t="n">
-        <v>89760</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5115,21 +4785,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5142,10 +4812,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550486</v>
+        <v>550413</v>
       </c>
       <c r="R42" t="n">
-        <v>6994062</v>
+        <v>6994137</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5205,53 +4875,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004540</v>
+        <v>102089839</v>
       </c>
       <c r="B43" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550505</v>
+        <v>550410</v>
       </c>
       <c r="R43" t="n">
-        <v>6994074</v>
+        <v>6994101</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5278,12 +4941,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5292,7 +4955,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5311,37 +4973,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121004368</v>
+        <v>121004337</v>
       </c>
       <c r="B44" t="n">
-        <v>92013</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5354,10 +5011,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550364</v>
+        <v>550319</v>
       </c>
       <c r="R44" t="n">
-        <v>6994169</v>
+        <v>6994143</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5390,6 +5047,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5417,37 +5079,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004550</v>
+        <v>121004358</v>
       </c>
       <c r="B45" t="n">
-        <v>80561</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5460,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550508</v>
+        <v>550362</v>
       </c>
       <c r="R45" t="n">
-        <v>6994113</v>
+        <v>6994156</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5523,37 +5180,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004374</v>
+        <v>121004395</v>
       </c>
       <c r="B46" t="n">
-        <v>79222</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5566,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550369</v>
+        <v>550381</v>
       </c>
       <c r="R46" t="n">
-        <v>6994167</v>
+        <v>6994155</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5629,37 +5281,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004341</v>
+        <v>121004439</v>
       </c>
       <c r="B47" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5672,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550344</v>
+        <v>550405</v>
       </c>
       <c r="R47" t="n">
-        <v>6994160</v>
+        <v>6994090</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5708,6 +5355,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5735,37 +5387,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004537</v>
+        <v>121004450</v>
       </c>
       <c r="B48" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5778,10 +5425,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550477</v>
+        <v>550379</v>
       </c>
       <c r="R48" t="n">
-        <v>6994042</v>
+        <v>6994086</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5841,15 +5488,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004472</v>
+        <v>121004511</v>
       </c>
       <c r="B49" t="n">
-        <v>90863</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5857,21 +5499,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5884,10 +5526,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550400</v>
+        <v>550470</v>
       </c>
       <c r="R49" t="n">
-        <v>6993983</v>
+        <v>6993852</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5920,6 +5562,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5947,15 +5594,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004514</v>
+        <v>121004515</v>
       </c>
       <c r="B50" t="n">
-        <v>90956</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5963,21 +5605,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6032,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
@@ -6053,37 +5695,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004349</v>
+        <v>126099630</v>
       </c>
       <c r="B51" t="n">
-        <v>79222</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6092,14 +5729,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550358</v>
+        <v>550494</v>
       </c>
       <c r="R51" t="n">
-        <v>6994160</v>
+        <v>6994148</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6126,12 +5763,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,56 +5801,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004500</v>
+        <v>134246394</v>
       </c>
       <c r="B52" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550496</v>
+        <v>550512</v>
       </c>
       <c r="R52" t="n">
-        <v>6993817</v>
+        <v>6994236</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6232,12 +5866,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6246,76 +5880,66 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004454</v>
+        <v>134246395</v>
       </c>
       <c r="B53" t="n">
-        <v>95641</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550389</v>
+        <v>550292</v>
       </c>
       <c r="R53" t="n">
-        <v>6994068</v>
+        <v>6994150</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6339,12 +5963,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6353,72 +5977,64 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121004416</v>
+        <v>102089806</v>
       </c>
       <c r="B54" t="n">
-        <v>90863</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550398</v>
+        <v>550469</v>
       </c>
       <c r="R54" t="n">
-        <v>6994131</v>
+        <v>6994094</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6445,12 +6061,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6459,7 +6075,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6478,43 +6093,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121004565</v>
+        <v>121004349</v>
       </c>
       <c r="B55" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6522,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550469</v>
+        <v>550358</v>
       </c>
       <c r="R55" t="n">
-        <v>6994270</v>
+        <v>6994160</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6585,43 +6194,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004422</v>
+        <v>121004374</v>
       </c>
       <c r="B56" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6629,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550395</v>
+        <v>550369</v>
       </c>
       <c r="R56" t="n">
-        <v>6994127</v>
+        <v>6994167</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6692,43 +6295,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004558</v>
+        <v>121004533</v>
       </c>
       <c r="B57" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6736,10 +6333,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550516</v>
+        <v>550456</v>
       </c>
       <c r="R57" t="n">
-        <v>6994130</v>
+        <v>6993982</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6772,6 +6369,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6799,54 +6401,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004562</v>
+        <v>126099591</v>
       </c>
       <c r="B58" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550520</v>
+        <v>550464</v>
       </c>
       <c r="R58" t="n">
-        <v>6994154</v>
+        <v>6994104</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6873,12 +6469,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6906,54 +6502,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004477</v>
+        <v>126099553</v>
       </c>
       <c r="B59" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550370</v>
+        <v>550465</v>
       </c>
       <c r="R59" t="n">
-        <v>6993853</v>
+        <v>6994163</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6980,12 +6570,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7013,54 +6608,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004405</v>
+        <v>102088995</v>
       </c>
       <c r="B60" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550404</v>
+        <v>550570</v>
       </c>
       <c r="R60" t="n">
-        <v>6994153</v>
+        <v>6994156</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7087,12 +6674,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7101,7 +6693,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7120,54 +6711,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004519</v>
+        <v>102089929</v>
       </c>
       <c r="B61" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550494</v>
+        <v>550373</v>
       </c>
       <c r="R61" t="n">
-        <v>6993901</v>
+        <v>6994082</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7194,17 +6777,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7213,7 +6791,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7232,43 +6809,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121004505</v>
+        <v>121004521</v>
       </c>
       <c r="B62" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7276,10 +6847,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550496</v>
+        <v>550494</v>
       </c>
       <c r="R62" t="n">
-        <v>6993835</v>
+        <v>6993901</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7312,6 +6883,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7339,53 +6915,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004449</v>
+        <v>102089008</v>
       </c>
       <c r="B63" t="n">
-        <v>88034</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550379</v>
+        <v>550570</v>
       </c>
       <c r="R63" t="n">
-        <v>6994086</v>
+        <v>6994156</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7412,12 +6981,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7426,7 +7000,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7445,53 +7018,46 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121004494</v>
+        <v>102089938</v>
       </c>
       <c r="B64" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4365</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550515</v>
+        <v>550373</v>
       </c>
       <c r="R64" t="n">
-        <v>6993816</v>
+        <v>6994082</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7518,12 +7084,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7532,7 +7098,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7551,53 +7116,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121004545</v>
+        <v>102089013</v>
       </c>
       <c r="B65" t="n">
-        <v>91993</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550493</v>
+        <v>550570</v>
       </c>
       <c r="R65" t="n">
-        <v>6994078</v>
+        <v>6994156</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7624,12 +7182,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7638,7 +7201,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7657,27 +7219,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126099630</v>
+        <v>102089935</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7686,19 +7248,17 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550494</v>
+        <v>550373</v>
       </c>
       <c r="R66" t="n">
-        <v>6994148</v>
+        <v>6994082</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7725,17 +7285,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7744,7 +7299,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7763,48 +7317,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126099623</v>
+        <v>121004525</v>
       </c>
       <c r="B67" t="n">
-        <v>78739</v>
+        <v>57141</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550481</v>
+        <v>550502</v>
       </c>
       <c r="R67" t="n">
-        <v>6994133</v>
+        <v>6993935</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7831,12 +7390,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7845,7 +7404,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7864,48 +7422,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126099520</v>
+        <v>134246389</v>
       </c>
       <c r="B68" t="n">
-        <v>80955</v>
+        <v>58131</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>103023</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550419</v>
+        <v>550466</v>
       </c>
       <c r="R68" t="n">
-        <v>6994207</v>
+        <v>6994147</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7932,12 +7487,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7946,29 +7501,28 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126099553</v>
+        <v>134246392</v>
       </c>
       <c r="B69" t="n">
-        <v>79987</v>
+        <v>98219</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7976,40 +7530,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>219815</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550465</v>
+        <v>550548</v>
       </c>
       <c r="R69" t="n">
-        <v>6994163</v>
+        <v>6994192</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8033,17 +7584,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8052,29 +7598,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126099534</v>
+        <v>102088784</v>
       </c>
       <c r="B70" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,20 +7645,18 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550463</v>
+        <v>550571</v>
       </c>
       <c r="R70" t="n">
-        <v>6994172</v>
+        <v>6994155</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8140,12 +7683,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8154,7 +7697,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8173,48 +7715,47 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126099588</v>
+        <v>102089119</v>
       </c>
       <c r="B71" t="n">
-        <v>78647</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550464</v>
+        <v>550567</v>
       </c>
       <c r="R71" t="n">
-        <v>6994104</v>
+        <v>6994155</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8241,12 +7782,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8255,7 +7796,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8274,48 +7814,47 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126099591</v>
+        <v>102089419</v>
       </c>
       <c r="B72" t="n">
-        <v>79598</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550464</v>
+        <v>550554</v>
       </c>
       <c r="R72" t="n">
-        <v>6994104</v>
+        <v>6994133</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8342,12 +7881,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8356,7 +7895,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8375,48 +7913,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134246393</v>
+        <v>102089819</v>
       </c>
       <c r="B73" t="n">
-        <v>99210</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550548</v>
+        <v>550446</v>
       </c>
       <c r="R73" t="n">
-        <v>6994192</v>
+        <v>6994089</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8440,12 +7980,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8460,60 +8000,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134246394</v>
+        <v>121004332</v>
       </c>
       <c r="B74" t="n">
-        <v>79366</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550512</v>
+        <v>550310</v>
       </c>
       <c r="R74" t="n">
-        <v>6994236</v>
+        <v>6994126</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8537,12 +8081,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8551,28 +8095,29 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134246388</v>
+        <v>121004405</v>
       </c>
       <c r="B75" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8598,19 +8143,23 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550414</v>
+        <v>550404</v>
       </c>
       <c r="R75" t="n">
-        <v>6994084</v>
+        <v>6994153</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8634,12 +8183,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8648,66 +8197,71 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134246390</v>
+        <v>121004422</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550466</v>
+        <v>550395</v>
       </c>
       <c r="R76" t="n">
-        <v>6994147</v>
+        <v>6994127</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8731,12 +8285,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,21 +8299,1430 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121004461</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>550389</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6994063</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121004477</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>550370</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6993853</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121004505</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>550496</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6993835</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121004519</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>550494</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6993901</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121004558</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>550516</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6994130</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121004562</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>550520</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6994154</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>121004565</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>550469</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6994270</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126099534</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>550463</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6994172</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134246388</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>550414</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6994084</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
+      <c r="AX85" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134246393</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>550548</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6994192</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4774,32 +4774,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004409</v>
+        <v>135457522</v>
       </c>
       <c r="B42" t="n">
-        <v>93209</v>
+        <v>93275</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550413</v>
+        <v>550478</v>
       </c>
       <c r="R42" t="n">
-        <v>6994137</v>
+        <v>6993873</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4875,46 +4875,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>102089839</v>
+        <v>121004409</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550410</v>
+        <v>550413</v>
       </c>
       <c r="R43" t="n">
-        <v>6994101</v>
+        <v>6994137</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4941,12 +4943,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4955,6 +4957,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4973,7 +4976,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121004337</v>
+        <v>102089839</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5002,19 +5005,17 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550319</v>
+        <v>550410</v>
       </c>
       <c r="R44" t="n">
-        <v>6994143</v>
+        <v>6994101</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5041,17 +5042,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5060,7 +5056,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5079,7 +5074,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004358</v>
+        <v>121004337</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5117,10 +5112,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550362</v>
+        <v>550319</v>
       </c>
       <c r="R45" t="n">
-        <v>6994156</v>
+        <v>6994143</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5153,6 +5148,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5180,7 +5180,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004395</v>
+        <v>121004358</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550381</v>
+        <v>550362</v>
       </c>
       <c r="R46" t="n">
-        <v>6994155</v>
+        <v>6994156</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004439</v>
+        <v>121004395</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550405</v>
+        <v>550381</v>
       </c>
       <c r="R47" t="n">
-        <v>6994090</v>
+        <v>6994155</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5355,11 +5355,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5387,7 +5382,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004450</v>
+        <v>121004439</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5425,10 +5420,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550379</v>
+        <v>550405</v>
       </c>
       <c r="R48" t="n">
-        <v>6994086</v>
+        <v>6994090</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5461,6 +5456,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,7 +5488,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004511</v>
+        <v>121004450</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550470</v>
+        <v>550379</v>
       </c>
       <c r="R49" t="n">
-        <v>6993852</v>
+        <v>6994086</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5562,11 +5562,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5594,7 +5589,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004515</v>
+        <v>121004511</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5632,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550464</v>
+        <v>550470</v>
       </c>
       <c r="R50" t="n">
-        <v>6993901</v>
+        <v>6993852</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5668,6 +5663,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5695,7 +5695,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126099630</v>
+        <v>121004515</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5729,14 +5729,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550494</v>
+        <v>550464</v>
       </c>
       <c r="R51" t="n">
-        <v>6994148</v>
+        <v>6993901</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5763,17 +5763,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5801,10 +5796,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134246394</v>
+        <v>126099630</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5830,19 +5825,22 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550512</v>
+        <v>550494</v>
       </c>
       <c r="R52" t="n">
-        <v>6994236</v>
+        <v>6994148</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5866,12 +5864,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5880,25 +5883,26 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246395</v>
+        <v>134246394</v>
       </c>
       <c r="B53" t="n">
         <v>79373</v>
@@ -5929,14 +5933,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550292</v>
+        <v>550512</v>
       </c>
       <c r="R53" t="n">
-        <v>6994150</v>
+        <v>6994236</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,49 +5999,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102089806</v>
+        <v>134246395</v>
       </c>
       <c r="B54" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550469</v>
+        <v>550292</v>
       </c>
       <c r="R54" t="n">
-        <v>6994094</v>
+        <v>6994150</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6061,12 +6064,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6081,19 +6084,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121004349</v>
+        <v>102089806</v>
       </c>
       <c r="B55" t="n">
         <v>79946</v>
@@ -6122,19 +6125,17 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550358</v>
+        <v>550469</v>
       </c>
       <c r="R55" t="n">
-        <v>6994160</v>
+        <v>6994094</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6161,12 +6162,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6175,7 +6176,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004374</v>
+        <v>121004349</v>
       </c>
       <c r="B56" t="n">
         <v>79946</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550369</v>
+        <v>550358</v>
       </c>
       <c r="R56" t="n">
-        <v>6994167</v>
+        <v>6994160</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004533</v>
+        <v>121004374</v>
       </c>
       <c r="B57" t="n">
         <v>79946</v>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550456</v>
+        <v>550369</v>
       </c>
       <c r="R57" t="n">
-        <v>6993982</v>
+        <v>6994167</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6369,11 +6369,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6401,7 +6396,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126099591</v>
+        <v>121004533</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6435,14 +6430,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550464</v>
+        <v>550456</v>
       </c>
       <c r="R58" t="n">
-        <v>6994104</v>
+        <v>6993982</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6469,12 +6464,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,32 +6502,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126099553</v>
+        <v>126099591</v>
       </c>
       <c r="B59" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550465</v>
+        <v>550464</v>
       </c>
       <c r="R59" t="n">
-        <v>6994163</v>
+        <v>6994104</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6576,11 +6576,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6608,46 +6603,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102088995</v>
+        <v>126099553</v>
       </c>
       <c r="B60" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550570</v>
+        <v>550465</v>
       </c>
       <c r="R60" t="n">
-        <v>6994156</v>
+        <v>6994163</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6674,17 +6671,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6693,6 +6690,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6711,7 +6709,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102089929</v>
+        <v>102088995</v>
       </c>
       <c r="B61" t="n">
         <v>80432</v>
@@ -6747,10 +6745,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R61" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6783,6 +6781,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6809,7 +6812,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121004521</v>
+        <v>102089929</v>
       </c>
       <c r="B62" t="n">
         <v>80432</v>
@@ -6838,19 +6841,17 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550494</v>
+        <v>550373</v>
       </c>
       <c r="R62" t="n">
-        <v>6993901</v>
+        <v>6994082</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6877,17 +6878,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6896,7 +6892,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6915,46 +6910,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102089008</v>
+        <v>121004521</v>
       </c>
       <c r="B63" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550570</v>
+        <v>550494</v>
       </c>
       <c r="R63" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6981,12 +6978,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7000,6 +6997,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7018,7 +7016,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102089938</v>
+        <v>102089008</v>
       </c>
       <c r="B64" t="n">
         <v>80461</v>
@@ -7054,10 +7052,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R64" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7090,6 +7088,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7116,10 +7119,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089013</v>
+        <v>102089938</v>
       </c>
       <c r="B65" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7127,21 +7130,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7152,10 +7155,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550570</v>
+        <v>550373</v>
       </c>
       <c r="R65" t="n">
-        <v>6994156</v>
+        <v>6994082</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7188,11 +7191,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7219,7 +7217,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102089935</v>
+        <v>102089013</v>
       </c>
       <c r="B66" t="n">
         <v>80467</v>
@@ -7255,10 +7253,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R66" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7291,6 +7289,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7317,10 +7320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121004525</v>
+        <v>102089935</v>
       </c>
       <c r="B67" t="n">
-        <v>57141</v>
+        <v>80467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7328,42 +7331,35 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550502</v>
+        <v>550373</v>
       </c>
       <c r="R67" t="n">
-        <v>6993935</v>
+        <v>6994082</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7390,12 +7386,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7422,10 +7418,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134246389</v>
+        <v>121004525</v>
       </c>
       <c r="B68" t="n">
-        <v>58131</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7433,34 +7429,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103023</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550466</v>
+        <v>550502</v>
       </c>
       <c r="R68" t="n">
-        <v>6994147</v>
+        <v>6993935</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7487,12 +7491,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7507,22 +7511,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134246392</v>
+        <v>134246389</v>
       </c>
       <c r="B69" t="n">
-        <v>98219</v>
+        <v>58131</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7530,21 +7534,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219815</v>
+        <v>103023</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7554,13 +7558,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550548</v>
+        <v>550466</v>
       </c>
       <c r="R69" t="n">
-        <v>6994192</v>
+        <v>6994147</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7616,50 +7620,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102088784</v>
+        <v>134246392</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550571</v>
+        <v>550548</v>
       </c>
       <c r="R70" t="n">
-        <v>6994155</v>
+        <v>6994192</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7683,12 +7685,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7703,19 +7705,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102089119</v>
+        <v>102088784</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -7748,11 +7750,11 @@
       <c r="L71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550567</v>
+        <v>550571</v>
       </c>
       <c r="R71" t="n">
         <v>6994155</v>
@@ -7814,7 +7816,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102089419</v>
+        <v>102089119</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -7851,10 +7853,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550554</v>
+        <v>550567</v>
       </c>
       <c r="R72" t="n">
-        <v>6994133</v>
+        <v>6994155</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7913,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102089819</v>
+        <v>102089419</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -7950,10 +7952,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550446</v>
+        <v>550554</v>
       </c>
       <c r="R73" t="n">
-        <v>6994089</v>
+        <v>6994133</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8012,7 +8014,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121004332</v>
+        <v>102089819</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8041,20 +8043,18 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550310</v>
+        <v>550446</v>
       </c>
       <c r="R74" t="n">
-        <v>6994126</v>
+        <v>6994089</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8081,12 +8081,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8095,7 +8095,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8114,7 +8113,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121004405</v>
+        <v>121004332</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8153,10 +8152,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550404</v>
+        <v>550310</v>
       </c>
       <c r="R75" t="n">
-        <v>6994153</v>
+        <v>6994126</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8216,7 +8215,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121004422</v>
+        <v>121004405</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8255,10 +8254,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550395</v>
+        <v>550404</v>
       </c>
       <c r="R76" t="n">
-        <v>6994127</v>
+        <v>6994153</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8318,7 +8317,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004461</v>
+        <v>121004422</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8357,10 +8356,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550389</v>
+        <v>550395</v>
       </c>
       <c r="R77" t="n">
-        <v>6994063</v>
+        <v>6994127</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8420,7 +8419,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121004477</v>
+        <v>121004461</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8459,10 +8458,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550370</v>
+        <v>550389</v>
       </c>
       <c r="R78" t="n">
-        <v>6993853</v>
+        <v>6994063</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8522,7 +8521,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004505</v>
+        <v>121004477</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8561,10 +8560,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550496</v>
+        <v>550370</v>
       </c>
       <c r="R79" t="n">
-        <v>6993835</v>
+        <v>6993853</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8624,7 +8623,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004519</v>
+        <v>121004505</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -8663,10 +8662,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550494</v>
+        <v>550496</v>
       </c>
       <c r="R80" t="n">
-        <v>6993901</v>
+        <v>6993835</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8699,11 +8698,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8731,7 +8725,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004558</v>
+        <v>121004519</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -8770,10 +8764,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550516</v>
+        <v>550494</v>
       </c>
       <c r="R81" t="n">
-        <v>6994130</v>
+        <v>6993901</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8806,6 +8800,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8833,7 +8832,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004562</v>
+        <v>121004558</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -8872,10 +8871,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550520</v>
+        <v>550516</v>
       </c>
       <c r="R82" t="n">
-        <v>6994154</v>
+        <v>6994130</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8935,7 +8934,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004565</v>
+        <v>121004562</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -8974,10 +8973,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550469</v>
+        <v>550520</v>
       </c>
       <c r="R83" t="n">
-        <v>6994270</v>
+        <v>6994154</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9037,7 +9036,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126099534</v>
+        <v>121004565</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9072,14 +9071,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550463</v>
+        <v>550469</v>
       </c>
       <c r="R84" t="n">
-        <v>6994172</v>
+        <v>6994270</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9106,12 +9105,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9139,10 +9138,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134246388</v>
+        <v>126099534</v>
       </c>
       <c r="B85" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9168,19 +9167,23 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550414</v>
+        <v>550463</v>
       </c>
       <c r="R85" t="n">
-        <v>6994084</v>
+        <v>6994172</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9204,12 +9207,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9218,50 +9221,51 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134246393</v>
+        <v>134246388</v>
       </c>
       <c r="B86" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9271,10 +9275,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550548</v>
+        <v>550414</v>
       </c>
       <c r="R86" t="n">
-        <v>6994192</v>
+        <v>6994084</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9333,7 +9337,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134246406</v>
+        <v>134246393</v>
       </c>
       <c r="B87" t="n">
         <v>99217</v>
@@ -9364,14 +9368,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550277</v>
+        <v>550548</v>
       </c>
       <c r="R87" t="n">
-        <v>6994166</v>
+        <v>6994192</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9430,51 +9434,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126099623</v>
+        <v>134246406</v>
       </c>
       <c r="B88" t="n">
-        <v>79085</v>
+        <v>99217</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550481</v>
+        <v>550277</v>
       </c>
       <c r="R88" t="n">
-        <v>6994133</v>
+        <v>6994166</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9498,12 +9499,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9512,29 +9513,28 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134246390</v>
+        <v>126099623</v>
       </c>
       <c r="B89" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9560,19 +9560,22 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550466</v>
+        <v>550481</v>
       </c>
       <c r="R89" t="n">
-        <v>6994147</v>
+        <v>6994133</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9596,12 +9599,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9610,67 +9613,67 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102089933</v>
+        <v>134246390</v>
       </c>
       <c r="B90" t="n">
-        <v>80392</v>
+        <v>79131</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550373</v>
+        <v>550466</v>
       </c>
       <c r="R90" t="n">
-        <v>6994082</v>
+        <v>6994147</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9694,12 +9697,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9714,15 +9717,113 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7717,47 +7717,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102088784</v>
+        <v>135466568</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>99230</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550571</v>
+        <v>550481</v>
       </c>
       <c r="R71" t="n">
-        <v>6994155</v>
+        <v>6993999</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7784,12 +7790,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,6 +7804,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7816,7 +7823,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102089119</v>
+        <v>102088784</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -7849,11 +7856,11 @@
       <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550567</v>
+        <v>550571</v>
       </c>
       <c r="R72" t="n">
         <v>6994155</v>
@@ -7915,7 +7922,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102089419</v>
+        <v>102089119</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -7952,10 +7959,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550554</v>
+        <v>550567</v>
       </c>
       <c r="R73" t="n">
-        <v>6994133</v>
+        <v>6994155</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8014,7 +8021,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102089819</v>
+        <v>102089419</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8051,10 +8058,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550446</v>
+        <v>550554</v>
       </c>
       <c r="R74" t="n">
-        <v>6994089</v>
+        <v>6994133</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8113,7 +8120,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121004332</v>
+        <v>102089819</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8142,20 +8149,18 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550310</v>
+        <v>550446</v>
       </c>
       <c r="R75" t="n">
-        <v>6994126</v>
+        <v>6994089</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8182,12 +8187,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8196,7 +8201,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8215,7 +8219,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121004405</v>
+        <v>121004332</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8254,10 +8258,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550404</v>
+        <v>550310</v>
       </c>
       <c r="R76" t="n">
-        <v>6994153</v>
+        <v>6994126</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8317,7 +8321,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004422</v>
+        <v>121004405</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8356,10 +8360,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550395</v>
+        <v>550404</v>
       </c>
       <c r="R77" t="n">
-        <v>6994127</v>
+        <v>6994153</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8419,7 +8423,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121004461</v>
+        <v>121004422</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8458,10 +8462,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550389</v>
+        <v>550395</v>
       </c>
       <c r="R78" t="n">
-        <v>6994063</v>
+        <v>6994127</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8521,7 +8525,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004477</v>
+        <v>121004461</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8560,10 +8564,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550370</v>
+        <v>550389</v>
       </c>
       <c r="R79" t="n">
-        <v>6993853</v>
+        <v>6994063</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8623,7 +8627,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004505</v>
+        <v>121004477</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -8662,10 +8666,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550496</v>
+        <v>550370</v>
       </c>
       <c r="R80" t="n">
-        <v>6993835</v>
+        <v>6993853</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8725,7 +8729,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004519</v>
+        <v>121004505</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -8764,10 +8768,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550494</v>
+        <v>550496</v>
       </c>
       <c r="R81" t="n">
-        <v>6993901</v>
+        <v>6993835</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8800,11 +8804,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8832,7 +8831,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004558</v>
+        <v>121004519</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -8871,10 +8870,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550516</v>
+        <v>550494</v>
       </c>
       <c r="R82" t="n">
-        <v>6994130</v>
+        <v>6993901</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8907,6 +8906,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8934,7 +8938,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004562</v>
+        <v>121004558</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -8973,10 +8977,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550520</v>
+        <v>550516</v>
       </c>
       <c r="R83" t="n">
-        <v>6994154</v>
+        <v>6994130</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9036,7 +9040,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004565</v>
+        <v>121004562</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9075,10 +9079,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550469</v>
+        <v>550520</v>
       </c>
       <c r="R84" t="n">
-        <v>6994270</v>
+        <v>6994154</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9138,7 +9142,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126099534</v>
+        <v>121004565</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9173,14 +9177,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550463</v>
+        <v>550469</v>
       </c>
       <c r="R85" t="n">
-        <v>6994172</v>
+        <v>6994270</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9207,12 +9211,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9240,10 +9244,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134246388</v>
+        <v>126099534</v>
       </c>
       <c r="B86" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9269,19 +9273,23 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550414</v>
+        <v>550463</v>
       </c>
       <c r="R86" t="n">
-        <v>6994084</v>
+        <v>6994172</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9305,12 +9313,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9319,50 +9327,51 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134246393</v>
+        <v>134246388</v>
       </c>
       <c r="B87" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9372,10 +9381,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550548</v>
+        <v>550414</v>
       </c>
       <c r="R87" t="n">
-        <v>6994192</v>
+        <v>6994084</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9434,10 +9443,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134246406</v>
+        <v>135466572</v>
       </c>
       <c r="B88" t="n">
-        <v>99217</v>
+        <v>98066</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9445,37 +9454,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550277</v>
+        <v>550481</v>
       </c>
       <c r="R88" t="n">
-        <v>6994166</v>
+        <v>6993999</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9499,12 +9512,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9513,69 +9526,67 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126099623</v>
+        <v>134246393</v>
       </c>
       <c r="B89" t="n">
-        <v>79085</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550481</v>
+        <v>550548</v>
       </c>
       <c r="R89" t="n">
-        <v>6994133</v>
+        <v>6994192</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9599,12 +9610,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9613,64 +9624,63 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246390</v>
+        <v>134246406</v>
       </c>
       <c r="B90" t="n">
-        <v>79131</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550466</v>
+        <v>550277</v>
       </c>
       <c r="R90" t="n">
-        <v>6994147</v>
+        <v>6994166</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9729,46 +9739,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>102089933</v>
+        <v>126099623</v>
       </c>
       <c r="B91" t="n">
-        <v>80392</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550373</v>
+        <v>550481</v>
       </c>
       <c r="R91" t="n">
-        <v>6994082</v>
+        <v>6994133</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9795,12 +9807,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9809,6 +9821,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9824,6 +9837,201 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1286,32 +1286,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004536</v>
+        <v>135457711</v>
       </c>
       <c r="B8" t="n">
-        <v>81312</v>
+        <v>92546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550477</v>
+        <v>550504</v>
       </c>
       <c r="R8" t="n">
-        <v>6994042</v>
+        <v>6993854</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004550</v>
+        <v>121004536</v>
       </c>
       <c r="B9" t="n">
         <v>81312</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550508</v>
+        <v>550477</v>
       </c>
       <c r="R9" t="n">
-        <v>6994113</v>
+        <v>6994042</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126099520</v>
+        <v>121004550</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550419</v>
+        <v>550508</v>
       </c>
       <c r="R10" t="n">
-        <v>6994207</v>
+        <v>6994113</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102089224</v>
+        <v>126099520</v>
       </c>
       <c r="B11" t="n">
-        <v>83173</v>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,35 +1600,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550562</v>
+        <v>550419</v>
       </c>
       <c r="R11" t="n">
-        <v>6994152</v>
+        <v>6994207</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1655,12 +1657,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,6 +1671,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1687,48 +1690,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004416</v>
+        <v>102089224</v>
       </c>
       <c r="B12" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550398</v>
+        <v>550562</v>
       </c>
       <c r="R12" t="n">
-        <v>6994131</v>
+        <v>6994152</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1755,12 +1756,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,7 +1770,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004472</v>
+        <v>121004416</v>
       </c>
       <c r="B13" t="n">
         <v>92083</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550400</v>
+        <v>550398</v>
       </c>
       <c r="R13" t="n">
-        <v>6993983</v>
+        <v>6994131</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1889,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004362</v>
+        <v>121004472</v>
       </c>
       <c r="B14" t="n">
-        <v>90932</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550364</v>
+        <v>550400</v>
       </c>
       <c r="R14" t="n">
-        <v>6994169</v>
+        <v>6993983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004490</v>
+        <v>121004362</v>
       </c>
       <c r="B15" t="n">
         <v>90932</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550508</v>
+        <v>550364</v>
       </c>
       <c r="R15" t="n">
-        <v>6993803</v>
+        <v>6994169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004539</v>
+        <v>121004490</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550486</v>
+        <v>550508</v>
       </c>
       <c r="R16" t="n">
-        <v>6994062</v>
+        <v>6993803</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62025591</v>
+        <v>121004539</v>
       </c>
       <c r="B17" t="n">
-        <v>91962</v>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2203,37 +2203,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550409</v>
+        <v>550486</v>
       </c>
       <c r="R17" t="n">
-        <v>6994048</v>
+        <v>6994062</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2257,12 +2260,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2271,38 +2274,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102089002</v>
+        <v>62025591</v>
       </c>
       <c r="B18" t="n">
-        <v>80433</v>
+        <v>91962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2310,38 +2304,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550570</v>
+        <v>550409</v>
       </c>
       <c r="R18" t="n">
-        <v>6994156</v>
+        <v>6994048</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2365,17 +2358,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2386,64 +2374,75 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103996059</v>
+        <v>102089002</v>
       </c>
       <c r="B19" t="n">
-        <v>96338</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550310</v>
+        <v>550570</v>
       </c>
       <c r="R19" t="n">
-        <v>6994183</v>
+        <v>6994156</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2467,22 +2466,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2493,11 +2487,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2507,62 +2496,55 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004351</v>
+        <v>103996059</v>
       </c>
       <c r="B20" t="n">
-        <v>91831</v>
+        <v>96338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3242</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550358</v>
+        <v>550310</v>
       </c>
       <c r="R20" t="n">
-        <v>6994160</v>
+        <v>6994183</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2586,12 +2568,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2600,9 +2592,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2612,14 +2608,18 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004470</v>
+        <v>121004351</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550383</v>
+        <v>550358</v>
       </c>
       <c r="R21" t="n">
-        <v>6993994</v>
+        <v>6994160</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2693,11 +2693,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2725,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>62025592</v>
+        <v>121004470</v>
       </c>
       <c r="B22" t="n">
-        <v>93197</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2736,37 +2731,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550409</v>
+        <v>550383</v>
       </c>
       <c r="R22" t="n">
-        <v>6994048</v>
+        <v>6993994</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2790,12 +2788,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2804,38 +2807,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102089700</v>
+        <v>135457707</v>
       </c>
       <c r="B23" t="n">
-        <v>93197</v>
+        <v>93263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,35 +2837,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550476</v>
+        <v>550510</v>
       </c>
       <c r="R23" t="n">
-        <v>6994117</v>
+        <v>6993821</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2898,12 +2894,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2912,6 +2908,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2930,7 +2927,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103996072</v>
+        <v>62025592</v>
       </c>
       <c r="B24" t="n">
         <v>93197</v>
@@ -2961,14 +2958,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550481</v>
+        <v>550409</v>
       </c>
       <c r="R24" t="n">
-        <v>6994068</v>
+        <v>6994048</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2995,22 +2992,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3022,31 +3009,32 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103996080</v>
+        <v>102089700</v>
       </c>
       <c r="B25" t="n">
         <v>93197</v>
@@ -3075,19 +3063,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550485</v>
+        <v>550476</v>
       </c>
       <c r="R25" t="n">
-        <v>6994105</v>
+        <v>6994117</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3111,22 +3100,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3137,11 +3116,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3151,18 +3125,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004341</v>
+        <v>103996072</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3191,22 +3161,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550344</v>
+        <v>550481</v>
       </c>
       <c r="R26" t="n">
-        <v>6994160</v>
+        <v>6994068</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3230,12 +3197,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3244,9 +3221,13 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3256,14 +3237,18 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004394</v>
+        <v>103996080</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3292,22 +3277,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550381</v>
+        <v>550485</v>
       </c>
       <c r="R27" t="n">
-        <v>6994155</v>
+        <v>6994105</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3331,12 +3313,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3345,9 +3337,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3357,14 +3353,18 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004399</v>
+        <v>121004341</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550384</v>
+        <v>550344</v>
       </c>
       <c r="R28" t="n">
-        <v>6994151</v>
+        <v>6994160</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004430</v>
+        <v>121004394</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550422</v>
+        <v>550381</v>
       </c>
       <c r="R29" t="n">
-        <v>6994093</v>
+        <v>6994155</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004475</v>
+        <v>121004399</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550385</v>
+        <v>550384</v>
       </c>
       <c r="R30" t="n">
-        <v>6993920</v>
+        <v>6994151</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004484</v>
+        <v>121004430</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550427</v>
+        <v>550422</v>
       </c>
       <c r="R31" t="n">
-        <v>6993867</v>
+        <v>6994093</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004500</v>
+        <v>121004475</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550496</v>
+        <v>550385</v>
       </c>
       <c r="R32" t="n">
-        <v>6993817</v>
+        <v>6993920</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004509</v>
+        <v>121004484</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550476</v>
+        <v>550427</v>
       </c>
       <c r="R33" t="n">
-        <v>6993841</v>
+        <v>6993867</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3970,7 +3970,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004524</v>
+        <v>121004500</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550502</v>
+        <v>550496</v>
       </c>
       <c r="R34" t="n">
-        <v>6993935</v>
+        <v>6993817</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004537</v>
+        <v>121004509</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550477</v>
+        <v>550476</v>
       </c>
       <c r="R35" t="n">
-        <v>6994042</v>
+        <v>6993841</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004540</v>
+        <v>121004524</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550505</v>
+        <v>550502</v>
       </c>
       <c r="R36" t="n">
-        <v>6994074</v>
+        <v>6993935</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004541</v>
+        <v>121004537</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550528</v>
+        <v>550477</v>
       </c>
       <c r="R37" t="n">
-        <v>6994067</v>
+        <v>6994042</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004547</v>
+        <v>121004540</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550493</v>
+        <v>550505</v>
       </c>
       <c r="R38" t="n">
-        <v>6994078</v>
+        <v>6994074</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134246391</v>
+        <v>121004541</v>
       </c>
       <c r="B39" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,19 +4504,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550317</v>
+        <v>550528</v>
       </c>
       <c r="R39" t="n">
-        <v>6994117</v>
+        <v>6994067</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4540,12 +4543,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,50 +4557,51 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004494</v>
+        <v>121004547</v>
       </c>
       <c r="B40" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4610,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550515</v>
+        <v>550493</v>
       </c>
       <c r="R40" t="n">
-        <v>6993816</v>
+        <v>6994078</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4673,51 +4677,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004545</v>
+        <v>134246391</v>
       </c>
       <c r="B41" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550493</v>
+        <v>550317</v>
       </c>
       <c r="R41" t="n">
-        <v>6994078</v>
+        <v>6994117</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4741,12 +4742,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4755,29 +4756,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135457522</v>
+        <v>121004494</v>
       </c>
       <c r="B42" t="n">
-        <v>93275</v>
+        <v>93201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550478</v>
+        <v>550515</v>
       </c>
       <c r="R42" t="n">
-        <v>6993873</v>
+        <v>6993816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4875,32 +4875,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004409</v>
+        <v>121004545</v>
       </c>
       <c r="B43" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550413</v>
+        <v>550493</v>
       </c>
       <c r="R43" t="n">
-        <v>6994137</v>
+        <v>6994078</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4976,10 +4976,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102089839</v>
+        <v>135457522</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>93275</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4987,38 +4987,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550410</v>
+        <v>550478</v>
       </c>
       <c r="R44" t="n">
-        <v>6994101</v>
+        <v>6993873</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5042,12 +5044,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5056,6 +5058,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5074,32 +5077,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004337</v>
+        <v>121004409</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5112,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550319</v>
+        <v>550413</v>
       </c>
       <c r="R45" t="n">
-        <v>6994143</v>
+        <v>6994137</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5148,11 +5151,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5180,32 +5178,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004358</v>
+        <v>135457649</v>
       </c>
       <c r="B46" t="n">
-        <v>79327</v>
+        <v>89218</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550362</v>
+        <v>550447</v>
       </c>
       <c r="R46" t="n">
-        <v>6994156</v>
+        <v>6993828</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5248,12 +5246,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5281,7 +5279,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004395</v>
+        <v>102089839</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5310,19 +5308,17 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550381</v>
+        <v>550410</v>
       </c>
       <c r="R47" t="n">
-        <v>6994155</v>
+        <v>6994101</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5349,12 +5345,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5363,7 +5359,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5382,7 +5377,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004439</v>
+        <v>121004337</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5420,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550405</v>
+        <v>550319</v>
       </c>
       <c r="R48" t="n">
-        <v>6994090</v>
+        <v>6994143</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5460,7 +5455,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,7 +5483,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004450</v>
+        <v>121004358</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5526,10 +5521,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550379</v>
+        <v>550362</v>
       </c>
       <c r="R49" t="n">
-        <v>6994086</v>
+        <v>6994156</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5589,7 +5584,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004511</v>
+        <v>121004395</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5627,10 +5622,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550470</v>
+        <v>550381</v>
       </c>
       <c r="R50" t="n">
-        <v>6993852</v>
+        <v>6994155</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5663,11 +5658,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5695,7 +5685,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004515</v>
+        <v>121004439</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5733,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550464</v>
+        <v>550405</v>
       </c>
       <c r="R51" t="n">
-        <v>6993901</v>
+        <v>6994090</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5769,6 +5759,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5796,7 +5791,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126099630</v>
+        <v>121004450</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -5830,14 +5825,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550494</v>
+        <v>550379</v>
       </c>
       <c r="R52" t="n">
-        <v>6994148</v>
+        <v>6994086</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5864,17 +5859,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5902,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246394</v>
+        <v>121004511</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5931,19 +5921,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550512</v>
+        <v>550470</v>
       </c>
       <c r="R53" t="n">
-        <v>6994236</v>
+        <v>6993852</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5967,12 +5960,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5981,28 +5979,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134246395</v>
+        <v>121004515</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,19 +6027,22 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550292</v>
+        <v>550464</v>
       </c>
       <c r="R54" t="n">
-        <v>6994150</v>
+        <v>6993901</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6064,12 +6066,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6078,64 +6080,67 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102089806</v>
+        <v>126099630</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R55" t="n">
-        <v>6994094</v>
+        <v>6994148</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6162,12 +6167,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6176,6 +6186,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6194,51 +6205,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004349</v>
+        <v>134246394</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550358</v>
+        <v>550512</v>
       </c>
       <c r="R56" t="n">
-        <v>6994160</v>
+        <v>6994236</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6262,12 +6270,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6276,70 +6284,66 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004374</v>
+        <v>134246395</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550369</v>
+        <v>550292</v>
       </c>
       <c r="R57" t="n">
-        <v>6994167</v>
+        <v>6994150</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6363,12 +6367,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6377,26 +6381,25 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004533</v>
+        <v>102089806</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6425,19 +6428,17 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550456</v>
+        <v>550469</v>
       </c>
       <c r="R58" t="n">
-        <v>6993982</v>
+        <v>6994094</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6464,17 +6465,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6483,7 +6479,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6502,7 +6497,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126099591</v>
+        <v>121004349</v>
       </c>
       <c r="B59" t="n">
         <v>79946</v>
@@ -6536,14 +6531,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550464</v>
+        <v>550358</v>
       </c>
       <c r="R59" t="n">
-        <v>6994104</v>
+        <v>6994160</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6570,12 +6565,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6603,32 +6598,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126099553</v>
+        <v>121004374</v>
       </c>
       <c r="B60" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6637,14 +6632,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550465</v>
+        <v>550369</v>
       </c>
       <c r="R60" t="n">
-        <v>6994163</v>
+        <v>6994167</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6671,17 +6666,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6709,10 +6699,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102088995</v>
+        <v>121004533</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6720,35 +6710,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550570</v>
+        <v>550456</v>
       </c>
       <c r="R61" t="n">
-        <v>6994156</v>
+        <v>6993982</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6775,17 +6767,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6794,6 +6786,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6812,10 +6805,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102089929</v>
+        <v>126099591</v>
       </c>
       <c r="B62" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6823,35 +6816,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550373</v>
+        <v>550464</v>
       </c>
       <c r="R62" t="n">
-        <v>6994082</v>
+        <v>6994104</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6878,12 +6873,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6892,6 +6887,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6910,32 +6906,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004521</v>
+        <v>126099553</v>
       </c>
       <c r="B63" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6944,14 +6940,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550494</v>
+        <v>550465</v>
       </c>
       <c r="R63" t="n">
-        <v>6993901</v>
+        <v>6994163</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6978,17 +6974,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7016,32 +7012,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102089008</v>
+        <v>102088995</v>
       </c>
       <c r="B64" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7119,32 +7115,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089938</v>
+        <v>102089929</v>
       </c>
       <c r="B65" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7217,46 +7213,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102089013</v>
+        <v>121004521</v>
       </c>
       <c r="B66" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550570</v>
+        <v>550494</v>
       </c>
       <c r="R66" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7283,12 +7281,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7302,6 +7300,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7320,10 +7319,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089935</v>
+        <v>102089008</v>
       </c>
       <c r="B67" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7331,21 +7330,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7356,10 +7355,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R67" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7392,6 +7391,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7418,10 +7422,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121004525</v>
+        <v>102089938</v>
       </c>
       <c r="B68" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7429,42 +7433,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550502</v>
+        <v>550373</v>
       </c>
       <c r="R68" t="n">
-        <v>6993935</v>
+        <v>6994082</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7491,12 +7488,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7523,10 +7520,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134246389</v>
+        <v>102089013</v>
       </c>
       <c r="B69" t="n">
-        <v>58131</v>
+        <v>80467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7534,34 +7531,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103023</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550466</v>
+        <v>550570</v>
       </c>
       <c r="R69" t="n">
-        <v>6994147</v>
+        <v>6994156</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7588,12 +7586,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7608,22 +7611,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134246392</v>
+        <v>102089935</v>
       </c>
       <c r="B70" t="n">
-        <v>98219</v>
+        <v>80467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7631,37 +7634,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219815</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550548</v>
+        <v>550373</v>
       </c>
       <c r="R70" t="n">
-        <v>6994192</v>
+        <v>6994082</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7685,12 +7689,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7705,22 +7709,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135466568</v>
+        <v>121004525</v>
       </c>
       <c r="B71" t="n">
-        <v>99230</v>
+        <v>57141</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,42 +7732,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550481</v>
+        <v>550502</v>
       </c>
       <c r="R71" t="n">
-        <v>6993999</v>
+        <v>6993935</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7790,12 +7794,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7804,7 +7808,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7823,47 +7826,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102088784</v>
+        <v>134246389</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>58131</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550571</v>
+        <v>550466</v>
       </c>
       <c r="R72" t="n">
-        <v>6994155</v>
+        <v>6994147</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7890,12 +7891,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7910,62 +7911,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102089119</v>
+        <v>134246392</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550567</v>
+        <v>550548</v>
       </c>
       <c r="R73" t="n">
-        <v>6994155</v>
+        <v>6994192</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7989,12 +7988,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8009,59 +8008,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102089419</v>
+        <v>135466568</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>99230</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550554</v>
+        <v>550481</v>
       </c>
       <c r="R74" t="n">
-        <v>6994133</v>
+        <v>6993999</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8088,12 +8093,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8102,6 +8107,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8120,7 +8126,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102089819</v>
+        <v>102088784</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8153,14 +8159,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550446</v>
+        <v>550571</v>
       </c>
       <c r="R75" t="n">
-        <v>6994089</v>
+        <v>6994155</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8219,7 +8225,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121004332</v>
+        <v>102089119</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8248,20 +8254,18 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550310</v>
+        <v>550567</v>
       </c>
       <c r="R76" t="n">
-        <v>6994126</v>
+        <v>6994155</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8288,12 +8292,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8302,7 +8306,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8321,7 +8324,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004405</v>
+        <v>102089419</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8350,20 +8353,18 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550404</v>
+        <v>550554</v>
       </c>
       <c r="R77" t="n">
-        <v>6994153</v>
+        <v>6994133</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8390,12 +8391,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8404,7 +8405,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8423,7 +8423,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121004422</v>
+        <v>102089819</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8452,20 +8452,18 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550395</v>
+        <v>550446</v>
       </c>
       <c r="R78" t="n">
-        <v>6994127</v>
+        <v>6994089</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8492,12 +8490,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8506,7 +8504,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8525,7 +8522,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004461</v>
+        <v>121004332</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8564,10 +8561,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550389</v>
+        <v>550310</v>
       </c>
       <c r="R79" t="n">
-        <v>6994063</v>
+        <v>6994126</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8627,7 +8624,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004477</v>
+        <v>121004405</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -8666,10 +8663,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550370</v>
+        <v>550404</v>
       </c>
       <c r="R80" t="n">
-        <v>6993853</v>
+        <v>6994153</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8729,7 +8726,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004505</v>
+        <v>121004422</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -8768,10 +8765,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550496</v>
+        <v>550395</v>
       </c>
       <c r="R81" t="n">
-        <v>6993835</v>
+        <v>6994127</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8831,7 +8828,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004519</v>
+        <v>121004461</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -8870,10 +8867,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550494</v>
+        <v>550389</v>
       </c>
       <c r="R82" t="n">
-        <v>6993901</v>
+        <v>6994063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8906,11 +8903,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8938,7 +8930,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004558</v>
+        <v>121004477</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -8977,10 +8969,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550516</v>
+        <v>550370</v>
       </c>
       <c r="R83" t="n">
-        <v>6994130</v>
+        <v>6993853</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9040,7 +9032,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004562</v>
+        <v>121004505</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9079,10 +9071,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550520</v>
+        <v>550496</v>
       </c>
       <c r="R84" t="n">
-        <v>6994154</v>
+        <v>6993835</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9142,7 +9134,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004565</v>
+        <v>121004519</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9181,10 +9173,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R85" t="n">
-        <v>6994270</v>
+        <v>6993901</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9217,6 +9209,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9244,7 +9241,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126099534</v>
+        <v>121004558</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9279,14 +9276,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550463</v>
+        <v>550516</v>
       </c>
       <c r="R86" t="n">
-        <v>6994172</v>
+        <v>6994130</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9313,12 +9310,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9346,10 +9343,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134246388</v>
+        <v>121004562</v>
       </c>
       <c r="B87" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9375,19 +9372,23 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550414</v>
+        <v>550520</v>
       </c>
       <c r="R87" t="n">
-        <v>6994084</v>
+        <v>6994154</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9411,12 +9412,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9425,50 +9426,51 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135466572</v>
+        <v>121004565</v>
       </c>
       <c r="B88" t="n">
-        <v>98066</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9482,10 +9484,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550481</v>
+        <v>550469</v>
       </c>
       <c r="R88" t="n">
-        <v>6993999</v>
+        <v>6994270</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9512,12 +9514,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9545,48 +9547,52 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134246393</v>
+        <v>126099534</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550548</v>
+        <v>550463</v>
       </c>
       <c r="R89" t="n">
-        <v>6994192</v>
+        <v>6994172</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9610,12 +9616,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9624,63 +9630,64 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246406</v>
+        <v>134246388</v>
       </c>
       <c r="B90" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550277</v>
+        <v>550414</v>
       </c>
       <c r="R90" t="n">
-        <v>6994166</v>
+        <v>6994084</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9739,48 +9746,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126099623</v>
+        <v>135457589</v>
       </c>
       <c r="B91" t="n">
-        <v>79085</v>
+        <v>99195</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550481</v>
+        <v>550445</v>
       </c>
       <c r="R91" t="n">
-        <v>6994133</v>
+        <v>6993808</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9807,12 +9819,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönpyrola.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9840,48 +9857,56 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134246390</v>
+        <v>135457681</v>
       </c>
       <c r="B92" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550466</v>
+        <v>550350</v>
       </c>
       <c r="R92" t="n">
-        <v>6994147</v>
+        <v>6993905</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9905,12 +9930,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9919,64 +9944,72 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>102089933</v>
+        <v>135457684</v>
       </c>
       <c r="B93" t="n">
-        <v>80392</v>
+        <v>99195</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550373</v>
+        <v>550343</v>
       </c>
       <c r="R93" t="n">
-        <v>6994082</v>
+        <v>6993884</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10003,12 +10036,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10017,6 +10050,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10032,6 +10066,921 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135457690</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>550353</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6993851</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135457698</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>550455</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6994009</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135457602</v>
+      </c>
+      <c r="B96" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>550445</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6993808</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Tillsammans med knärot.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135466572</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6993999</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134246393</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>550548</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6994192</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B102" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089262</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004514</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099588</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004449</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,35 +1313,40 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025590</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135457711</v>
+        <v>121004536</v>
       </c>
       <c r="B8" t="n">
-        <v>92546</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550504</v>
+        <v>550477</v>
       </c>
       <c r="R8" t="n">
-        <v>6993854</v>
+        <v>6994042</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1419,15 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004536</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004536</v>
+        <v>121004550</v>
       </c>
       <c r="B9" t="n">
         <v>81312</v>
@@ -1425,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550477</v>
+        <v>550508</v>
       </c>
       <c r="R9" t="n">
-        <v>6994042</v>
+        <v>6994113</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1485,10 +1525,15 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004550</v>
+        <v>126099520</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1522,14 +1567,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550508</v>
+        <v>550419</v>
       </c>
       <c r="R10" t="n">
-        <v>6994113</v>
+        <v>6994207</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1556,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,13 +1631,18 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099520</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126099520</v>
+        <v>102089224</v>
       </c>
       <c r="B11" t="n">
-        <v>81312</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,37 +1650,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550419</v>
+        <v>550562</v>
       </c>
       <c r="R11" t="n">
-        <v>6994207</v>
+        <v>6994152</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1657,12 +1705,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1671,7 +1719,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1687,49 +1734,56 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089224</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102089224</v>
+        <v>121004416</v>
       </c>
       <c r="B12" t="n">
-        <v>83173</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550562</v>
+        <v>550398</v>
       </c>
       <c r="R12" t="n">
-        <v>6994152</v>
+        <v>6994131</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1756,12 +1810,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,6 +1824,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1785,10 +1840,15 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004416</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004416</v>
+        <v>121004472</v>
       </c>
       <c r="B13" t="n">
         <v>92083</v>
@@ -1826,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550398</v>
+        <v>550400</v>
       </c>
       <c r="R13" t="n">
-        <v>6994131</v>
+        <v>6993983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1886,35 +1946,40 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004472</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004472</v>
+        <v>121004362</v>
       </c>
       <c r="B14" t="n">
-        <v>92083</v>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550400</v>
+        <v>550364</v>
       </c>
       <c r="R14" t="n">
-        <v>6993983</v>
+        <v>6994169</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1987,10 +2052,15 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004362</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004362</v>
+        <v>121004490</v>
       </c>
       <c r="B15" t="n">
         <v>90932</v>
@@ -2028,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550364</v>
+        <v>550508</v>
       </c>
       <c r="R15" t="n">
-        <v>6994169</v>
+        <v>6993803</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2088,10 +2158,15 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004490</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004490</v>
+        <v>121004539</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2129,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550508</v>
+        <v>550486</v>
       </c>
       <c r="R16" t="n">
-        <v>6993803</v>
+        <v>6994062</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2189,13 +2264,18 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004539</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004539</v>
+        <v>62025591</v>
       </c>
       <c r="B17" t="n">
-        <v>90932</v>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2203,40 +2283,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550486</v>
+        <v>550409</v>
       </c>
       <c r="R17" t="n">
-        <v>6994062</v>
+        <v>6994048</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2260,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,29 +2351,43 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025591</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62025591</v>
+        <v>102089002</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,37 +2395,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550409</v>
+        <v>550570</v>
       </c>
       <c r="R18" t="n">
-        <v>6994048</v>
+        <v>6994156</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2358,12 +2450,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,75 +2471,69 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089002</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102089002</v>
+        <v>103996059</v>
       </c>
       <c r="B19" t="n">
-        <v>80433</v>
+        <v>96338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550570</v>
+        <v>550310</v>
       </c>
       <c r="R19" t="n">
-        <v>6994156</v>
+        <v>6994183</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2466,17 +2557,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2487,6 +2583,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2496,55 +2597,67 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996059</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103996059</v>
+        <v>121004351</v>
       </c>
       <c r="B20" t="n">
-        <v>96338</v>
+        <v>91831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550310</v>
+        <v>550358</v>
       </c>
       <c r="R20" t="n">
-        <v>6994183</v>
+        <v>6994160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2568,22 +2681,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2592,13 +2695,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2608,18 +2707,19 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004351</v>
+        <v>121004470</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2657,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550358</v>
+        <v>550383</v>
       </c>
       <c r="R21" t="n">
-        <v>6994160</v>
+        <v>6993994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2695,6 +2795,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2717,13 +2822,18 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004470</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004470</v>
+        <v>62025592</v>
       </c>
       <c r="B22" t="n">
-        <v>91831</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,40 +2841,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550383</v>
+        <v>550409</v>
       </c>
       <c r="R22" t="n">
-        <v>6993994</v>
+        <v>6994048</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2788,17 +2895,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2807,29 +2909,43 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025592</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135457707</v>
+        <v>102089700</v>
       </c>
       <c r="B23" t="n">
-        <v>93263</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,37 +2953,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550510</v>
+        <v>550476</v>
       </c>
       <c r="R23" t="n">
-        <v>6993821</v>
+        <v>6994117</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2894,12 +3008,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2908,7 +3022,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2924,10 +3037,15 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089700</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62025592</v>
+        <v>103996072</v>
       </c>
       <c r="B24" t="n">
         <v>93197</v>
@@ -2958,14 +3076,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550409</v>
+        <v>550481</v>
       </c>
       <c r="R24" t="n">
-        <v>6994048</v>
+        <v>6994068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2992,12 +3110,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3009,32 +3137,36 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996072</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102089700</v>
+        <v>103996080</v>
       </c>
       <c r="B25" t="n">
         <v>93197</v>
@@ -3063,20 +3195,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550476</v>
+        <v>550485</v>
       </c>
       <c r="R25" t="n">
-        <v>6994117</v>
+        <v>6994105</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3100,12 +3231,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3116,6 +3257,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3125,14 +3271,23 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996080</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103996072</v>
+        <v>121004341</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3161,19 +3316,22 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550481</v>
+        <v>550344</v>
       </c>
       <c r="R26" t="n">
-        <v>6994068</v>
+        <v>6994160</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3197,22 +3355,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3221,13 +3369,9 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3237,18 +3381,19 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103996080</v>
+        <v>121004394</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3277,19 +3422,22 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550485</v>
+        <v>550381</v>
       </c>
       <c r="R27" t="n">
-        <v>6994105</v>
+        <v>6994155</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3313,22 +3461,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,13 +3475,9 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3353,18 +3487,19 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004341</v>
+        <v>121004399</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3402,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550344</v>
+        <v>550384</v>
       </c>
       <c r="R28" t="n">
-        <v>6994160</v>
+        <v>6994151</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3462,10 +3597,15 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004399</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004394</v>
+        <v>121004430</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3503,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550381</v>
+        <v>550422</v>
       </c>
       <c r="R29" t="n">
-        <v>6994155</v>
+        <v>6994093</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3563,10 +3703,15 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004430</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004399</v>
+        <v>121004475</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3604,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550384</v>
+        <v>550385</v>
       </c>
       <c r="R30" t="n">
-        <v>6994151</v>
+        <v>6993920</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3664,10 +3809,15 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004475</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004430</v>
+        <v>121004484</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3705,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550422</v>
+        <v>550427</v>
       </c>
       <c r="R31" t="n">
-        <v>6994093</v>
+        <v>6993867</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3765,10 +3915,15 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004484</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004475</v>
+        <v>121004500</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3806,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550385</v>
+        <v>550496</v>
       </c>
       <c r="R32" t="n">
-        <v>6993920</v>
+        <v>6993817</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3866,10 +4021,15 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004500</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004484</v>
+        <v>121004509</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -3907,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550427</v>
+        <v>550476</v>
       </c>
       <c r="R33" t="n">
-        <v>6993867</v>
+        <v>6993841</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3967,10 +4127,15 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004509</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004500</v>
+        <v>121004524</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4008,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550496</v>
+        <v>550502</v>
       </c>
       <c r="R34" t="n">
-        <v>6993817</v>
+        <v>6993935</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4068,10 +4233,15 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004524</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004509</v>
+        <v>121004537</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4109,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550476</v>
+        <v>550477</v>
       </c>
       <c r="R35" t="n">
-        <v>6993841</v>
+        <v>6994042</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4169,10 +4339,15 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004537</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004524</v>
+        <v>121004540</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4210,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550502</v>
+        <v>550505</v>
       </c>
       <c r="R36" t="n">
-        <v>6993935</v>
+        <v>6994074</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4270,10 +4445,15 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004540</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004537</v>
+        <v>121004541</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4311,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550477</v>
+        <v>550528</v>
       </c>
       <c r="R37" t="n">
-        <v>6994042</v>
+        <v>6994067</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4371,10 +4551,15 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004541</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004540</v>
+        <v>121004547</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4412,10 +4597,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550505</v>
+        <v>550493</v>
       </c>
       <c r="R38" t="n">
-        <v>6994074</v>
+        <v>6994078</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4472,13 +4657,18 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004547</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004541</v>
+        <v>134246391</v>
       </c>
       <c r="B39" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,22 +4694,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550528</v>
+        <v>550317</v>
       </c>
       <c r="R39" t="n">
-        <v>6994067</v>
+        <v>6994117</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4543,12 +4730,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4557,51 +4744,55 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246391</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004547</v>
+        <v>121004494</v>
       </c>
       <c r="B40" t="n">
-        <v>93197</v>
+        <v>93201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4614,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550493</v>
+        <v>550515</v>
       </c>
       <c r="R40" t="n">
-        <v>6994078</v>
+        <v>6993816</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4674,51 +4865,59 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004494</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134246391</v>
+        <v>121004545</v>
       </c>
       <c r="B41" t="n">
-        <v>93271</v>
+        <v>93201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550317</v>
+        <v>550493</v>
       </c>
       <c r="R41" t="n">
-        <v>6994117</v>
+        <v>6994078</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4742,12 +4941,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4756,28 +4955,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004545</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004494</v>
+        <v>135457522</v>
       </c>
       <c r="B42" t="n">
-        <v>93201</v>
+        <v>93275</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4812,13 +5017,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550515</v>
+        <v>550478</v>
       </c>
       <c r="R42" t="n">
-        <v>6993816</v>
+        <v>6993873</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4842,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4872,35 +5077,40 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457522</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004545</v>
+        <v>121004409</v>
       </c>
       <c r="B43" t="n">
-        <v>93201</v>
+        <v>93209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4913,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550493</v>
+        <v>550413</v>
       </c>
       <c r="R43" t="n">
-        <v>6994078</v>
+        <v>6994137</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4973,13 +5183,18 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004409</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135457522</v>
+        <v>102089839</v>
       </c>
       <c r="B44" t="n">
-        <v>93275</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4987,40 +5202,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550478</v>
+        <v>550410</v>
       </c>
       <c r="R44" t="n">
-        <v>6993873</v>
+        <v>6994101</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5044,12 +5257,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5058,7 +5271,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5074,35 +5286,40 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089839</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004409</v>
+        <v>121004337</v>
       </c>
       <c r="B45" t="n">
-        <v>93209</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5115,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550413</v>
+        <v>550319</v>
       </c>
       <c r="R45" t="n">
-        <v>6994137</v>
+        <v>6994143</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5153,6 +5370,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5175,35 +5397,40 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004337</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135457649</v>
+        <v>121004358</v>
       </c>
       <c r="B46" t="n">
-        <v>89218</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5216,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550447</v>
+        <v>550362</v>
       </c>
       <c r="R46" t="n">
-        <v>6993828</v>
+        <v>6994156</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5246,12 +5473,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5276,10 +5503,15 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004358</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102089839</v>
+        <v>121004395</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5308,17 +5540,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550410</v>
+        <v>550381</v>
       </c>
       <c r="R47" t="n">
-        <v>6994101</v>
+        <v>6994155</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5345,12 +5579,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5359,6 +5593,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5374,10 +5609,15 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004395</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004337</v>
+        <v>121004439</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5415,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550319</v>
+        <v>550405</v>
       </c>
       <c r="R48" t="n">
-        <v>6994143</v>
+        <v>6994090</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5455,7 +5695,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5480,10 +5720,15 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004439</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004358</v>
+        <v>121004450</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5521,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550362</v>
+        <v>550379</v>
       </c>
       <c r="R49" t="n">
-        <v>6994156</v>
+        <v>6994086</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5581,10 +5826,15 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004450</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004395</v>
+        <v>121004511</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5622,10 +5872,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550381</v>
+        <v>550470</v>
       </c>
       <c r="R50" t="n">
-        <v>6994155</v>
+        <v>6993852</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5660,6 +5910,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5682,10 +5937,15 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004511</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004439</v>
+        <v>121004515</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5723,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550405</v>
+        <v>550464</v>
       </c>
       <c r="R51" t="n">
-        <v>6994090</v>
+        <v>6993901</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5761,11 +6021,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5788,10 +6043,15 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004515</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004450</v>
+        <v>126099630</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -5825,14 +6085,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550379</v>
+        <v>550494</v>
       </c>
       <c r="R52" t="n">
-        <v>6994086</v>
+        <v>6994148</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5859,12 +6119,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5889,13 +6154,18 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099630</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004511</v>
+        <v>134246394</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5921,22 +6191,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550470</v>
+        <v>550512</v>
       </c>
       <c r="R53" t="n">
-        <v>6993852</v>
+        <v>6994236</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5960,17 +6227,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5979,29 +6241,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246394</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121004515</v>
+        <v>134246395</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6027,22 +6293,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550464</v>
+        <v>550292</v>
       </c>
       <c r="R54" t="n">
-        <v>6993901</v>
+        <v>6994150</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6066,12 +6329,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6080,67 +6343,69 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246395</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126099630</v>
+        <v>102089806</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550494</v>
+        <v>550469</v>
       </c>
       <c r="R55" t="n">
-        <v>6994148</v>
+        <v>6994094</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6167,17 +6432,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6186,7 +6446,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6202,51 +6461,59 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089806</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134246394</v>
+        <v>121004349</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550512</v>
+        <v>550358</v>
       </c>
       <c r="R56" t="n">
-        <v>6994236</v>
+        <v>6994160</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6270,12 +6537,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6284,66 +6551,75 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004349</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134246395</v>
+        <v>121004374</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550292</v>
+        <v>550369</v>
       </c>
       <c r="R57" t="n">
-        <v>6994150</v>
+        <v>6994167</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6367,12 +6643,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,25 +6657,31 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004374</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102089806</v>
+        <v>121004533</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6428,17 +6710,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550469</v>
+        <v>550456</v>
       </c>
       <c r="R58" t="n">
-        <v>6994094</v>
+        <v>6993982</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6465,12 +6749,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6479,6 +6768,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6494,10 +6784,15 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004533</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004349</v>
+        <v>126099591</v>
       </c>
       <c r="B59" t="n">
         <v>79946</v>
@@ -6531,14 +6826,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550358</v>
+        <v>550464</v>
       </c>
       <c r="R59" t="n">
-        <v>6994160</v>
+        <v>6994104</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6565,12 +6860,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6595,35 +6890,40 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099591</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004374</v>
+        <v>126099553</v>
       </c>
       <c r="B60" t="n">
-        <v>79946</v>
+        <v>80336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6632,14 +6932,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550369</v>
+        <v>550465</v>
       </c>
       <c r="R60" t="n">
-        <v>6994167</v>
+        <v>6994163</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6666,12 +6966,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6696,13 +7001,18 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099553</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004533</v>
+        <v>102088995</v>
       </c>
       <c r="B61" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6710,37 +7020,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550456</v>
+        <v>550570</v>
       </c>
       <c r="R61" t="n">
-        <v>6993982</v>
+        <v>6994156</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6767,17 +7075,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På kolad högstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6786,7 +7094,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6802,13 +7109,18 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102088995</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126099591</v>
+        <v>102089929</v>
       </c>
       <c r="B62" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6816,37 +7128,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550464</v>
+        <v>550373</v>
       </c>
       <c r="R62" t="n">
-        <v>6994104</v>
+        <v>6994082</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6873,12 +7183,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6887,7 +7197,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6903,35 +7212,40 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089929</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126099553</v>
+        <v>121004521</v>
       </c>
       <c r="B63" t="n">
-        <v>80336</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6940,14 +7254,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550465</v>
+        <v>550494</v>
       </c>
       <c r="R63" t="n">
-        <v>6994163</v>
+        <v>6993901</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6974,17 +7288,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7009,35 +7323,40 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004521</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102088995</v>
+        <v>102089008</v>
       </c>
       <c r="B64" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7112,35 +7431,40 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089008</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089929</v>
+        <v>102089938</v>
       </c>
       <c r="B65" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7210,51 +7534,54 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089938</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121004521</v>
+        <v>102089013</v>
       </c>
       <c r="B66" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550494</v>
+        <v>550570</v>
       </c>
       <c r="R66" t="n">
-        <v>6993901</v>
+        <v>6994156</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7281,12 +7608,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7300,7 +7627,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7316,13 +7642,18 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089013</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089008</v>
+        <v>102089935</v>
       </c>
       <c r="B67" t="n">
-        <v>80461</v>
+        <v>80467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7330,21 +7661,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7355,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550570</v>
+        <v>550373</v>
       </c>
       <c r="R67" t="n">
-        <v>6994156</v>
+        <v>6994082</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7393,11 +7724,6 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7419,13 +7745,18 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089935</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102089938</v>
+        <v>121004525</v>
       </c>
       <c r="B68" t="n">
-        <v>80461</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7433,35 +7764,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550373</v>
+        <v>550502</v>
       </c>
       <c r="R68" t="n">
-        <v>6994082</v>
+        <v>6993935</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7488,12 +7826,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7517,13 +7855,18 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004525</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102089013</v>
+        <v>134246389</v>
       </c>
       <c r="B69" t="n">
-        <v>80467</v>
+        <v>58131</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7531,35 +7874,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>103023</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550570</v>
+        <v>550466</v>
       </c>
       <c r="R69" t="n">
-        <v>6994156</v>
+        <v>6994147</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7586,17 +7928,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7611,22 +7948,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246389</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102089935</v>
+        <v>134246392</v>
       </c>
       <c r="B70" t="n">
-        <v>80467</v>
+        <v>98219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7634,38 +7976,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>219815</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550373</v>
+        <v>550548</v>
       </c>
       <c r="R70" t="n">
-        <v>6994082</v>
+        <v>6994192</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7689,12 +8030,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7709,22 +8050,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246392</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121004525</v>
+        <v>135466568</v>
       </c>
       <c r="B71" t="n">
-        <v>57141</v>
+        <v>99230</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7732,42 +8078,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550502</v>
+        <v>550481</v>
       </c>
       <c r="R71" t="n">
-        <v>6993935</v>
+        <v>6993999</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7794,12 +8140,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7808,6 +8154,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7823,48 +8170,55 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466568</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134246389</v>
+        <v>102088784</v>
       </c>
       <c r="B72" t="n">
-        <v>58131</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103023</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550466</v>
+        <v>550571</v>
       </c>
       <c r="R72" t="n">
-        <v>6994147</v>
+        <v>6994155</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7891,12 +8245,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7911,60 +8265,67 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102088784</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134246392</v>
+        <v>102089119</v>
       </c>
       <c r="B73" t="n">
-        <v>98219</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219815</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550548</v>
+        <v>550567</v>
       </c>
       <c r="R73" t="n">
-        <v>6994192</v>
+        <v>6994155</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7988,12 +8349,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8008,65 +8369,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089119</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135466568</v>
+        <v>102089419</v>
       </c>
       <c r="B74" t="n">
-        <v>99230</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550481</v>
+        <v>550554</v>
       </c>
       <c r="R74" t="n">
-        <v>6993999</v>
+        <v>6994133</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8093,12 +8453,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8107,7 +8467,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8123,10 +8482,15 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089419</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102088784</v>
+        <v>102089819</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8159,14 +8523,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550571</v>
+        <v>550446</v>
       </c>
       <c r="R75" t="n">
-        <v>6994155</v>
+        <v>6994089</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8222,10 +8586,15 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089819</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102089119</v>
+        <v>121004332</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8254,18 +8623,20 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550567</v>
+        <v>550310</v>
       </c>
       <c r="R76" t="n">
-        <v>6994155</v>
+        <v>6994126</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8292,12 +8663,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8306,6 +8677,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8321,10 +8693,15 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004332</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102089419</v>
+        <v>121004405</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8353,18 +8730,20 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550554</v>
+        <v>550404</v>
       </c>
       <c r="R77" t="n">
-        <v>6994133</v>
+        <v>6994153</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8391,12 +8770,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8405,6 +8784,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8420,10 +8800,15 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004405</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102089819</v>
+        <v>121004422</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8452,18 +8837,20 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550446</v>
+        <v>550395</v>
       </c>
       <c r="R78" t="n">
-        <v>6994089</v>
+        <v>6994127</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8490,12 +8877,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8504,6 +8891,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8519,10 +8907,15 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004422</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004332</v>
+        <v>121004461</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8561,10 +8954,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550310</v>
+        <v>550389</v>
       </c>
       <c r="R79" t="n">
-        <v>6994126</v>
+        <v>6994063</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8621,10 +9014,15 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004461</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004405</v>
+        <v>121004477</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -8663,10 +9061,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550404</v>
+        <v>550370</v>
       </c>
       <c r="R80" t="n">
-        <v>6994153</v>
+        <v>6993853</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8723,10 +9121,15 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004477</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004422</v>
+        <v>121004505</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -8765,10 +9168,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550395</v>
+        <v>550496</v>
       </c>
       <c r="R81" t="n">
-        <v>6994127</v>
+        <v>6993835</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8825,10 +9228,15 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004505</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004461</v>
+        <v>121004519</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -8867,10 +9275,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550389</v>
+        <v>550494</v>
       </c>
       <c r="R82" t="n">
-        <v>6994063</v>
+        <v>6993901</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8905,6 +9313,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -8927,10 +9340,15 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004519</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004477</v>
+        <v>121004558</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -8969,10 +9387,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550370</v>
+        <v>550516</v>
       </c>
       <c r="R83" t="n">
-        <v>6993853</v>
+        <v>6994130</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9029,10 +9447,15 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004558</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004505</v>
+        <v>121004562</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9071,10 +9494,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550496</v>
+        <v>550520</v>
       </c>
       <c r="R84" t="n">
-        <v>6993835</v>
+        <v>6994154</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9131,10 +9554,15 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004562</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004519</v>
+        <v>121004565</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9173,10 +9601,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550494</v>
+        <v>550469</v>
       </c>
       <c r="R85" t="n">
-        <v>6993901</v>
+        <v>6994270</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9211,11 +9639,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9238,10 +9661,15 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004565</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121004558</v>
+        <v>126099534</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9276,14 +9704,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550516</v>
+        <v>550463</v>
       </c>
       <c r="R86" t="n">
-        <v>6994130</v>
+        <v>6994172</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9310,12 +9738,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9340,13 +9768,18 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099534</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121004562</v>
+        <v>134246388</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9372,23 +9805,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550520</v>
+        <v>550414</v>
       </c>
       <c r="R87" t="n">
-        <v>6994154</v>
+        <v>6994084</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9412,12 +9841,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9426,51 +9855,55 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246388</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121004565</v>
+        <v>135466572</v>
       </c>
       <c r="B88" t="n">
-        <v>99118</v>
+        <v>98066</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9484,10 +9917,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550469</v>
+        <v>550481</v>
       </c>
       <c r="R88" t="n">
-        <v>6994270</v>
+        <v>6993999</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9514,12 +9947,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9544,55 +9977,56 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466572</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126099534</v>
+        <v>134246393</v>
       </c>
       <c r="B89" t="n">
-        <v>99118</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550463</v>
+        <v>550548</v>
       </c>
       <c r="R89" t="n">
-        <v>6994172</v>
+        <v>6994192</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9616,12 +10050,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9630,64 +10064,68 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246393</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246388</v>
+        <v>134246406</v>
       </c>
       <c r="B90" t="n">
-        <v>99195</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550414</v>
+        <v>550277</v>
       </c>
       <c r="R90" t="n">
-        <v>6994084</v>
+        <v>6994166</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9743,56 +10181,56 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135457589</v>
+        <v>126099623</v>
       </c>
       <c r="B91" t="n">
-        <v>99195</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550445</v>
+        <v>550481</v>
       </c>
       <c r="R91" t="n">
-        <v>6993808</v>
+        <v>6994133</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9819,17 +10257,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönpyrola.</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9854,59 +10287,56 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099623</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135457681</v>
+        <v>134246390</v>
       </c>
       <c r="B92" t="n">
-        <v>99195</v>
+        <v>79131</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550350</v>
+        <v>550466</v>
       </c>
       <c r="R92" t="n">
-        <v>6993905</v>
+        <v>6994147</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9930,12 +10360,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9944,72 +10374,69 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246390</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135457684</v>
+        <v>102089933</v>
       </c>
       <c r="B93" t="n">
-        <v>99195</v>
+        <v>80392</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550343</v>
+        <v>550373</v>
       </c>
       <c r="R93" t="n">
-        <v>6993884</v>
+        <v>6994082</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10036,12 +10463,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10050,7 +10477,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10066,923 +10492,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>135457690</v>
-      </c>
-      <c r="B94" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>550353</v>
-      </c>
-      <c r="R94" t="n">
-        <v>6993851</v>
-      </c>
-      <c r="S94" t="n">
-        <v>25</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135457698</v>
-      </c>
-      <c r="B95" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>550455</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6994009</v>
-      </c>
-      <c r="S95" t="n">
-        <v>25</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>135457602</v>
-      </c>
-      <c r="B96" t="n">
-        <v>106324</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>550445</v>
-      </c>
-      <c r="R96" t="n">
-        <v>6993808</v>
-      </c>
-      <c r="S96" t="n">
-        <v>25</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Tillsammans med knärot.</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>135466572</v>
-      </c>
-      <c r="B97" t="n">
-        <v>98066</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>550481</v>
-      </c>
-      <c r="R97" t="n">
-        <v>6993999</v>
-      </c>
-      <c r="S97" t="n">
-        <v>25</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>134246393</v>
-      </c>
-      <c r="B98" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>550548</v>
-      </c>
-      <c r="R98" t="n">
-        <v>6994192</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>134246406</v>
-      </c>
-      <c r="B99" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Lapprännbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>550277</v>
-      </c>
-      <c r="R99" t="n">
-        <v>6994166</v>
-      </c>
-      <c r="S99" t="n">
-        <v>10</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>126099623</v>
-      </c>
-      <c r="B100" t="n">
-        <v>79085</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q100" t="n">
-        <v>550481</v>
-      </c>
-      <c r="R100" t="n">
-        <v>6994133</v>
-      </c>
-      <c r="S100" t="n">
-        <v>25</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AD100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="inlineStr"/>
-      <c r="AW100" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>134246390</v>
-      </c>
-      <c r="B101" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>550466</v>
-      </c>
-      <c r="R101" t="n">
-        <v>6994147</v>
-      </c>
-      <c r="S101" t="n">
-        <v>10</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>102089933</v>
-      </c>
-      <c r="B102" t="n">
-        <v>80392</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q102" t="n">
-        <v>550373</v>
-      </c>
-      <c r="R102" t="n">
-        <v>6994082</v>
-      </c>
-      <c r="S102" t="n">
-        <v>25</v>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AD102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT102" t="inlineStr"/>
-      <c r="AW102" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089933</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ93"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,32 +1321,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004536</v>
+        <v>135457711</v>
       </c>
       <c r="B8" t="n">
-        <v>81312</v>
+        <v>92588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550477</v>
+        <v>550504</v>
       </c>
       <c r="R8" t="n">
-        <v>6994042</v>
+        <v>6993854</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,13 +1421,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004536</t>
+          <t>https://artportalen.se/Sighting/135457711</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004550</v>
+        <v>121004536</v>
       </c>
       <c r="B9" t="n">
         <v>81312</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550508</v>
+        <v>550477</v>
       </c>
       <c r="R9" t="n">
-        <v>6994113</v>
+        <v>6994042</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1527,13 +1527,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004550</t>
+          <t>https://artportalen.se/Sighting/121004536</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126099520</v>
+        <v>121004550</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1567,14 +1567,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550419</v>
+        <v>550508</v>
       </c>
       <c r="R10" t="n">
-        <v>6994207</v>
+        <v>6994113</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,16 +1633,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099520</t>
+          <t>https://artportalen.se/Sighting/121004550</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102089224</v>
+        <v>126099520</v>
       </c>
       <c r="B11" t="n">
-        <v>83173</v>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,35 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550562</v>
+        <v>550419</v>
       </c>
       <c r="R11" t="n">
-        <v>6994152</v>
+        <v>6994207</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1705,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,6 +1721,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,54 +1739,52 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089224</t>
+          <t>https://artportalen.se/Sighting/126099520</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004416</v>
+        <v>102089224</v>
       </c>
       <c r="B12" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550398</v>
+        <v>550562</v>
       </c>
       <c r="R12" t="n">
-        <v>6994131</v>
+        <v>6994152</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1810,12 +1811,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1842,13 +1842,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004416</t>
+          <t>https://artportalen.se/Sighting/102089224</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004472</v>
+        <v>121004416</v>
       </c>
       <c r="B13" t="n">
         <v>92083</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550400</v>
+        <v>550398</v>
       </c>
       <c r="R13" t="n">
-        <v>6993983</v>
+        <v>6994131</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,38 +1948,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004472</t>
+          <t>https://artportalen.se/Sighting/121004416</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004362</v>
+        <v>121004472</v>
       </c>
       <c r="B14" t="n">
-        <v>90932</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550364</v>
+        <v>550400</v>
       </c>
       <c r="R14" t="n">
-        <v>6994169</v>
+        <v>6993983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,13 +2054,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004362</t>
+          <t>https://artportalen.se/Sighting/121004472</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004490</v>
+        <v>121004362</v>
       </c>
       <c r="B15" t="n">
         <v>90932</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550508</v>
+        <v>550364</v>
       </c>
       <c r="R15" t="n">
-        <v>6993803</v>
+        <v>6994169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004490</t>
+          <t>https://artportalen.se/Sighting/121004362</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004539</v>
+        <v>121004490</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550486</v>
+        <v>550508</v>
       </c>
       <c r="R16" t="n">
-        <v>6994062</v>
+        <v>6993803</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,16 +2266,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004539</t>
+          <t>https://artportalen.se/Sighting/121004490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62025591</v>
+        <v>121004539</v>
       </c>
       <c r="B17" t="n">
-        <v>91962</v>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,37 +2283,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550409</v>
+        <v>550486</v>
       </c>
       <c r="R17" t="n">
-        <v>6994048</v>
+        <v>6994062</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,12 +2340,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,43 +2354,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025591</t>
+          <t>https://artportalen.se/Sighting/121004539</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102089002</v>
+        <v>62025591</v>
       </c>
       <c r="B18" t="n">
-        <v>80433</v>
+        <v>91962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,38 +2389,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550570</v>
+        <v>550409</v>
       </c>
       <c r="R18" t="n">
-        <v>6994156</v>
+        <v>6994048</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2450,17 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2471,69 +2459,80 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089002</t>
+          <t>https://artportalen.se/Sighting/62025591</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103996059</v>
+        <v>102089002</v>
       </c>
       <c r="B19" t="n">
-        <v>96338</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550310</v>
+        <v>550570</v>
       </c>
       <c r="R19" t="n">
-        <v>6994183</v>
+        <v>6994156</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,22 +2556,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,11 +2577,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2597,67 +2586,60 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/102089002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004351</v>
+        <v>103996059</v>
       </c>
       <c r="B20" t="n">
-        <v>91831</v>
+        <v>96338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3242</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550358</v>
+        <v>550310</v>
       </c>
       <c r="R20" t="n">
-        <v>6994160</v>
+        <v>6994183</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,12 +2663,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,9 +2687,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2707,19 +2703,23 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004351</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004470</v>
+        <v>121004351</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550383</v>
+        <v>550358</v>
       </c>
       <c r="R21" t="n">
-        <v>6993994</v>
+        <v>6994160</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2795,11 +2795,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2824,16 +2819,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004470</t>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>62025592</v>
+        <v>121004470</v>
       </c>
       <c r="B22" t="n">
-        <v>93197</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,37 +2836,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550409</v>
+        <v>550383</v>
       </c>
       <c r="R22" t="n">
-        <v>6994048</v>
+        <v>6993994</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2895,12 +2893,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2909,43 +2912,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025592</t>
+          <t>https://artportalen.se/Sighting/121004470</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102089700</v>
+        <v>135457707</v>
       </c>
       <c r="B23" t="n">
-        <v>93197</v>
+        <v>93305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,35 +2947,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550476</v>
+        <v>550510</v>
       </c>
       <c r="R23" t="n">
-        <v>6994117</v>
+        <v>6993821</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3008,12 +3004,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,6 +3018,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3039,13 +3036,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089700</t>
+          <t>https://artportalen.se/Sighting/135457707</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103996072</v>
+        <v>62025592</v>
       </c>
       <c r="B24" t="n">
         <v>93197</v>
@@ -3076,14 +3073,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550481</v>
+        <v>550409</v>
       </c>
       <c r="R24" t="n">
-        <v>6994068</v>
+        <v>6994048</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3110,22 +3107,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,36 +3124,37 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996072</t>
+          <t>https://artportalen.se/Sighting/62025592</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103996080</v>
+        <v>102089700</v>
       </c>
       <c r="B25" t="n">
         <v>93197</v>
@@ -3195,19 +3183,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550485</v>
+        <v>550476</v>
       </c>
       <c r="R25" t="n">
-        <v>6994105</v>
+        <v>6994117</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,22 +3220,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,11 +3236,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3271,23 +3245,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996080</t>
+          <t>https://artportalen.se/Sighting/102089700</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004341</v>
+        <v>103996072</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3316,22 +3286,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550344</v>
+        <v>550481</v>
       </c>
       <c r="R26" t="n">
-        <v>6994160</v>
+        <v>6994068</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3355,12 +3322,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,9 +3346,13 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3381,19 +3362,23 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004341</t>
+          <t>https://artportalen.se/Sighting/103996072</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004394</v>
+        <v>103996080</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3422,22 +3407,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550381</v>
+        <v>550485</v>
       </c>
       <c r="R27" t="n">
-        <v>6994155</v>
+        <v>6994105</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,12 +3443,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,9 +3467,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3487,19 +3483,23 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004394</t>
+          <t>https://artportalen.se/Sighting/103996080</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004399</v>
+        <v>121004341</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550384</v>
+        <v>550344</v>
       </c>
       <c r="R28" t="n">
-        <v>6994151</v>
+        <v>6994160</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3599,13 +3599,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004399</t>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004430</v>
+        <v>121004394</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550422</v>
+        <v>550381</v>
       </c>
       <c r="R29" t="n">
-        <v>6994093</v>
+        <v>6994155</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3705,13 +3705,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004430</t>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004475</v>
+        <v>121004399</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550385</v>
+        <v>550384</v>
       </c>
       <c r="R30" t="n">
-        <v>6993920</v>
+        <v>6994151</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3811,13 +3811,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004475</t>
+          <t>https://artportalen.se/Sighting/121004399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004484</v>
+        <v>121004430</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550427</v>
+        <v>550422</v>
       </c>
       <c r="R31" t="n">
-        <v>6993867</v>
+        <v>6994093</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,13 +3917,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004484</t>
+          <t>https://artportalen.se/Sighting/121004430</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004500</v>
+        <v>121004475</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550496</v>
+        <v>550385</v>
       </c>
       <c r="R32" t="n">
-        <v>6993817</v>
+        <v>6993920</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4023,13 +4023,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004500</t>
+          <t>https://artportalen.se/Sighting/121004475</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004509</v>
+        <v>121004484</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550476</v>
+        <v>550427</v>
       </c>
       <c r="R33" t="n">
-        <v>6993841</v>
+        <v>6993867</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,13 +4129,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004509</t>
+          <t>https://artportalen.se/Sighting/121004484</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004524</v>
+        <v>121004500</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550502</v>
+        <v>550496</v>
       </c>
       <c r="R34" t="n">
-        <v>6993935</v>
+        <v>6993817</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,13 +4235,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004524</t>
+          <t>https://artportalen.se/Sighting/121004500</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004537</v>
+        <v>121004509</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550477</v>
+        <v>550476</v>
       </c>
       <c r="R35" t="n">
-        <v>6994042</v>
+        <v>6993841</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4341,13 +4341,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004537</t>
+          <t>https://artportalen.se/Sighting/121004509</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004540</v>
+        <v>121004524</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550505</v>
+        <v>550502</v>
       </c>
       <c r="R36" t="n">
-        <v>6994074</v>
+        <v>6993935</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4447,13 +4447,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004540</t>
+          <t>https://artportalen.se/Sighting/121004524</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004541</v>
+        <v>121004537</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550528</v>
+        <v>550477</v>
       </c>
       <c r="R37" t="n">
-        <v>6994067</v>
+        <v>6994042</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4553,13 +4553,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004541</t>
+          <t>https://artportalen.se/Sighting/121004537</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004547</v>
+        <v>121004540</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550493</v>
+        <v>550505</v>
       </c>
       <c r="R38" t="n">
-        <v>6994078</v>
+        <v>6994074</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4659,16 +4659,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004547</t>
+          <t>https://artportalen.se/Sighting/121004540</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134246391</v>
+        <v>121004541</v>
       </c>
       <c r="B39" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,19 +4694,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550317</v>
+        <v>550528</v>
       </c>
       <c r="R39" t="n">
-        <v>6994117</v>
+        <v>6994067</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4730,12 +4733,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,55 +4747,56 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/121004541</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004494</v>
+        <v>121004547</v>
       </c>
       <c r="B40" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4805,10 +4809,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550515</v>
+        <v>550493</v>
       </c>
       <c r="R40" t="n">
-        <v>6993816</v>
+        <v>6994078</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4867,57 +4871,54 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004494</t>
+          <t>https://artportalen.se/Sighting/121004547</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004545</v>
+        <v>134246391</v>
       </c>
       <c r="B41" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550493</v>
+        <v>550317</v>
       </c>
       <c r="R41" t="n">
-        <v>6994078</v>
+        <v>6994117</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4941,12 +4942,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,34 +4956,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004545</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135457522</v>
+        <v>121004494</v>
       </c>
       <c r="B42" t="n">
-        <v>93275</v>
+        <v>93201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550478</v>
+        <v>550515</v>
       </c>
       <c r="R42" t="n">
-        <v>6993873</v>
+        <v>6993816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,38 +5079,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457522</t>
+          <t>https://artportalen.se/Sighting/121004494</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004409</v>
+        <v>121004545</v>
       </c>
       <c r="B43" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550413</v>
+        <v>550493</v>
       </c>
       <c r="R43" t="n">
-        <v>6994137</v>
+        <v>6994078</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5185,16 +5185,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/121004545</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102089839</v>
+        <v>135457522</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>93317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5202,38 +5202,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550410</v>
+        <v>550478</v>
       </c>
       <c r="R44" t="n">
-        <v>6994101</v>
+        <v>6993873</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5257,12 +5259,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,6 +5273,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5288,38 +5291,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004337</v>
+        <v>121004409</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550319</v>
+        <v>550413</v>
       </c>
       <c r="R45" t="n">
-        <v>6994143</v>
+        <v>6994137</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5370,11 +5373,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5399,38 +5397,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004358</v>
+        <v>135457649</v>
       </c>
       <c r="B46" t="n">
-        <v>79327</v>
+        <v>89260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5443,10 +5441,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550362</v>
+        <v>550447</v>
       </c>
       <c r="R46" t="n">
-        <v>6994156</v>
+        <v>6993828</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5473,12 +5471,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5505,13 +5503,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/135457649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004395</v>
+        <v>102089839</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5540,19 +5538,17 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550381</v>
+        <v>550410</v>
       </c>
       <c r="R47" t="n">
-        <v>6994155</v>
+        <v>6994101</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,12 +5575,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,7 +5589,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5611,13 +5606,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004439</v>
+        <v>121004337</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5655,10 +5650,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550405</v>
+        <v>550319</v>
       </c>
       <c r="R48" t="n">
-        <v>6994090</v>
+        <v>6994143</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5695,7 +5690,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,13 +5717,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004450</v>
+        <v>121004358</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5766,10 +5761,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550379</v>
+        <v>550362</v>
       </c>
       <c r="R49" t="n">
-        <v>6994086</v>
+        <v>6994156</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5828,13 +5823,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004511</v>
+        <v>121004395</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550470</v>
+        <v>550381</v>
       </c>
       <c r="R50" t="n">
-        <v>6993852</v>
+        <v>6994155</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5910,11 +5905,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5939,13 +5929,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004515</v>
+        <v>121004439</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5983,10 +5973,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550464</v>
+        <v>550405</v>
       </c>
       <c r="R51" t="n">
-        <v>6993901</v>
+        <v>6994090</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6021,6 +6011,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6045,13 +6040,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126099630</v>
+        <v>121004450</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6085,14 +6080,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550494</v>
+        <v>550379</v>
       </c>
       <c r="R52" t="n">
-        <v>6994148</v>
+        <v>6994086</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6119,17 +6114,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6156,16 +6146,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246394</v>
+        <v>121004511</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6191,19 +6181,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550512</v>
+        <v>550470</v>
       </c>
       <c r="R53" t="n">
-        <v>6994236</v>
+        <v>6993852</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6227,12 +6220,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6241,33 +6239,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134246395</v>
+        <v>121004515</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6293,19 +6292,22 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550292</v>
+        <v>550464</v>
       </c>
       <c r="R54" t="n">
-        <v>6994150</v>
+        <v>6993901</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6329,12 +6331,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6343,69 +6345,72 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102089806</v>
+        <v>126099630</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R55" t="n">
-        <v>6994094</v>
+        <v>6994148</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6432,12 +6437,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,6 +6456,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6463,57 +6474,54 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004349</v>
+        <v>134246394</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550358</v>
+        <v>550512</v>
       </c>
       <c r="R56" t="n">
-        <v>6994160</v>
+        <v>6994236</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6537,12 +6545,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6551,75 +6559,71 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004374</v>
+        <v>134246395</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550369</v>
+        <v>550292</v>
       </c>
       <c r="R57" t="n">
-        <v>6994167</v>
+        <v>6994150</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6643,12 +6647,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6657,31 +6661,30 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004533</v>
+        <v>102089806</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6710,19 +6713,17 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550456</v>
+        <v>550469</v>
       </c>
       <c r="R58" t="n">
-        <v>6993982</v>
+        <v>6994094</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6749,17 +6750,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,7 +6764,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6786,13 +6781,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126099591</v>
+        <v>121004349</v>
       </c>
       <c r="B59" t="n">
         <v>79946</v>
@@ -6826,14 +6821,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550464</v>
+        <v>550358</v>
       </c>
       <c r="R59" t="n">
-        <v>6994104</v>
+        <v>6994160</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6860,12 +6855,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6892,38 +6887,38 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126099553</v>
+        <v>121004374</v>
       </c>
       <c r="B60" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6932,14 +6927,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550465</v>
+        <v>550369</v>
       </c>
       <c r="R60" t="n">
-        <v>6994163</v>
+        <v>6994167</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6966,17 +6961,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,16 +6993,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102088995</v>
+        <v>121004533</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7020,35 +7010,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550570</v>
+        <v>550456</v>
       </c>
       <c r="R61" t="n">
-        <v>6994156</v>
+        <v>6993982</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7075,17 +7067,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7094,6 +7086,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7111,16 +7104,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102089929</v>
+        <v>126099591</v>
       </c>
       <c r="B62" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,35 +7121,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550373</v>
+        <v>550464</v>
       </c>
       <c r="R62" t="n">
-        <v>6994082</v>
+        <v>6994104</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7183,12 +7178,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7197,6 +7192,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7214,38 +7210,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004521</v>
+        <v>126099553</v>
       </c>
       <c r="B63" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7254,14 +7250,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550494</v>
+        <v>550465</v>
       </c>
       <c r="R63" t="n">
-        <v>6993901</v>
+        <v>6994163</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7288,17 +7284,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7325,38 +7321,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102089008</v>
+        <v>102088995</v>
       </c>
       <c r="B64" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7433,38 +7429,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089938</v>
+        <v>102089929</v>
       </c>
       <c r="B65" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7536,52 +7532,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102089013</v>
+        <v>121004521</v>
       </c>
       <c r="B66" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550570</v>
+        <v>550494</v>
       </c>
       <c r="R66" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7608,12 +7606,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7627,6 +7625,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7644,16 +7643,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089935</v>
+        <v>102089008</v>
       </c>
       <c r="B67" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7661,21 +7660,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7685,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R67" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7724,6 +7723,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7747,16 +7751,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121004525</v>
+        <v>102089938</v>
       </c>
       <c r="B68" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7764,42 +7768,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550502</v>
+        <v>550373</v>
       </c>
       <c r="R68" t="n">
-        <v>6993935</v>
+        <v>6994082</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7826,12 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,16 +7854,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134246389</v>
+        <v>102089013</v>
       </c>
       <c r="B69" t="n">
-        <v>58131</v>
+        <v>80467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7874,34 +7871,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103023</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550466</v>
+        <v>550570</v>
       </c>
       <c r="R69" t="n">
-        <v>6994147</v>
+        <v>6994156</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7928,12 +7926,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,27 +7951,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134246392</v>
+        <v>102089935</v>
       </c>
       <c r="B70" t="n">
-        <v>98219</v>
+        <v>80467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7976,37 +7979,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219815</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550548</v>
+        <v>550373</v>
       </c>
       <c r="R70" t="n">
-        <v>6994192</v>
+        <v>6994082</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8030,12 +8034,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8050,27 +8054,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135466568</v>
+        <v>121004525</v>
       </c>
       <c r="B71" t="n">
-        <v>99230</v>
+        <v>57141</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,42 +8082,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550481</v>
+        <v>550502</v>
       </c>
       <c r="R71" t="n">
-        <v>6993999</v>
+        <v>6993935</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8140,12 +8144,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8154,7 +8158,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8172,53 +8175,51 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466568</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102088784</v>
+        <v>134246389</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>58131</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550571</v>
+        <v>550466</v>
       </c>
       <c r="R72" t="n">
-        <v>6994155</v>
+        <v>6994147</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8245,12 +8246,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8265,67 +8266,65 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102089119</v>
+        <v>134246392</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550567</v>
+        <v>550548</v>
       </c>
       <c r="R73" t="n">
-        <v>6994155</v>
+        <v>6994192</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8349,12 +8348,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8369,64 +8368,70 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102089419</v>
+        <v>135466568</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>99277</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550554</v>
+        <v>550481</v>
       </c>
       <c r="R74" t="n">
-        <v>6994133</v>
+        <v>6993999</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8453,12 +8458,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8467,6 +8472,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8484,13 +8490,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102089819</v>
+        <v>102088784</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8523,14 +8529,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550446</v>
+        <v>550571</v>
       </c>
       <c r="R75" t="n">
-        <v>6994089</v>
+        <v>6994155</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8588,13 +8594,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121004332</v>
+        <v>102089119</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8623,20 +8629,18 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550310</v>
+        <v>550567</v>
       </c>
       <c r="R76" t="n">
-        <v>6994126</v>
+        <v>6994155</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8663,12 +8667,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8677,7 +8681,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8695,13 +8698,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004405</v>
+        <v>102089419</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8730,20 +8733,18 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550404</v>
+        <v>550554</v>
       </c>
       <c r="R77" t="n">
-        <v>6994153</v>
+        <v>6994133</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8770,12 +8771,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,7 +8785,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8802,13 +8802,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121004422</v>
+        <v>102089819</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8837,20 +8837,18 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550395</v>
+        <v>550446</v>
       </c>
       <c r="R78" t="n">
-        <v>6994127</v>
+        <v>6994089</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8877,12 +8875,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8891,7 +8889,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8909,13 +8906,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004461</v>
+        <v>121004332</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8954,10 +8951,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550389</v>
+        <v>550310</v>
       </c>
       <c r="R79" t="n">
-        <v>6994063</v>
+        <v>6994126</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9016,13 +9013,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004477</v>
+        <v>121004405</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9061,10 +9058,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550370</v>
+        <v>550404</v>
       </c>
       <c r="R80" t="n">
-        <v>6993853</v>
+        <v>6994153</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9123,13 +9120,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004505</v>
+        <v>121004422</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9168,10 +9165,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550496</v>
+        <v>550395</v>
       </c>
       <c r="R81" t="n">
-        <v>6993835</v>
+        <v>6994127</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9230,13 +9227,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004519</v>
+        <v>121004461</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9275,10 +9272,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550494</v>
+        <v>550389</v>
       </c>
       <c r="R82" t="n">
-        <v>6993901</v>
+        <v>6994063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9313,11 +9310,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9342,13 +9334,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004558</v>
+        <v>121004477</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9387,10 +9379,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550516</v>
+        <v>550370</v>
       </c>
       <c r="R83" t="n">
-        <v>6994130</v>
+        <v>6993853</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9449,13 +9441,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004562</v>
+        <v>121004505</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9494,10 +9486,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550520</v>
+        <v>550496</v>
       </c>
       <c r="R84" t="n">
-        <v>6994154</v>
+        <v>6993835</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9556,13 +9548,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004565</v>
+        <v>121004519</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9601,10 +9593,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R85" t="n">
-        <v>6994270</v>
+        <v>6993901</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9639,6 +9631,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9663,13 +9660,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126099534</v>
+        <v>121004558</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9704,14 +9701,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550463</v>
+        <v>550516</v>
       </c>
       <c r="R86" t="n">
-        <v>6994172</v>
+        <v>6994130</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9738,12 +9735,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9770,16 +9767,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134246388</v>
+        <v>121004562</v>
       </c>
       <c r="B87" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9805,19 +9802,23 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550414</v>
+        <v>550520</v>
       </c>
       <c r="R87" t="n">
-        <v>6994084</v>
+        <v>6994154</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9841,12 +9842,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9855,55 +9856,56 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135466572</v>
+        <v>121004565</v>
       </c>
       <c r="B88" t="n">
-        <v>98066</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9917,10 +9919,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550481</v>
+        <v>550469</v>
       </c>
       <c r="R88" t="n">
-        <v>6993999</v>
+        <v>6994270</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9947,12 +9949,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9979,54 +9981,58 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466572</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134246393</v>
+        <v>126099534</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550548</v>
+        <v>550463</v>
       </c>
       <c r="R89" t="n">
-        <v>6994192</v>
+        <v>6994172</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10050,12 +10056,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10064,68 +10070,69 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246406</v>
+        <v>134246388</v>
       </c>
       <c r="B90" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550277</v>
+        <v>550414</v>
       </c>
       <c r="R90" t="n">
-        <v>6994166</v>
+        <v>6994084</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10183,54 +10190,59 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
+          <t>https://artportalen.se/Sighting/134246388</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126099623</v>
+        <v>135457589</v>
       </c>
       <c r="B91" t="n">
-        <v>79085</v>
+        <v>99242</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550481</v>
+        <v>550445</v>
       </c>
       <c r="R91" t="n">
-        <v>6994133</v>
+        <v>6993808</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10257,12 +10269,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönpyrola.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10289,54 +10306,62 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
+          <t>https://artportalen.se/Sighting/135457589</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134246390</v>
+        <v>135457681</v>
       </c>
       <c r="B92" t="n">
-        <v>79131</v>
+        <v>99242</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550466</v>
+        <v>550350</v>
       </c>
       <c r="R92" t="n">
-        <v>6994147</v>
+        <v>6993905</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10360,12 +10385,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10374,69 +10399,77 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
+          <t>https://artportalen.se/Sighting/135457681</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>102089933</v>
+        <v>135457684</v>
       </c>
       <c r="B93" t="n">
-        <v>80392</v>
+        <v>99242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550373</v>
+        <v>550343</v>
       </c>
       <c r="R93" t="n">
-        <v>6994082</v>
+        <v>6993884</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10463,12 +10496,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10477,6 +10510,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10493,6 +10527,966 @@
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457684</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135457690</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>550353</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6993851</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457690</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135457698</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>550455</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6994009</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457698</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135457602</v>
+      </c>
+      <c r="B96" t="n">
+        <v>106379</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>550445</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6993808</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Tillsammans med knärot.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457602</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135466572</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98110</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6993999</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466572</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134246393</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>550548</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6994192</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246393</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099623</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246390</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B102" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102089933</t>
         </is>
@@ -10592,6 +11586,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1324,7 +1324,7 @@
         <v>135457711</v>
       </c>
       <c r="B8" t="n">
-        <v>92588</v>
+        <v>92615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>135457707</v>
       </c>
       <c r="B23" t="n">
-        <v>93305</v>
+        <v>93332</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>135457522</v>
       </c>
       <c r="B44" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135457649</v>
       </c>
       <c r="B46" t="n">
-        <v>89260</v>
+        <v>89287</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>135466568</v>
       </c>
       <c r="B74" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>135457589</v>
       </c>
       <c r="B91" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>135457681</v>
       </c>
       <c r="B92" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>135457684</v>
       </c>
       <c r="B93" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>135457690</v>
       </c>
       <c r="B94" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>135457698</v>
       </c>
       <c r="B95" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>135457602</v>
       </c>
       <c r="B96" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>135466572</v>
       </c>
       <c r="B97" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,32 +1321,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135457711</v>
+        <v>121004536</v>
       </c>
       <c r="B8" t="n">
-        <v>92615</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550504</v>
+        <v>550477</v>
       </c>
       <c r="R8" t="n">
-        <v>6993854</v>
+        <v>6994042</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,13 +1421,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457711</t>
+          <t>https://artportalen.se/Sighting/121004536</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004536</v>
+        <v>121004550</v>
       </c>
       <c r="B9" t="n">
         <v>81312</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550477</v>
+        <v>550508</v>
       </c>
       <c r="R9" t="n">
-        <v>6994042</v>
+        <v>6994113</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1527,13 +1527,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004536</t>
+          <t>https://artportalen.se/Sighting/121004550</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004550</v>
+        <v>126099520</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1567,14 +1567,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550508</v>
+        <v>550419</v>
       </c>
       <c r="R10" t="n">
-        <v>6994113</v>
+        <v>6994207</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,16 +1633,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004550</t>
+          <t>https://artportalen.se/Sighting/126099520</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126099520</v>
+        <v>102089224</v>
       </c>
       <c r="B11" t="n">
-        <v>81312</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,37 +1650,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550419</v>
+        <v>550562</v>
       </c>
       <c r="R11" t="n">
-        <v>6994207</v>
+        <v>6994152</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1707,12 +1705,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,7 +1719,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1739,52 +1736,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099520</t>
+          <t>https://artportalen.se/Sighting/102089224</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102089224</v>
+        <v>121004416</v>
       </c>
       <c r="B12" t="n">
-        <v>83173</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550562</v>
+        <v>550398</v>
       </c>
       <c r="R12" t="n">
-        <v>6994152</v>
+        <v>6994131</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,12 +1810,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,6 +1824,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1842,13 +1842,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089224</t>
+          <t>https://artportalen.se/Sighting/121004416</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004416</v>
+        <v>121004472</v>
       </c>
       <c r="B13" t="n">
         <v>92083</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550398</v>
+        <v>550400</v>
       </c>
       <c r="R13" t="n">
-        <v>6994131</v>
+        <v>6993983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,38 +1948,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004416</t>
+          <t>https://artportalen.se/Sighting/121004472</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004472</v>
+        <v>121004362</v>
       </c>
       <c r="B14" t="n">
-        <v>92083</v>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550400</v>
+        <v>550364</v>
       </c>
       <c r="R14" t="n">
-        <v>6993983</v>
+        <v>6994169</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,13 +2054,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004472</t>
+          <t>https://artportalen.se/Sighting/121004362</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004362</v>
+        <v>121004490</v>
       </c>
       <c r="B15" t="n">
         <v>90932</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550364</v>
+        <v>550508</v>
       </c>
       <c r="R15" t="n">
-        <v>6994169</v>
+        <v>6993803</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004362</t>
+          <t>https://artportalen.se/Sighting/121004490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004490</v>
+        <v>121004539</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550508</v>
+        <v>550486</v>
       </c>
       <c r="R16" t="n">
-        <v>6993803</v>
+        <v>6994062</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,16 +2266,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004490</t>
+          <t>https://artportalen.se/Sighting/121004539</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004539</v>
+        <v>62025591</v>
       </c>
       <c r="B17" t="n">
-        <v>90932</v>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,40 +2283,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550486</v>
+        <v>550409</v>
       </c>
       <c r="R17" t="n">
-        <v>6994062</v>
+        <v>6994048</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,34 +2351,43 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004539</t>
+          <t>https://artportalen.se/Sighting/62025591</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62025591</v>
+        <v>102089002</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2389,37 +2395,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550409</v>
+        <v>550570</v>
       </c>
       <c r="R18" t="n">
-        <v>6994048</v>
+        <v>6994156</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,12 +2450,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,80 +2471,69 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025591</t>
+          <t>https://artportalen.se/Sighting/102089002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102089002</v>
+        <v>103996059</v>
       </c>
       <c r="B19" t="n">
-        <v>80433</v>
+        <v>96338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550570</v>
+        <v>550310</v>
       </c>
       <c r="R19" t="n">
-        <v>6994156</v>
+        <v>6994183</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2556,17 +2557,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2577,6 +2583,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2586,60 +2597,67 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089002</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103996059</v>
+        <v>121004351</v>
       </c>
       <c r="B20" t="n">
-        <v>96338</v>
+        <v>91831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550310</v>
+        <v>550358</v>
       </c>
       <c r="R20" t="n">
-        <v>6994183</v>
+        <v>6994160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2663,22 +2681,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,13 +2695,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2703,23 +2707,19 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004351</v>
+        <v>121004470</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550358</v>
+        <v>550383</v>
       </c>
       <c r="R21" t="n">
-        <v>6994160</v>
+        <v>6993994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2795,6 +2795,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2819,16 +2824,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004351</t>
+          <t>https://artportalen.se/Sighting/121004470</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004470</v>
+        <v>62025592</v>
       </c>
       <c r="B22" t="n">
-        <v>91831</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,40 +2841,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550383</v>
+        <v>550409</v>
       </c>
       <c r="R22" t="n">
-        <v>6993994</v>
+        <v>6994048</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2893,17 +2895,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,34 +2909,43 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004470</t>
+          <t>https://artportalen.se/Sighting/62025592</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135457707</v>
+        <v>102089700</v>
       </c>
       <c r="B23" t="n">
-        <v>93332</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,37 +2953,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550510</v>
+        <v>550476</v>
       </c>
       <c r="R23" t="n">
-        <v>6993821</v>
+        <v>6994117</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3004,12 +3008,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,7 +3022,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3036,13 +3039,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457707</t>
+          <t>https://artportalen.se/Sighting/102089700</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62025592</v>
+        <v>103996072</v>
       </c>
       <c r="B24" t="n">
         <v>93197</v>
@@ -3073,14 +3076,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550409</v>
+        <v>550481</v>
       </c>
       <c r="R24" t="n">
-        <v>6994048</v>
+        <v>6994068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3107,12 +3110,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,37 +3137,36 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025592</t>
+          <t>https://artportalen.se/Sighting/103996072</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102089700</v>
+        <v>103996080</v>
       </c>
       <c r="B25" t="n">
         <v>93197</v>
@@ -3183,20 +3195,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550476</v>
+        <v>550485</v>
       </c>
       <c r="R25" t="n">
-        <v>6994117</v>
+        <v>6994105</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3220,12 +3231,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,6 +3257,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3245,19 +3271,23 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089700</t>
+          <t>https://artportalen.se/Sighting/103996080</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103996072</v>
+        <v>121004341</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3286,19 +3316,22 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550481</v>
+        <v>550344</v>
       </c>
       <c r="R26" t="n">
-        <v>6994068</v>
+        <v>6994160</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3322,22 +3355,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3346,13 +3369,9 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3362,23 +3381,19 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996072</t>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103996080</v>
+        <v>121004394</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3407,19 +3422,22 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550485</v>
+        <v>550381</v>
       </c>
       <c r="R27" t="n">
-        <v>6994105</v>
+        <v>6994155</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3443,22 +3461,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,13 +3475,9 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3483,23 +3487,19 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996080</t>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004341</v>
+        <v>121004399</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550344</v>
+        <v>550384</v>
       </c>
       <c r="R28" t="n">
-        <v>6994160</v>
+        <v>6994151</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3599,13 +3599,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004341</t>
+          <t>https://artportalen.se/Sighting/121004399</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004394</v>
+        <v>121004430</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550381</v>
+        <v>550422</v>
       </c>
       <c r="R29" t="n">
-        <v>6994155</v>
+        <v>6994093</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3705,13 +3705,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004394</t>
+          <t>https://artportalen.se/Sighting/121004430</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004399</v>
+        <v>121004475</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550384</v>
+        <v>550385</v>
       </c>
       <c r="R30" t="n">
-        <v>6994151</v>
+        <v>6993920</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3811,13 +3811,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004399</t>
+          <t>https://artportalen.se/Sighting/121004475</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004430</v>
+        <v>121004484</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550422</v>
+        <v>550427</v>
       </c>
       <c r="R31" t="n">
-        <v>6994093</v>
+        <v>6993867</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,13 +3917,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004430</t>
+          <t>https://artportalen.se/Sighting/121004484</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004475</v>
+        <v>121004500</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550385</v>
+        <v>550496</v>
       </c>
       <c r="R32" t="n">
-        <v>6993920</v>
+        <v>6993817</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4023,13 +4023,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004475</t>
+          <t>https://artportalen.se/Sighting/121004500</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004484</v>
+        <v>121004509</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550427</v>
+        <v>550476</v>
       </c>
       <c r="R33" t="n">
-        <v>6993867</v>
+        <v>6993841</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,13 +4129,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004484</t>
+          <t>https://artportalen.se/Sighting/121004509</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004500</v>
+        <v>121004524</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550496</v>
+        <v>550502</v>
       </c>
       <c r="R34" t="n">
-        <v>6993817</v>
+        <v>6993935</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,13 +4235,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004500</t>
+          <t>https://artportalen.se/Sighting/121004524</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004509</v>
+        <v>121004537</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550476</v>
+        <v>550477</v>
       </c>
       <c r="R35" t="n">
-        <v>6993841</v>
+        <v>6994042</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4341,13 +4341,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004509</t>
+          <t>https://artportalen.se/Sighting/121004537</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004524</v>
+        <v>121004540</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550502</v>
+        <v>550505</v>
       </c>
       <c r="R36" t="n">
-        <v>6993935</v>
+        <v>6994074</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4447,13 +4447,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004524</t>
+          <t>https://artportalen.se/Sighting/121004540</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004537</v>
+        <v>121004541</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550477</v>
+        <v>550528</v>
       </c>
       <c r="R37" t="n">
-        <v>6994042</v>
+        <v>6994067</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4553,13 +4553,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004537</t>
+          <t>https://artportalen.se/Sighting/121004541</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004540</v>
+        <v>121004547</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550505</v>
+        <v>550493</v>
       </c>
       <c r="R38" t="n">
-        <v>6994074</v>
+        <v>6994078</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4659,16 +4659,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004540</t>
+          <t>https://artportalen.se/Sighting/121004547</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004541</v>
+        <v>134246391</v>
       </c>
       <c r="B39" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,22 +4694,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550528</v>
+        <v>550317</v>
       </c>
       <c r="R39" t="n">
-        <v>6994067</v>
+        <v>6994117</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4733,12 +4730,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4747,56 +4744,55 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004541</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004547</v>
+        <v>121004494</v>
       </c>
       <c r="B40" t="n">
-        <v>93197</v>
+        <v>93201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4809,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550493</v>
+        <v>550515</v>
       </c>
       <c r="R40" t="n">
-        <v>6994078</v>
+        <v>6993816</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4871,54 +4867,57 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004547</t>
+          <t>https://artportalen.se/Sighting/121004494</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134246391</v>
+        <v>121004545</v>
       </c>
       <c r="B41" t="n">
-        <v>93271</v>
+        <v>93201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550317</v>
+        <v>550493</v>
       </c>
       <c r="R41" t="n">
-        <v>6994117</v>
+        <v>6994078</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,12 +4941,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4956,33 +4955,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/121004545</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004494</v>
+        <v>135457522</v>
       </c>
       <c r="B42" t="n">
-        <v>93201</v>
+        <v>93344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550515</v>
+        <v>550478</v>
       </c>
       <c r="R42" t="n">
-        <v>6993816</v>
+        <v>6993873</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,38 +5079,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004494</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004545</v>
+        <v>121004409</v>
       </c>
       <c r="B43" t="n">
-        <v>93201</v>
+        <v>93209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550493</v>
+        <v>550413</v>
       </c>
       <c r="R43" t="n">
-        <v>6994078</v>
+        <v>6994137</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5185,16 +5185,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004545</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135457522</v>
+        <v>102089839</v>
       </c>
       <c r="B44" t="n">
-        <v>93344</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5202,40 +5202,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550478</v>
+        <v>550410</v>
       </c>
       <c r="R44" t="n">
-        <v>6993873</v>
+        <v>6994101</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5259,12 +5257,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5273,7 +5271,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5291,38 +5288,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457522</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004409</v>
+        <v>121004337</v>
       </c>
       <c r="B45" t="n">
-        <v>93209</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550413</v>
+        <v>550319</v>
       </c>
       <c r="R45" t="n">
-        <v>6994137</v>
+        <v>6994143</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5373,6 +5370,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5397,38 +5399,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135457649</v>
+        <v>121004358</v>
       </c>
       <c r="B46" t="n">
-        <v>89287</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5441,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550447</v>
+        <v>550362</v>
       </c>
       <c r="R46" t="n">
-        <v>6993828</v>
+        <v>6994156</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5471,12 +5473,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5503,13 +5505,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457649</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102089839</v>
+        <v>121004395</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5538,17 +5540,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550410</v>
+        <v>550381</v>
       </c>
       <c r="R47" t="n">
-        <v>6994101</v>
+        <v>6994155</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5575,12 +5579,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5589,6 +5593,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5606,13 +5611,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004337</v>
+        <v>121004439</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5650,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550319</v>
+        <v>550405</v>
       </c>
       <c r="R48" t="n">
-        <v>6994143</v>
+        <v>6994090</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5690,7 +5695,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5717,13 +5722,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004358</v>
+        <v>121004450</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5761,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550362</v>
+        <v>550379</v>
       </c>
       <c r="R49" t="n">
-        <v>6994156</v>
+        <v>6994086</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5823,13 +5828,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004395</v>
+        <v>121004511</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5867,10 +5872,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550381</v>
+        <v>550470</v>
       </c>
       <c r="R50" t="n">
-        <v>6994155</v>
+        <v>6993852</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5905,6 +5910,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5929,13 +5939,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004439</v>
+        <v>121004515</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5973,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550405</v>
+        <v>550464</v>
       </c>
       <c r="R51" t="n">
-        <v>6994090</v>
+        <v>6993901</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6011,11 +6021,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6040,13 +6045,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004450</v>
+        <v>126099630</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6080,14 +6085,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550379</v>
+        <v>550494</v>
       </c>
       <c r="R52" t="n">
-        <v>6994086</v>
+        <v>6994148</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,12 +6119,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6146,16 +6156,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004511</v>
+        <v>134246394</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6181,22 +6191,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550470</v>
+        <v>550512</v>
       </c>
       <c r="R53" t="n">
-        <v>6993852</v>
+        <v>6994236</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6220,17 +6227,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,34 +6241,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121004515</v>
+        <v>134246395</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6292,22 +6293,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550464</v>
+        <v>550292</v>
       </c>
       <c r="R54" t="n">
-        <v>6993901</v>
+        <v>6994150</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6331,12 +6329,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6345,72 +6343,69 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126099630</v>
+        <v>102089806</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550494</v>
+        <v>550469</v>
       </c>
       <c r="R55" t="n">
-        <v>6994148</v>
+        <v>6994094</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6437,17 +6432,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6446,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6474,54 +6463,57 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134246394</v>
+        <v>121004349</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550512</v>
+        <v>550358</v>
       </c>
       <c r="R56" t="n">
-        <v>6994236</v>
+        <v>6994160</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6545,12 +6537,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6559,71 +6551,75 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134246395</v>
+        <v>121004374</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550292</v>
+        <v>550369</v>
       </c>
       <c r="R57" t="n">
-        <v>6994150</v>
+        <v>6994167</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,12 +6643,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6661,30 +6657,31 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102089806</v>
+        <v>121004533</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6713,17 +6710,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550469</v>
+        <v>550456</v>
       </c>
       <c r="R58" t="n">
-        <v>6994094</v>
+        <v>6993982</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6750,12 +6749,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6764,6 +6768,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6781,13 +6786,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004349</v>
+        <v>126099591</v>
       </c>
       <c r="B59" t="n">
         <v>79946</v>
@@ -6821,14 +6826,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550358</v>
+        <v>550464</v>
       </c>
       <c r="R59" t="n">
-        <v>6994160</v>
+        <v>6994104</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6855,12 +6860,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6887,38 +6892,38 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004374</v>
+        <v>126099553</v>
       </c>
       <c r="B60" t="n">
-        <v>79946</v>
+        <v>80336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6927,14 +6932,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550369</v>
+        <v>550465</v>
       </c>
       <c r="R60" t="n">
-        <v>6994167</v>
+        <v>6994163</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6961,12 +6966,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,16 +7003,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004533</v>
+        <v>102088995</v>
       </c>
       <c r="B61" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7010,37 +7020,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550456</v>
+        <v>550570</v>
       </c>
       <c r="R61" t="n">
-        <v>6993982</v>
+        <v>6994156</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7067,17 +7075,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På kolad högstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7086,7 +7094,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7104,16 +7111,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126099591</v>
+        <v>102089929</v>
       </c>
       <c r="B62" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7121,37 +7128,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550464</v>
+        <v>550373</v>
       </c>
       <c r="R62" t="n">
-        <v>6994104</v>
+        <v>6994082</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7178,12 +7183,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7192,7 +7197,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7210,38 +7214,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126099553</v>
+        <v>121004521</v>
       </c>
       <c r="B63" t="n">
-        <v>80336</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,14 +7254,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550465</v>
+        <v>550494</v>
       </c>
       <c r="R63" t="n">
-        <v>6994163</v>
+        <v>6993901</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7284,17 +7288,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7321,38 +7325,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102088995</v>
+        <v>102089008</v>
       </c>
       <c r="B64" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7429,38 +7433,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089929</v>
+        <v>102089938</v>
       </c>
       <c r="B65" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7532,54 +7536,52 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121004521</v>
+        <v>102089013</v>
       </c>
       <c r="B66" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550494</v>
+        <v>550570</v>
       </c>
       <c r="R66" t="n">
-        <v>6993901</v>
+        <v>6994156</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7606,12 +7608,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7625,7 +7627,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7643,16 +7644,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089008</v>
+        <v>102089935</v>
       </c>
       <c r="B67" t="n">
-        <v>80461</v>
+        <v>80467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7660,21 +7661,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7685,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550570</v>
+        <v>550373</v>
       </c>
       <c r="R67" t="n">
-        <v>6994156</v>
+        <v>6994082</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7723,11 +7724,6 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7751,16 +7747,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102089938</v>
+        <v>121004525</v>
       </c>
       <c r="B68" t="n">
-        <v>80461</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7768,35 +7764,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550373</v>
+        <v>550502</v>
       </c>
       <c r="R68" t="n">
-        <v>6994082</v>
+        <v>6993935</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7823,12 +7826,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7854,16 +7857,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102089013</v>
+        <v>134246389</v>
       </c>
       <c r="B69" t="n">
-        <v>80467</v>
+        <v>58131</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7871,35 +7874,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>103023</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550570</v>
+        <v>550466</v>
       </c>
       <c r="R69" t="n">
-        <v>6994156</v>
+        <v>6994147</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7926,17 +7928,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7951,27 +7948,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102089935</v>
+        <v>134246392</v>
       </c>
       <c r="B70" t="n">
-        <v>80467</v>
+        <v>98219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7979,38 +7976,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>219815</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550373</v>
+        <v>550548</v>
       </c>
       <c r="R70" t="n">
-        <v>6994082</v>
+        <v>6994192</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8034,12 +8030,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8054,27 +8050,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121004525</v>
+        <v>135466568</v>
       </c>
       <c r="B71" t="n">
-        <v>57141</v>
+        <v>99304</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8082,42 +8078,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550502</v>
+        <v>550481</v>
       </c>
       <c r="R71" t="n">
-        <v>6993935</v>
+        <v>6993999</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8144,12 +8140,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8158,6 +8154,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8175,51 +8172,53 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134246389</v>
+        <v>102088784</v>
       </c>
       <c r="B72" t="n">
-        <v>58131</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103023</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550466</v>
+        <v>550571</v>
       </c>
       <c r="R72" t="n">
-        <v>6994147</v>
+        <v>6994155</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8246,12 +8245,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8266,65 +8265,67 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134246392</v>
+        <v>102089119</v>
       </c>
       <c r="B73" t="n">
-        <v>98219</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219815</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550548</v>
+        <v>550567</v>
       </c>
       <c r="R73" t="n">
-        <v>6994192</v>
+        <v>6994155</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8348,12 +8349,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8368,70 +8369,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135466568</v>
+        <v>102089419</v>
       </c>
       <c r="B74" t="n">
-        <v>99304</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550481</v>
+        <v>550554</v>
       </c>
       <c r="R74" t="n">
-        <v>6993999</v>
+        <v>6994133</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8458,12 +8453,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8472,7 +8467,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8490,13 +8484,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466568</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102088784</v>
+        <v>102089819</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8529,14 +8523,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550571</v>
+        <v>550446</v>
       </c>
       <c r="R75" t="n">
-        <v>6994155</v>
+        <v>6994089</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8594,13 +8588,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102089119</v>
+        <v>121004332</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8629,18 +8623,20 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550567</v>
+        <v>550310</v>
       </c>
       <c r="R76" t="n">
-        <v>6994155</v>
+        <v>6994126</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8667,12 +8663,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8681,6 +8677,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8698,13 +8695,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102089419</v>
+        <v>121004405</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8733,18 +8730,20 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550554</v>
+        <v>550404</v>
       </c>
       <c r="R77" t="n">
-        <v>6994133</v>
+        <v>6994153</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8771,12 +8770,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8785,6 +8784,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8802,13 +8802,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102089819</v>
+        <v>121004422</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8837,18 +8837,20 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550446</v>
+        <v>550395</v>
       </c>
       <c r="R78" t="n">
-        <v>6994089</v>
+        <v>6994127</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8875,12 +8877,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8889,6 +8891,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8906,13 +8909,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004332</v>
+        <v>121004461</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8951,10 +8954,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550310</v>
+        <v>550389</v>
       </c>
       <c r="R79" t="n">
-        <v>6994126</v>
+        <v>6994063</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9013,13 +9016,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004405</v>
+        <v>121004477</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9058,10 +9061,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550404</v>
+        <v>550370</v>
       </c>
       <c r="R80" t="n">
-        <v>6994153</v>
+        <v>6993853</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9120,13 +9123,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004422</v>
+        <v>121004505</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9165,10 +9168,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550395</v>
+        <v>550496</v>
       </c>
       <c r="R81" t="n">
-        <v>6994127</v>
+        <v>6993835</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9227,13 +9230,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004461</v>
+        <v>121004519</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9272,10 +9275,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550389</v>
+        <v>550494</v>
       </c>
       <c r="R82" t="n">
-        <v>6994063</v>
+        <v>6993901</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9310,6 +9313,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9334,13 +9342,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004477</v>
+        <v>121004558</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9379,10 +9387,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550370</v>
+        <v>550516</v>
       </c>
       <c r="R83" t="n">
-        <v>6993853</v>
+        <v>6994130</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9441,13 +9449,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004505</v>
+        <v>121004562</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9486,10 +9494,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550496</v>
+        <v>550520</v>
       </c>
       <c r="R84" t="n">
-        <v>6993835</v>
+        <v>6994154</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9548,13 +9556,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004519</v>
+        <v>121004565</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9593,10 +9601,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550494</v>
+        <v>550469</v>
       </c>
       <c r="R85" t="n">
-        <v>6993901</v>
+        <v>6994270</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9631,11 +9639,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9660,13 +9663,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121004558</v>
+        <v>126099534</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9701,14 +9704,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550516</v>
+        <v>550463</v>
       </c>
       <c r="R86" t="n">
-        <v>6994130</v>
+        <v>6994172</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9735,12 +9738,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9767,16 +9770,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121004562</v>
+        <v>134246388</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9802,23 +9805,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550520</v>
+        <v>550414</v>
       </c>
       <c r="R87" t="n">
-        <v>6994154</v>
+        <v>6994084</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9842,12 +9841,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9856,56 +9855,55 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/134246388</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121004565</v>
+        <v>135466572</v>
       </c>
       <c r="B88" t="n">
-        <v>99118</v>
+        <v>98137</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9919,10 +9917,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550469</v>
+        <v>550481</v>
       </c>
       <c r="R88" t="n">
-        <v>6994270</v>
+        <v>6993999</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9949,12 +9947,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9981,58 +9979,54 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/135466572</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126099534</v>
+        <v>134246393</v>
       </c>
       <c r="B89" t="n">
-        <v>99118</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550463</v>
+        <v>550548</v>
       </c>
       <c r="R89" t="n">
-        <v>6994172</v>
+        <v>6994192</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10056,12 +10050,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10070,69 +10064,68 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/134246393</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246388</v>
+        <v>134246406</v>
       </c>
       <c r="B90" t="n">
-        <v>99195</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550414</v>
+        <v>550277</v>
       </c>
       <c r="R90" t="n">
-        <v>6994084</v>
+        <v>6994166</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10190,59 +10183,54 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/134246406</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135457589</v>
+        <v>126099623</v>
       </c>
       <c r="B91" t="n">
-        <v>99269</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550445</v>
+        <v>550481</v>
       </c>
       <c r="R91" t="n">
-        <v>6993808</v>
+        <v>6994133</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10269,17 +10257,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönpyrola.</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10306,62 +10289,54 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457589</t>
+          <t>https://artportalen.se/Sighting/126099623</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135457681</v>
+        <v>134246390</v>
       </c>
       <c r="B92" t="n">
-        <v>99269</v>
+        <v>79131</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550350</v>
+        <v>550466</v>
       </c>
       <c r="R92" t="n">
-        <v>6993905</v>
+        <v>6994147</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10385,12 +10360,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10399,77 +10374,69 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457681</t>
+          <t>https://artportalen.se/Sighting/134246390</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135457684</v>
+        <v>102089933</v>
       </c>
       <c r="B93" t="n">
-        <v>99269</v>
+        <v>80392</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550343</v>
+        <v>550373</v>
       </c>
       <c r="R93" t="n">
-        <v>6993884</v>
+        <v>6994082</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10496,12 +10463,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10510,7 +10477,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10527,966 +10493,6 @@
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457684</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>135457690</v>
-      </c>
-      <c r="B94" t="n">
-        <v>99269</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>550353</v>
-      </c>
-      <c r="R94" t="n">
-        <v>6993851</v>
-      </c>
-      <c r="S94" t="n">
-        <v>25</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457690</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135457698</v>
-      </c>
-      <c r="B95" t="n">
-        <v>99269</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>550455</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6994009</v>
-      </c>
-      <c r="S95" t="n">
-        <v>25</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457698</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>135457602</v>
-      </c>
-      <c r="B96" t="n">
-        <v>106406</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>550445</v>
-      </c>
-      <c r="R96" t="n">
-        <v>6993808</v>
-      </c>
-      <c r="S96" t="n">
-        <v>25</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Tillsammans med knärot.</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457602</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>135466572</v>
-      </c>
-      <c r="B97" t="n">
-        <v>98137</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>550481</v>
-      </c>
-      <c r="R97" t="n">
-        <v>6993999</v>
-      </c>
-      <c r="S97" t="n">
-        <v>25</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135466572</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>134246393</v>
-      </c>
-      <c r="B98" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>550548</v>
-      </c>
-      <c r="R98" t="n">
-        <v>6994192</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>134246406</v>
-      </c>
-      <c r="B99" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Lapprännbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>550277</v>
-      </c>
-      <c r="R99" t="n">
-        <v>6994166</v>
-      </c>
-      <c r="S99" t="n">
-        <v>10</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>126099623</v>
-      </c>
-      <c r="B100" t="n">
-        <v>79085</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q100" t="n">
-        <v>550481</v>
-      </c>
-      <c r="R100" t="n">
-        <v>6994133</v>
-      </c>
-      <c r="S100" t="n">
-        <v>25</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AD100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="inlineStr"/>
-      <c r="AW100" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>134246390</v>
-      </c>
-      <c r="B101" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>550466</v>
-      </c>
-      <c r="R101" t="n">
-        <v>6994147</v>
-      </c>
-      <c r="S101" t="n">
-        <v>10</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>102089933</v>
-      </c>
-      <c r="B102" t="n">
-        <v>80392</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q102" t="n">
-        <v>550373</v>
-      </c>
-      <c r="R102" t="n">
-        <v>6994082</v>
-      </c>
-      <c r="S102" t="n">
-        <v>25</v>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AD102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT102" t="inlineStr"/>
-      <c r="AW102" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
-      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102089933</t>
         </is>
@@ -11586,15 +10592,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ90"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4979,32 +4979,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004409</v>
+        <v>135457522</v>
       </c>
       <c r="B42" t="n">
-        <v>93209</v>
+        <v>93349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550413</v>
+        <v>550478</v>
       </c>
       <c r="R42" t="n">
-        <v>6994137</v>
+        <v>6993873</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,52 +5079,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>102089839</v>
+        <v>121004409</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550410</v>
+        <v>550413</v>
       </c>
       <c r="R43" t="n">
-        <v>6994101</v>
+        <v>6994137</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,12 +5153,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5165,6 +5167,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5182,13 +5185,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121004337</v>
+        <v>102089839</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5217,19 +5220,17 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550319</v>
+        <v>550410</v>
       </c>
       <c r="R44" t="n">
-        <v>6994143</v>
+        <v>6994101</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5256,17 +5257,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5275,7 +5271,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5293,13 +5288,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004358</v>
+        <v>121004337</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5337,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550362</v>
+        <v>550319</v>
       </c>
       <c r="R45" t="n">
-        <v>6994156</v>
+        <v>6994143</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5375,6 +5370,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5399,13 +5399,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004395</v>
+        <v>121004358</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550381</v>
+        <v>550362</v>
       </c>
       <c r="R46" t="n">
-        <v>6994155</v>
+        <v>6994156</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5505,13 +5505,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004439</v>
+        <v>121004395</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550405</v>
+        <v>550381</v>
       </c>
       <c r="R47" t="n">
-        <v>6994090</v>
+        <v>6994155</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5587,11 +5587,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5616,13 +5611,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004450</v>
+        <v>121004439</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5660,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550379</v>
+        <v>550405</v>
       </c>
       <c r="R48" t="n">
-        <v>6994086</v>
+        <v>6994090</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5698,6 +5693,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5722,13 +5722,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004511</v>
+        <v>121004450</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550470</v>
+        <v>550379</v>
       </c>
       <c r="R49" t="n">
-        <v>6993852</v>
+        <v>6994086</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5804,11 +5804,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5833,13 +5828,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004515</v>
+        <v>121004511</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5877,10 +5872,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550464</v>
+        <v>550470</v>
       </c>
       <c r="R50" t="n">
-        <v>6993901</v>
+        <v>6993852</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5915,6 +5910,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5939,13 +5939,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126099630</v>
+        <v>121004515</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5979,14 +5979,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550494</v>
+        <v>550464</v>
       </c>
       <c r="R51" t="n">
-        <v>6994148</v>
+        <v>6993901</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6013,17 +6013,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6050,16 +6045,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134246394</v>
+        <v>126099630</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6085,19 +6080,22 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550512</v>
+        <v>550494</v>
       </c>
       <c r="R52" t="n">
-        <v>6994236</v>
+        <v>6994148</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6121,12 +6119,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,30 +6138,31 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246395</v>
+        <v>134246394</v>
       </c>
       <c r="B53" t="n">
         <v>79373</v>
@@ -6189,14 +6193,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550292</v>
+        <v>550512</v>
       </c>
       <c r="R53" t="n">
-        <v>6994150</v>
+        <v>6994236</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6254,55 +6258,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102089806</v>
+        <v>134246395</v>
       </c>
       <c r="B54" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550469</v>
+        <v>550292</v>
       </c>
       <c r="R54" t="n">
-        <v>6994094</v>
+        <v>6994150</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6326,12 +6329,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,24 +6349,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121004349</v>
+        <v>102089806</v>
       </c>
       <c r="B55" t="n">
         <v>79946</v>
@@ -6392,19 +6395,17 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550358</v>
+        <v>550469</v>
       </c>
       <c r="R55" t="n">
-        <v>6994160</v>
+        <v>6994094</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6431,12 +6432,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,7 +6446,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6463,13 +6463,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004374</v>
+        <v>121004349</v>
       </c>
       <c r="B56" t="n">
         <v>79946</v>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550369</v>
+        <v>550358</v>
       </c>
       <c r="R56" t="n">
-        <v>6994167</v>
+        <v>6994160</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6569,13 +6569,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004533</v>
+        <v>121004374</v>
       </c>
       <c r="B57" t="n">
         <v>79946</v>
@@ -6613,10 +6613,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550456</v>
+        <v>550369</v>
       </c>
       <c r="R57" t="n">
-        <v>6993982</v>
+        <v>6994167</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6651,11 +6651,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6680,13 +6675,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126099591</v>
+        <v>121004533</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6720,14 +6715,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550464</v>
+        <v>550456</v>
       </c>
       <c r="R58" t="n">
-        <v>6994104</v>
+        <v>6993982</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6754,12 +6749,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6786,38 +6786,38 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126099553</v>
+        <v>126099591</v>
       </c>
       <c r="B59" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550465</v>
+        <v>550464</v>
       </c>
       <c r="R59" t="n">
-        <v>6994163</v>
+        <v>6994104</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6868,11 +6868,6 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6897,52 +6892,54 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102088995</v>
+        <v>126099553</v>
       </c>
       <c r="B60" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550570</v>
+        <v>550465</v>
       </c>
       <c r="R60" t="n">
-        <v>6994156</v>
+        <v>6994163</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6969,17 +6966,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,6 +6985,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7005,13 +7003,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102089929</v>
+        <v>102088995</v>
       </c>
       <c r="B61" t="n">
         <v>80432</v>
@@ -7047,10 +7045,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R61" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7085,6 +7083,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7108,13 +7111,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121004521</v>
+        <v>102089929</v>
       </c>
       <c r="B62" t="n">
         <v>80432</v>
@@ -7143,19 +7146,17 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550494</v>
+        <v>550373</v>
       </c>
       <c r="R62" t="n">
-        <v>6993901</v>
+        <v>6994082</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7182,17 +7183,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7201,7 +7197,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7219,52 +7214,54 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102089008</v>
+        <v>121004521</v>
       </c>
       <c r="B63" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550570</v>
+        <v>550494</v>
       </c>
       <c r="R63" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7291,12 +7288,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7310,6 +7307,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7327,13 +7325,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102089938</v>
+        <v>102089008</v>
       </c>
       <c r="B64" t="n">
         <v>80461</v>
@@ -7369,10 +7367,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R64" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7407,6 +7405,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7430,16 +7433,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089013</v>
+        <v>102089938</v>
       </c>
       <c r="B65" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7447,21 +7450,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7472,10 +7475,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550570</v>
+        <v>550373</v>
       </c>
       <c r="R65" t="n">
-        <v>6994156</v>
+        <v>6994082</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7510,11 +7513,6 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7538,13 +7536,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102089935</v>
+        <v>102089013</v>
       </c>
       <c r="B66" t="n">
         <v>80467</v>
@@ -7580,10 +7578,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R66" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7618,6 +7616,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7641,16 +7644,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121004525</v>
+        <v>102089935</v>
       </c>
       <c r="B67" t="n">
-        <v>57141</v>
+        <v>80467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7658,42 +7661,35 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550502</v>
+        <v>550373</v>
       </c>
       <c r="R67" t="n">
-        <v>6993935</v>
+        <v>6994082</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7720,12 +7716,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7751,16 +7747,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134246389</v>
+        <v>121004525</v>
       </c>
       <c r="B68" t="n">
-        <v>58131</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7768,34 +7764,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103023</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550466</v>
+        <v>550502</v>
       </c>
       <c r="R68" t="n">
-        <v>6994147</v>
+        <v>6993935</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7822,12 +7826,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7842,27 +7846,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134246392</v>
+        <v>134246389</v>
       </c>
       <c r="B69" t="n">
-        <v>98219</v>
+        <v>58131</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7870,21 +7874,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219815</v>
+        <v>103023</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7894,13 +7898,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550548</v>
+        <v>550466</v>
       </c>
       <c r="R69" t="n">
-        <v>6994192</v>
+        <v>6994147</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7955,56 +7959,54 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102088784</v>
+        <v>134246392</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550571</v>
+        <v>550548</v>
       </c>
       <c r="R70" t="n">
-        <v>6994155</v>
+        <v>6994192</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8028,12 +8030,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8048,64 +8050,70 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102089119</v>
+        <v>135466568</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>99309</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550567</v>
+        <v>550481</v>
       </c>
       <c r="R71" t="n">
-        <v>6994155</v>
+        <v>6993999</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8132,12 +8140,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8146,6 +8154,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8163,13 +8172,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102089419</v>
+        <v>102088784</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8202,14 +8211,14 @@
       <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550554</v>
+        <v>550571</v>
       </c>
       <c r="R72" t="n">
-        <v>6994133</v>
+        <v>6994155</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8267,13 +8276,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102089819</v>
+        <v>102089119</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8310,10 +8319,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550446</v>
+        <v>550567</v>
       </c>
       <c r="R73" t="n">
-        <v>6994089</v>
+        <v>6994155</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8371,13 +8380,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121004332</v>
+        <v>102089419</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8406,20 +8415,18 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550310</v>
+        <v>550554</v>
       </c>
       <c r="R74" t="n">
-        <v>6994126</v>
+        <v>6994133</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8446,12 +8453,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8460,7 +8467,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8478,13 +8484,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121004405</v>
+        <v>102089819</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8513,20 +8519,18 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550404</v>
+        <v>550446</v>
       </c>
       <c r="R75" t="n">
-        <v>6994153</v>
+        <v>6994089</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8553,12 +8557,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8567,7 +8571,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8585,13 +8588,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121004422</v>
+        <v>121004332</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8630,10 +8633,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550395</v>
+        <v>550310</v>
       </c>
       <c r="R76" t="n">
-        <v>6994127</v>
+        <v>6994126</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8692,13 +8695,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004461</v>
+        <v>121004405</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8737,10 +8740,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550389</v>
+        <v>550404</v>
       </c>
       <c r="R77" t="n">
-        <v>6994063</v>
+        <v>6994153</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8799,13 +8802,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121004477</v>
+        <v>121004422</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8844,10 +8847,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550370</v>
+        <v>550395</v>
       </c>
       <c r="R78" t="n">
-        <v>6993853</v>
+        <v>6994127</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8906,13 +8909,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004505</v>
+        <v>121004461</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8951,10 +8954,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550496</v>
+        <v>550389</v>
       </c>
       <c r="R79" t="n">
-        <v>6993835</v>
+        <v>6994063</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9013,13 +9016,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004519</v>
+        <v>121004477</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9058,10 +9061,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550494</v>
+        <v>550370</v>
       </c>
       <c r="R80" t="n">
-        <v>6993901</v>
+        <v>6993853</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9096,11 +9099,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9125,13 +9123,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004558</v>
+        <v>121004505</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9170,10 +9168,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550516</v>
+        <v>550496</v>
       </c>
       <c r="R81" t="n">
-        <v>6994130</v>
+        <v>6993835</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9232,13 +9230,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004562</v>
+        <v>121004519</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9277,10 +9275,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550520</v>
+        <v>550494</v>
       </c>
       <c r="R82" t="n">
-        <v>6994154</v>
+        <v>6993901</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9315,6 +9313,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9339,13 +9342,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004565</v>
+        <v>121004558</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9384,10 +9387,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550469</v>
+        <v>550516</v>
       </c>
       <c r="R83" t="n">
-        <v>6994270</v>
+        <v>6994130</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9446,13 +9449,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126099534</v>
+        <v>121004562</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9487,14 +9490,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550463</v>
+        <v>550520</v>
       </c>
       <c r="R84" t="n">
-        <v>6994172</v>
+        <v>6994154</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9521,12 +9524,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9553,16 +9556,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134246388</v>
+        <v>121004565</v>
       </c>
       <c r="B85" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9588,19 +9591,23 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550414</v>
+        <v>550469</v>
       </c>
       <c r="R85" t="n">
-        <v>6994084</v>
+        <v>6994270</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9624,12 +9631,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9638,71 +9645,76 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134246393</v>
+        <v>126099534</v>
       </c>
       <c r="B86" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550548</v>
+        <v>550463</v>
       </c>
       <c r="R86" t="n">
-        <v>6994192</v>
+        <v>6994172</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9726,12 +9738,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9740,68 +9752,69 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134246406</v>
+        <v>134246388</v>
       </c>
       <c r="B87" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550277</v>
+        <v>550414</v>
       </c>
       <c r="R87" t="n">
-        <v>6994166</v>
+        <v>6994084</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9859,54 +9872,55 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
+          <t>https://artportalen.se/Sighting/134246388</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126099623</v>
+        <v>135466572</v>
       </c>
       <c r="B88" t="n">
-        <v>79085</v>
+        <v>98142</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>550481</v>
       </c>
       <c r="R88" t="n">
-        <v>6994133</v>
+        <v>6993999</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9933,12 +9947,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9965,38 +9979,38 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
+          <t>https://artportalen.se/Sighting/135466572</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134246390</v>
+        <v>134246393</v>
       </c>
       <c r="B89" t="n">
-        <v>79131</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10006,10 +10020,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550466</v>
+        <v>550548</v>
       </c>
       <c r="R89" t="n">
-        <v>6994147</v>
+        <v>6994192</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10067,16 +10081,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
+          <t>https://artportalen.se/Sighting/134246393</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102089933</v>
+        <v>134246406</v>
       </c>
       <c r="B90" t="n">
-        <v>80392</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,38 +10098,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550373</v>
+        <v>550277</v>
       </c>
       <c r="R90" t="n">
-        <v>6994082</v>
+        <v>6994166</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10139,12 +10152,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10159,16 +10172,327 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099623</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246390</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102089933</t>
         </is>
@@ -10265,6 +10589,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ93"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,32 +1321,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004536</v>
+        <v>135457711</v>
       </c>
       <c r="B8" t="n">
-        <v>81312</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550477</v>
+        <v>550504</v>
       </c>
       <c r="R8" t="n">
-        <v>6994042</v>
+        <v>6993854</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,13 +1421,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004536</t>
+          <t>https://artportalen.se/Sighting/135457711</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004550</v>
+        <v>121004536</v>
       </c>
       <c r="B9" t="n">
         <v>81312</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550508</v>
+        <v>550477</v>
       </c>
       <c r="R9" t="n">
-        <v>6994113</v>
+        <v>6994042</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1527,13 +1527,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004550</t>
+          <t>https://artportalen.se/Sighting/121004536</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126099520</v>
+        <v>121004550</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1567,14 +1567,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550419</v>
+        <v>550508</v>
       </c>
       <c r="R10" t="n">
-        <v>6994207</v>
+        <v>6994113</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,16 +1633,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099520</t>
+          <t>https://artportalen.se/Sighting/121004550</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102089224</v>
+        <v>126099520</v>
       </c>
       <c r="B11" t="n">
-        <v>83173</v>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,35 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550562</v>
+        <v>550419</v>
       </c>
       <c r="R11" t="n">
-        <v>6994152</v>
+        <v>6994207</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1705,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,6 +1721,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,54 +1739,52 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089224</t>
+          <t>https://artportalen.se/Sighting/126099520</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004416</v>
+        <v>102089224</v>
       </c>
       <c r="B12" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550398</v>
+        <v>550562</v>
       </c>
       <c r="R12" t="n">
-        <v>6994131</v>
+        <v>6994152</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1810,12 +1811,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1842,13 +1842,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004416</t>
+          <t>https://artportalen.se/Sighting/102089224</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004472</v>
+        <v>121004416</v>
       </c>
       <c r="B13" t="n">
         <v>92083</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550400</v>
+        <v>550398</v>
       </c>
       <c r="R13" t="n">
-        <v>6993983</v>
+        <v>6994131</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,38 +1948,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004472</t>
+          <t>https://artportalen.se/Sighting/121004416</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004362</v>
+        <v>121004472</v>
       </c>
       <c r="B14" t="n">
-        <v>90932</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550364</v>
+        <v>550400</v>
       </c>
       <c r="R14" t="n">
-        <v>6994169</v>
+        <v>6993983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,13 +2054,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004362</t>
+          <t>https://artportalen.se/Sighting/121004472</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004490</v>
+        <v>121004362</v>
       </c>
       <c r="B15" t="n">
         <v>90932</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550508</v>
+        <v>550364</v>
       </c>
       <c r="R15" t="n">
-        <v>6993803</v>
+        <v>6994169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004490</t>
+          <t>https://artportalen.se/Sighting/121004362</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004539</v>
+        <v>121004490</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550486</v>
+        <v>550508</v>
       </c>
       <c r="R16" t="n">
-        <v>6994062</v>
+        <v>6993803</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,16 +2266,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004539</t>
+          <t>https://artportalen.se/Sighting/121004490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62025591</v>
+        <v>121004539</v>
       </c>
       <c r="B17" t="n">
-        <v>91962</v>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,37 +2283,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550409</v>
+        <v>550486</v>
       </c>
       <c r="R17" t="n">
-        <v>6994048</v>
+        <v>6994062</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,12 +2340,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,43 +2354,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025591</t>
+          <t>https://artportalen.se/Sighting/121004539</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102089002</v>
+        <v>62025591</v>
       </c>
       <c r="B18" t="n">
-        <v>80433</v>
+        <v>91962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,38 +2389,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550570</v>
+        <v>550409</v>
       </c>
       <c r="R18" t="n">
-        <v>6994156</v>
+        <v>6994048</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2450,17 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2471,69 +2459,80 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089002</t>
+          <t>https://artportalen.se/Sighting/62025591</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103996059</v>
+        <v>102089002</v>
       </c>
       <c r="B19" t="n">
-        <v>96338</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550310</v>
+        <v>550570</v>
       </c>
       <c r="R19" t="n">
-        <v>6994183</v>
+        <v>6994156</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,22 +2556,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,11 +2577,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2597,67 +2586,60 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/102089002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004351</v>
+        <v>103996059</v>
       </c>
       <c r="B20" t="n">
-        <v>91831</v>
+        <v>96338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3242</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550358</v>
+        <v>550310</v>
       </c>
       <c r="R20" t="n">
-        <v>6994160</v>
+        <v>6994183</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,12 +2663,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,9 +2687,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2707,19 +2703,23 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004351</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004470</v>
+        <v>121004351</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550383</v>
+        <v>550358</v>
       </c>
       <c r="R21" t="n">
-        <v>6993994</v>
+        <v>6994160</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2795,11 +2795,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2824,16 +2819,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004470</t>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>62025592</v>
+        <v>121004470</v>
       </c>
       <c r="B22" t="n">
-        <v>93197</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,37 +2836,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550409</v>
+        <v>550383</v>
       </c>
       <c r="R22" t="n">
-        <v>6994048</v>
+        <v>6993994</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2895,12 +2893,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2909,43 +2912,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025592</t>
+          <t>https://artportalen.se/Sighting/121004470</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102089700</v>
+        <v>135457707</v>
       </c>
       <c r="B23" t="n">
-        <v>93197</v>
+        <v>93339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,35 +2947,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550476</v>
+        <v>550510</v>
       </c>
       <c r="R23" t="n">
-        <v>6994117</v>
+        <v>6993821</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3008,12 +3004,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,6 +3018,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3039,13 +3036,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089700</t>
+          <t>https://artportalen.se/Sighting/135457707</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103996072</v>
+        <v>62025592</v>
       </c>
       <c r="B24" t="n">
         <v>93197</v>
@@ -3076,14 +3073,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550481</v>
+        <v>550409</v>
       </c>
       <c r="R24" t="n">
-        <v>6994068</v>
+        <v>6994048</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3110,22 +3107,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,36 +3124,37 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996072</t>
+          <t>https://artportalen.se/Sighting/62025592</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103996080</v>
+        <v>102089700</v>
       </c>
       <c r="B25" t="n">
         <v>93197</v>
@@ -3195,19 +3183,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550485</v>
+        <v>550476</v>
       </c>
       <c r="R25" t="n">
-        <v>6994105</v>
+        <v>6994117</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,22 +3220,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,11 +3236,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3271,23 +3245,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996080</t>
+          <t>https://artportalen.se/Sighting/102089700</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004341</v>
+        <v>103996072</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3316,22 +3286,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550344</v>
+        <v>550481</v>
       </c>
       <c r="R26" t="n">
-        <v>6994160</v>
+        <v>6994068</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3355,12 +3322,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,9 +3346,13 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3381,19 +3362,23 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004341</t>
+          <t>https://artportalen.se/Sighting/103996072</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004394</v>
+        <v>103996080</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3422,22 +3407,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550381</v>
+        <v>550485</v>
       </c>
       <c r="R27" t="n">
-        <v>6994155</v>
+        <v>6994105</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,12 +3443,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,9 +3467,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3487,19 +3483,23 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004394</t>
+          <t>https://artportalen.se/Sighting/103996080</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004399</v>
+        <v>121004341</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550384</v>
+        <v>550344</v>
       </c>
       <c r="R28" t="n">
-        <v>6994151</v>
+        <v>6994160</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3599,13 +3599,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004399</t>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004430</v>
+        <v>121004394</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550422</v>
+        <v>550381</v>
       </c>
       <c r="R29" t="n">
-        <v>6994093</v>
+        <v>6994155</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3705,13 +3705,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004430</t>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004475</v>
+        <v>121004399</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550385</v>
+        <v>550384</v>
       </c>
       <c r="R30" t="n">
-        <v>6993920</v>
+        <v>6994151</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3811,13 +3811,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004475</t>
+          <t>https://artportalen.se/Sighting/121004399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004484</v>
+        <v>121004430</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550427</v>
+        <v>550422</v>
       </c>
       <c r="R31" t="n">
-        <v>6993867</v>
+        <v>6994093</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,13 +3917,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004484</t>
+          <t>https://artportalen.se/Sighting/121004430</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004500</v>
+        <v>121004475</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550496</v>
+        <v>550385</v>
       </c>
       <c r="R32" t="n">
-        <v>6993817</v>
+        <v>6993920</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4023,13 +4023,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004500</t>
+          <t>https://artportalen.se/Sighting/121004475</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004509</v>
+        <v>121004484</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550476</v>
+        <v>550427</v>
       </c>
       <c r="R33" t="n">
-        <v>6993841</v>
+        <v>6993867</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,13 +4129,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004509</t>
+          <t>https://artportalen.se/Sighting/121004484</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004524</v>
+        <v>121004500</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550502</v>
+        <v>550496</v>
       </c>
       <c r="R34" t="n">
-        <v>6993935</v>
+        <v>6993817</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,13 +4235,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004524</t>
+          <t>https://artportalen.se/Sighting/121004500</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004537</v>
+        <v>121004509</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550477</v>
+        <v>550476</v>
       </c>
       <c r="R35" t="n">
-        <v>6994042</v>
+        <v>6993841</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4341,13 +4341,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004537</t>
+          <t>https://artportalen.se/Sighting/121004509</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004540</v>
+        <v>121004524</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550505</v>
+        <v>550502</v>
       </c>
       <c r="R36" t="n">
-        <v>6994074</v>
+        <v>6993935</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4447,13 +4447,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004540</t>
+          <t>https://artportalen.se/Sighting/121004524</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004541</v>
+        <v>121004537</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550528</v>
+        <v>550477</v>
       </c>
       <c r="R37" t="n">
-        <v>6994067</v>
+        <v>6994042</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4553,13 +4553,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004541</t>
+          <t>https://artportalen.se/Sighting/121004537</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004547</v>
+        <v>121004540</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550493</v>
+        <v>550505</v>
       </c>
       <c r="R38" t="n">
-        <v>6994078</v>
+        <v>6994074</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4659,16 +4659,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004547</t>
+          <t>https://artportalen.se/Sighting/121004540</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134246391</v>
+        <v>121004541</v>
       </c>
       <c r="B39" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,19 +4694,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550317</v>
+        <v>550528</v>
       </c>
       <c r="R39" t="n">
-        <v>6994117</v>
+        <v>6994067</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4730,12 +4733,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,55 +4747,56 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/121004541</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004494</v>
+        <v>121004547</v>
       </c>
       <c r="B40" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4805,10 +4809,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550515</v>
+        <v>550493</v>
       </c>
       <c r="R40" t="n">
-        <v>6993816</v>
+        <v>6994078</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4867,57 +4871,54 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004494</t>
+          <t>https://artportalen.se/Sighting/121004547</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004545</v>
+        <v>134246391</v>
       </c>
       <c r="B41" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550493</v>
+        <v>550317</v>
       </c>
       <c r="R41" t="n">
-        <v>6994078</v>
+        <v>6994117</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4941,12 +4942,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,34 +4956,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004545</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135457522</v>
+        <v>121004494</v>
       </c>
       <c r="B42" t="n">
-        <v>93349</v>
+        <v>93201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550478</v>
+        <v>550515</v>
       </c>
       <c r="R42" t="n">
-        <v>6993873</v>
+        <v>6993816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,38 +5079,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457522</t>
+          <t>https://artportalen.se/Sighting/121004494</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004409</v>
+        <v>121004545</v>
       </c>
       <c r="B43" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550413</v>
+        <v>550493</v>
       </c>
       <c r="R43" t="n">
-        <v>6994137</v>
+        <v>6994078</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5185,16 +5185,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/121004545</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102089839</v>
+        <v>135457522</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>93351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5202,38 +5202,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550410</v>
+        <v>550478</v>
       </c>
       <c r="R44" t="n">
-        <v>6994101</v>
+        <v>6993873</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5257,12 +5259,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,6 +5273,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5288,38 +5291,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004337</v>
+        <v>121004409</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550319</v>
+        <v>550413</v>
       </c>
       <c r="R45" t="n">
-        <v>6994143</v>
+        <v>6994137</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5370,11 +5373,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5399,38 +5397,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004358</v>
+        <v>135457649</v>
       </c>
       <c r="B46" t="n">
-        <v>79327</v>
+        <v>89292</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5443,10 +5441,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550362</v>
+        <v>550447</v>
       </c>
       <c r="R46" t="n">
-        <v>6994156</v>
+        <v>6993828</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5473,12 +5471,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5505,13 +5503,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/135457649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004395</v>
+        <v>102089839</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5540,19 +5538,17 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550381</v>
+        <v>550410</v>
       </c>
       <c r="R47" t="n">
-        <v>6994155</v>
+        <v>6994101</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,12 +5575,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,7 +5589,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5611,13 +5606,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004439</v>
+        <v>121004337</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5655,10 +5650,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550405</v>
+        <v>550319</v>
       </c>
       <c r="R48" t="n">
-        <v>6994090</v>
+        <v>6994143</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5695,7 +5690,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,13 +5717,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004450</v>
+        <v>121004358</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5766,10 +5761,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550379</v>
+        <v>550362</v>
       </c>
       <c r="R49" t="n">
-        <v>6994086</v>
+        <v>6994156</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5828,13 +5823,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004511</v>
+        <v>121004395</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550470</v>
+        <v>550381</v>
       </c>
       <c r="R50" t="n">
-        <v>6993852</v>
+        <v>6994155</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5910,11 +5905,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5939,13 +5929,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004515</v>
+        <v>121004439</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5983,10 +5973,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550464</v>
+        <v>550405</v>
       </c>
       <c r="R51" t="n">
-        <v>6993901</v>
+        <v>6994090</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6021,6 +6011,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6045,13 +6040,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126099630</v>
+        <v>121004450</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6085,14 +6080,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550494</v>
+        <v>550379</v>
       </c>
       <c r="R52" t="n">
-        <v>6994148</v>
+        <v>6994086</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6119,17 +6114,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6156,16 +6146,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246394</v>
+        <v>121004511</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6191,19 +6181,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550512</v>
+        <v>550470</v>
       </c>
       <c r="R53" t="n">
-        <v>6994236</v>
+        <v>6993852</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6227,12 +6220,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6241,33 +6239,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134246395</v>
+        <v>121004515</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6293,19 +6292,22 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550292</v>
+        <v>550464</v>
       </c>
       <c r="R54" t="n">
-        <v>6994150</v>
+        <v>6993901</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6329,12 +6331,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6343,69 +6345,72 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102089806</v>
+        <v>126099630</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R55" t="n">
-        <v>6994094</v>
+        <v>6994148</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6432,12 +6437,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,6 +6456,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6463,57 +6474,54 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004349</v>
+        <v>134246394</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550358</v>
+        <v>550512</v>
       </c>
       <c r="R56" t="n">
-        <v>6994160</v>
+        <v>6994236</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6537,12 +6545,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6551,75 +6559,71 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004374</v>
+        <v>134246395</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550369</v>
+        <v>550292</v>
       </c>
       <c r="R57" t="n">
-        <v>6994167</v>
+        <v>6994150</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6643,12 +6647,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6657,31 +6661,30 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004533</v>
+        <v>102089806</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6710,19 +6713,17 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550456</v>
+        <v>550469</v>
       </c>
       <c r="R58" t="n">
-        <v>6993982</v>
+        <v>6994094</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6749,17 +6750,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,7 +6764,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6786,13 +6781,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126099591</v>
+        <v>121004349</v>
       </c>
       <c r="B59" t="n">
         <v>79946</v>
@@ -6826,14 +6821,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550464</v>
+        <v>550358</v>
       </c>
       <c r="R59" t="n">
-        <v>6994104</v>
+        <v>6994160</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6860,12 +6855,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6892,38 +6887,38 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126099553</v>
+        <v>121004374</v>
       </c>
       <c r="B60" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6932,14 +6927,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550465</v>
+        <v>550369</v>
       </c>
       <c r="R60" t="n">
-        <v>6994163</v>
+        <v>6994167</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6966,17 +6961,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,16 +6993,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102088995</v>
+        <v>121004533</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7020,35 +7010,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550570</v>
+        <v>550456</v>
       </c>
       <c r="R61" t="n">
-        <v>6994156</v>
+        <v>6993982</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7075,17 +7067,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7094,6 +7086,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7111,16 +7104,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102089929</v>
+        <v>126099591</v>
       </c>
       <c r="B62" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,35 +7121,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550373</v>
+        <v>550464</v>
       </c>
       <c r="R62" t="n">
-        <v>6994082</v>
+        <v>6994104</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7183,12 +7178,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7197,6 +7192,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7214,38 +7210,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004521</v>
+        <v>126099553</v>
       </c>
       <c r="B63" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7254,14 +7250,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550494</v>
+        <v>550465</v>
       </c>
       <c r="R63" t="n">
-        <v>6993901</v>
+        <v>6994163</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7288,17 +7284,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7325,38 +7321,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102089008</v>
+        <v>102088995</v>
       </c>
       <c r="B64" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7433,38 +7429,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089938</v>
+        <v>102089929</v>
       </c>
       <c r="B65" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7536,52 +7532,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102089013</v>
+        <v>121004521</v>
       </c>
       <c r="B66" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550570</v>
+        <v>550494</v>
       </c>
       <c r="R66" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7608,12 +7606,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7627,6 +7625,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7644,16 +7643,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089935</v>
+        <v>102089008</v>
       </c>
       <c r="B67" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7661,21 +7660,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7685,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R67" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7724,6 +7723,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7747,16 +7751,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121004525</v>
+        <v>102089938</v>
       </c>
       <c r="B68" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7764,42 +7768,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550502</v>
+        <v>550373</v>
       </c>
       <c r="R68" t="n">
-        <v>6993935</v>
+        <v>6994082</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7826,12 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,16 +7854,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134246389</v>
+        <v>102089013</v>
       </c>
       <c r="B69" t="n">
-        <v>58131</v>
+        <v>80467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7874,34 +7871,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103023</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550466</v>
+        <v>550570</v>
       </c>
       <c r="R69" t="n">
-        <v>6994147</v>
+        <v>6994156</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7928,12 +7926,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,27 +7951,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134246392</v>
+        <v>102089935</v>
       </c>
       <c r="B70" t="n">
-        <v>98219</v>
+        <v>80467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7976,37 +7979,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219815</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550548</v>
+        <v>550373</v>
       </c>
       <c r="R70" t="n">
-        <v>6994192</v>
+        <v>6994082</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8030,12 +8034,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8050,27 +8054,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135466568</v>
+        <v>121004525</v>
       </c>
       <c r="B71" t="n">
-        <v>99309</v>
+        <v>57141</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,42 +8082,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550481</v>
+        <v>550502</v>
       </c>
       <c r="R71" t="n">
-        <v>6993999</v>
+        <v>6993935</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8140,12 +8144,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8154,7 +8158,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8172,53 +8175,51 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466568</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102088784</v>
+        <v>134246389</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>58131</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550571</v>
+        <v>550466</v>
       </c>
       <c r="R72" t="n">
-        <v>6994155</v>
+        <v>6994147</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8245,12 +8246,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8265,67 +8266,65 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102089119</v>
+        <v>134246392</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550567</v>
+        <v>550548</v>
       </c>
       <c r="R73" t="n">
-        <v>6994155</v>
+        <v>6994192</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8349,12 +8348,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8369,64 +8368,70 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102089419</v>
+        <v>135466568</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>99311</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550554</v>
+        <v>550481</v>
       </c>
       <c r="R74" t="n">
-        <v>6994133</v>
+        <v>6993999</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8453,12 +8458,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8467,6 +8472,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8484,13 +8490,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102089819</v>
+        <v>102088784</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8523,14 +8529,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550446</v>
+        <v>550571</v>
       </c>
       <c r="R75" t="n">
-        <v>6994089</v>
+        <v>6994155</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8588,13 +8594,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121004332</v>
+        <v>102089119</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8623,20 +8629,18 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550310</v>
+        <v>550567</v>
       </c>
       <c r="R76" t="n">
-        <v>6994126</v>
+        <v>6994155</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8663,12 +8667,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8677,7 +8681,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8695,13 +8698,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004405</v>
+        <v>102089419</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8730,20 +8733,18 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550404</v>
+        <v>550554</v>
       </c>
       <c r="R77" t="n">
-        <v>6994153</v>
+        <v>6994133</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8770,12 +8771,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,7 +8785,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8802,13 +8802,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121004422</v>
+        <v>102089819</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8837,20 +8837,18 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550395</v>
+        <v>550446</v>
       </c>
       <c r="R78" t="n">
-        <v>6994127</v>
+        <v>6994089</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8877,12 +8875,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8891,7 +8889,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8909,13 +8906,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004461</v>
+        <v>121004332</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8954,10 +8951,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550389</v>
+        <v>550310</v>
       </c>
       <c r="R79" t="n">
-        <v>6994063</v>
+        <v>6994126</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9016,13 +9013,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004477</v>
+        <v>121004405</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9061,10 +9058,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550370</v>
+        <v>550404</v>
       </c>
       <c r="R80" t="n">
-        <v>6993853</v>
+        <v>6994153</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9123,13 +9120,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004505</v>
+        <v>121004422</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9168,10 +9165,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550496</v>
+        <v>550395</v>
       </c>
       <c r="R81" t="n">
-        <v>6993835</v>
+        <v>6994127</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9230,13 +9227,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004519</v>
+        <v>121004461</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9275,10 +9272,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550494</v>
+        <v>550389</v>
       </c>
       <c r="R82" t="n">
-        <v>6993901</v>
+        <v>6994063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9313,11 +9310,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9342,13 +9334,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004558</v>
+        <v>121004477</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9387,10 +9379,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550516</v>
+        <v>550370</v>
       </c>
       <c r="R83" t="n">
-        <v>6994130</v>
+        <v>6993853</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9449,13 +9441,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004562</v>
+        <v>121004505</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9494,10 +9486,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550520</v>
+        <v>550496</v>
       </c>
       <c r="R84" t="n">
-        <v>6994154</v>
+        <v>6993835</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9556,13 +9548,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004565</v>
+        <v>121004519</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9601,10 +9593,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R85" t="n">
-        <v>6994270</v>
+        <v>6993901</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9639,6 +9631,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9663,13 +9660,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126099534</v>
+        <v>121004558</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9704,14 +9701,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550463</v>
+        <v>550516</v>
       </c>
       <c r="R86" t="n">
-        <v>6994172</v>
+        <v>6994130</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9738,12 +9735,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9770,16 +9767,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134246388</v>
+        <v>121004562</v>
       </c>
       <c r="B87" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9805,19 +9802,23 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550414</v>
+        <v>550520</v>
       </c>
       <c r="R87" t="n">
-        <v>6994084</v>
+        <v>6994154</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9841,12 +9842,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9855,55 +9856,56 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135466572</v>
+        <v>121004565</v>
       </c>
       <c r="B88" t="n">
-        <v>98142</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9917,10 +9919,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550481</v>
+        <v>550469</v>
       </c>
       <c r="R88" t="n">
-        <v>6993999</v>
+        <v>6994270</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9947,12 +9949,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9979,54 +9981,58 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466572</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134246393</v>
+        <v>126099534</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550548</v>
+        <v>550463</v>
       </c>
       <c r="R89" t="n">
-        <v>6994192</v>
+        <v>6994172</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10050,12 +10056,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10064,68 +10070,69 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246406</v>
+        <v>134246388</v>
       </c>
       <c r="B90" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550277</v>
+        <v>550414</v>
       </c>
       <c r="R90" t="n">
-        <v>6994166</v>
+        <v>6994084</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10183,54 +10190,59 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
+          <t>https://artportalen.se/Sighting/134246388</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126099623</v>
+        <v>135457589</v>
       </c>
       <c r="B91" t="n">
-        <v>79085</v>
+        <v>99276</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550481</v>
+        <v>550445</v>
       </c>
       <c r="R91" t="n">
-        <v>6994133</v>
+        <v>6993808</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10257,12 +10269,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönpyrola.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10289,54 +10306,62 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
+          <t>https://artportalen.se/Sighting/135457589</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134246390</v>
+        <v>135457681</v>
       </c>
       <c r="B92" t="n">
-        <v>79131</v>
+        <v>99276</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550466</v>
+        <v>550350</v>
       </c>
       <c r="R92" t="n">
-        <v>6994147</v>
+        <v>6993905</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10360,12 +10385,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10374,69 +10399,77 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
+          <t>https://artportalen.se/Sighting/135457681</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>102089933</v>
+        <v>135457684</v>
       </c>
       <c r="B93" t="n">
-        <v>80392</v>
+        <v>99276</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550373</v>
+        <v>550343</v>
       </c>
       <c r="R93" t="n">
-        <v>6994082</v>
+        <v>6993884</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10463,12 +10496,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10477,6 +10510,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10493,6 +10527,966 @@
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457684</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135457690</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>550353</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6993851</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457690</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135457698</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>550455</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6994009</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457698</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135457602</v>
+      </c>
+      <c r="B96" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>550445</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6993808</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Tillsammans med knärot.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457602</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135466572</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98144</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6993999</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466572</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134246393</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>550548</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6994192</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246393</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099623</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246390</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B102" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102089933</t>
         </is>
@@ -10592,6 +11586,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,32 +1321,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135457711</v>
+        <v>121004536</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550504</v>
+        <v>550477</v>
       </c>
       <c r="R8" t="n">
-        <v>6993854</v>
+        <v>6994042</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,13 +1421,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457711</t>
+          <t>https://artportalen.se/Sighting/121004536</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004536</v>
+        <v>121004550</v>
       </c>
       <c r="B9" t="n">
         <v>81312</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550477</v>
+        <v>550508</v>
       </c>
       <c r="R9" t="n">
-        <v>6994042</v>
+        <v>6994113</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1527,13 +1527,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004536</t>
+          <t>https://artportalen.se/Sighting/121004550</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004550</v>
+        <v>126099520</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1567,14 +1567,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550508</v>
+        <v>550419</v>
       </c>
       <c r="R10" t="n">
-        <v>6994113</v>
+        <v>6994207</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,16 +1633,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004550</t>
+          <t>https://artportalen.se/Sighting/126099520</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126099520</v>
+        <v>102089224</v>
       </c>
       <c r="B11" t="n">
-        <v>81312</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,37 +1650,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550419</v>
+        <v>550562</v>
       </c>
       <c r="R11" t="n">
-        <v>6994207</v>
+        <v>6994152</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1707,12 +1705,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,7 +1719,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1739,52 +1736,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099520</t>
+          <t>https://artportalen.se/Sighting/102089224</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102089224</v>
+        <v>121004416</v>
       </c>
       <c r="B12" t="n">
-        <v>83173</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550562</v>
+        <v>550398</v>
       </c>
       <c r="R12" t="n">
-        <v>6994152</v>
+        <v>6994131</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,12 +1810,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,6 +1824,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1842,13 +1842,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089224</t>
+          <t>https://artportalen.se/Sighting/121004416</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004416</v>
+        <v>121004472</v>
       </c>
       <c r="B13" t="n">
         <v>92083</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550398</v>
+        <v>550400</v>
       </c>
       <c r="R13" t="n">
-        <v>6994131</v>
+        <v>6993983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,38 +1948,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004416</t>
+          <t>https://artportalen.se/Sighting/121004472</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004472</v>
+        <v>121004362</v>
       </c>
       <c r="B14" t="n">
-        <v>92083</v>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550400</v>
+        <v>550364</v>
       </c>
       <c r="R14" t="n">
-        <v>6993983</v>
+        <v>6994169</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,13 +2054,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004472</t>
+          <t>https://artportalen.se/Sighting/121004362</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004362</v>
+        <v>121004490</v>
       </c>
       <c r="B15" t="n">
         <v>90932</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550364</v>
+        <v>550508</v>
       </c>
       <c r="R15" t="n">
-        <v>6994169</v>
+        <v>6993803</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004362</t>
+          <t>https://artportalen.se/Sighting/121004490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004490</v>
+        <v>121004539</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550508</v>
+        <v>550486</v>
       </c>
       <c r="R16" t="n">
-        <v>6993803</v>
+        <v>6994062</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,16 +2266,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004490</t>
+          <t>https://artportalen.se/Sighting/121004539</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004539</v>
+        <v>62025591</v>
       </c>
       <c r="B17" t="n">
-        <v>90932</v>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,40 +2283,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550486</v>
+        <v>550409</v>
       </c>
       <c r="R17" t="n">
-        <v>6994062</v>
+        <v>6994048</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,34 +2351,43 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004539</t>
+          <t>https://artportalen.se/Sighting/62025591</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62025591</v>
+        <v>102089002</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2389,37 +2395,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550409</v>
+        <v>550570</v>
       </c>
       <c r="R18" t="n">
-        <v>6994048</v>
+        <v>6994156</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,12 +2450,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,80 +2471,69 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025591</t>
+          <t>https://artportalen.se/Sighting/102089002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102089002</v>
+        <v>103996059</v>
       </c>
       <c r="B19" t="n">
-        <v>80433</v>
+        <v>96338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550570</v>
+        <v>550310</v>
       </c>
       <c r="R19" t="n">
-        <v>6994156</v>
+        <v>6994183</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2556,17 +2557,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2577,6 +2583,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2586,60 +2597,67 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089002</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103996059</v>
+        <v>121004351</v>
       </c>
       <c r="B20" t="n">
-        <v>96338</v>
+        <v>91831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550310</v>
+        <v>550358</v>
       </c>
       <c r="R20" t="n">
-        <v>6994183</v>
+        <v>6994160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2663,22 +2681,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,13 +2695,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2703,23 +2707,19 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004351</v>
+        <v>121004470</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550358</v>
+        <v>550383</v>
       </c>
       <c r="R21" t="n">
-        <v>6994160</v>
+        <v>6993994</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2795,6 +2795,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2819,16 +2824,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004351</t>
+          <t>https://artportalen.se/Sighting/121004470</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004470</v>
+        <v>62025592</v>
       </c>
       <c r="B22" t="n">
-        <v>91831</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,40 +2841,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550383</v>
+        <v>550409</v>
       </c>
       <c r="R22" t="n">
-        <v>6993994</v>
+        <v>6994048</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2893,17 +2895,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,34 +2909,43 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004470</t>
+          <t>https://artportalen.se/Sighting/62025592</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135457707</v>
+        <v>102089700</v>
       </c>
       <c r="B23" t="n">
-        <v>93339</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,37 +2953,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550510</v>
+        <v>550476</v>
       </c>
       <c r="R23" t="n">
-        <v>6993821</v>
+        <v>6994117</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3004,12 +3008,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,7 +3022,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3036,13 +3039,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457707</t>
+          <t>https://artportalen.se/Sighting/102089700</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62025592</v>
+        <v>103996072</v>
       </c>
       <c r="B24" t="n">
         <v>93197</v>
@@ -3073,14 +3076,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550409</v>
+        <v>550481</v>
       </c>
       <c r="R24" t="n">
-        <v>6994048</v>
+        <v>6994068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3107,12 +3110,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,37 +3137,36 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025592</t>
+          <t>https://artportalen.se/Sighting/103996072</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102089700</v>
+        <v>103996080</v>
       </c>
       <c r="B25" t="n">
         <v>93197</v>
@@ -3183,20 +3195,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550476</v>
+        <v>550485</v>
       </c>
       <c r="R25" t="n">
-        <v>6994117</v>
+        <v>6994105</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3220,12 +3231,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,6 +3257,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3245,19 +3271,23 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089700</t>
+          <t>https://artportalen.se/Sighting/103996080</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103996072</v>
+        <v>121004341</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3286,19 +3316,22 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550481</v>
+        <v>550344</v>
       </c>
       <c r="R26" t="n">
-        <v>6994068</v>
+        <v>6994160</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3322,22 +3355,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3346,13 +3369,9 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3362,23 +3381,19 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996072</t>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103996080</v>
+        <v>121004394</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3407,19 +3422,22 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550485</v>
+        <v>550381</v>
       </c>
       <c r="R27" t="n">
-        <v>6994105</v>
+        <v>6994155</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3443,22 +3461,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,13 +3475,9 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3483,23 +3487,19 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996080</t>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004341</v>
+        <v>121004399</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550344</v>
+        <v>550384</v>
       </c>
       <c r="R28" t="n">
-        <v>6994160</v>
+        <v>6994151</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3599,13 +3599,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004341</t>
+          <t>https://artportalen.se/Sighting/121004399</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004394</v>
+        <v>121004430</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550381</v>
+        <v>550422</v>
       </c>
       <c r="R29" t="n">
-        <v>6994155</v>
+        <v>6994093</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3705,13 +3705,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004394</t>
+          <t>https://artportalen.se/Sighting/121004430</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004399</v>
+        <v>121004475</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550384</v>
+        <v>550385</v>
       </c>
       <c r="R30" t="n">
-        <v>6994151</v>
+        <v>6993920</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3811,13 +3811,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004399</t>
+          <t>https://artportalen.se/Sighting/121004475</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004430</v>
+        <v>121004484</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550422</v>
+        <v>550427</v>
       </c>
       <c r="R31" t="n">
-        <v>6994093</v>
+        <v>6993867</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,13 +3917,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004430</t>
+          <t>https://artportalen.se/Sighting/121004484</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004475</v>
+        <v>121004500</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550385</v>
+        <v>550496</v>
       </c>
       <c r="R32" t="n">
-        <v>6993920</v>
+        <v>6993817</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4023,13 +4023,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004475</t>
+          <t>https://artportalen.se/Sighting/121004500</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004484</v>
+        <v>121004509</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550427</v>
+        <v>550476</v>
       </c>
       <c r="R33" t="n">
-        <v>6993867</v>
+        <v>6993841</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,13 +4129,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004484</t>
+          <t>https://artportalen.se/Sighting/121004509</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004500</v>
+        <v>121004524</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550496</v>
+        <v>550502</v>
       </c>
       <c r="R34" t="n">
-        <v>6993817</v>
+        <v>6993935</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,13 +4235,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004500</t>
+          <t>https://artportalen.se/Sighting/121004524</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004509</v>
+        <v>121004537</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550476</v>
+        <v>550477</v>
       </c>
       <c r="R35" t="n">
-        <v>6993841</v>
+        <v>6994042</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4341,13 +4341,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004509</t>
+          <t>https://artportalen.se/Sighting/121004537</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004524</v>
+        <v>121004540</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550502</v>
+        <v>550505</v>
       </c>
       <c r="R36" t="n">
-        <v>6993935</v>
+        <v>6994074</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4447,13 +4447,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004524</t>
+          <t>https://artportalen.se/Sighting/121004540</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004537</v>
+        <v>121004541</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550477</v>
+        <v>550528</v>
       </c>
       <c r="R37" t="n">
-        <v>6994042</v>
+        <v>6994067</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4553,13 +4553,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004537</t>
+          <t>https://artportalen.se/Sighting/121004541</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004540</v>
+        <v>121004547</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550505</v>
+        <v>550493</v>
       </c>
       <c r="R38" t="n">
-        <v>6994074</v>
+        <v>6994078</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4659,16 +4659,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004540</t>
+          <t>https://artportalen.se/Sighting/121004547</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004541</v>
+        <v>134246391</v>
       </c>
       <c r="B39" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,22 +4694,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550528</v>
+        <v>550317</v>
       </c>
       <c r="R39" t="n">
-        <v>6994067</v>
+        <v>6994117</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4733,12 +4730,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4747,56 +4744,55 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004541</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004547</v>
+        <v>121004494</v>
       </c>
       <c r="B40" t="n">
-        <v>93197</v>
+        <v>93201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4809,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550493</v>
+        <v>550515</v>
       </c>
       <c r="R40" t="n">
-        <v>6994078</v>
+        <v>6993816</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4871,54 +4867,57 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004547</t>
+          <t>https://artportalen.se/Sighting/121004494</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134246391</v>
+        <v>121004545</v>
       </c>
       <c r="B41" t="n">
-        <v>93271</v>
+        <v>93201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550317</v>
+        <v>550493</v>
       </c>
       <c r="R41" t="n">
-        <v>6994117</v>
+        <v>6994078</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,12 +4941,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4956,33 +4955,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/121004545</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004494</v>
+        <v>135457522</v>
       </c>
       <c r="B42" t="n">
-        <v>93201</v>
+        <v>93351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550515</v>
+        <v>550478</v>
       </c>
       <c r="R42" t="n">
-        <v>6993816</v>
+        <v>6993873</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,38 +5079,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004494</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004545</v>
+        <v>121004409</v>
       </c>
       <c r="B43" t="n">
-        <v>93201</v>
+        <v>93209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550493</v>
+        <v>550413</v>
       </c>
       <c r="R43" t="n">
-        <v>6994078</v>
+        <v>6994137</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5185,16 +5185,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004545</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135457522</v>
+        <v>102089839</v>
       </c>
       <c r="B44" t="n">
-        <v>93351</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5202,40 +5202,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550478</v>
+        <v>550410</v>
       </c>
       <c r="R44" t="n">
-        <v>6993873</v>
+        <v>6994101</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5259,12 +5257,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5273,7 +5271,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5291,38 +5288,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457522</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004409</v>
+        <v>121004337</v>
       </c>
       <c r="B45" t="n">
-        <v>93209</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550413</v>
+        <v>550319</v>
       </c>
       <c r="R45" t="n">
-        <v>6994137</v>
+        <v>6994143</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5373,6 +5370,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5397,38 +5399,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135457649</v>
+        <v>121004358</v>
       </c>
       <c r="B46" t="n">
-        <v>89292</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5441,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550447</v>
+        <v>550362</v>
       </c>
       <c r="R46" t="n">
-        <v>6993828</v>
+        <v>6994156</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5471,12 +5473,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5503,13 +5505,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457649</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102089839</v>
+        <v>121004395</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5538,17 +5540,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550410</v>
+        <v>550381</v>
       </c>
       <c r="R47" t="n">
-        <v>6994101</v>
+        <v>6994155</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5575,12 +5579,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5589,6 +5593,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5606,13 +5611,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004337</v>
+        <v>121004439</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5650,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550319</v>
+        <v>550405</v>
       </c>
       <c r="R48" t="n">
-        <v>6994143</v>
+        <v>6994090</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5690,7 +5695,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5717,13 +5722,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004358</v>
+        <v>121004450</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5761,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550362</v>
+        <v>550379</v>
       </c>
       <c r="R49" t="n">
-        <v>6994156</v>
+        <v>6994086</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5823,13 +5828,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004395</v>
+        <v>121004511</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5867,10 +5872,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550381</v>
+        <v>550470</v>
       </c>
       <c r="R50" t="n">
-        <v>6994155</v>
+        <v>6993852</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5905,6 +5910,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5929,13 +5939,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004439</v>
+        <v>121004515</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5973,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550405</v>
+        <v>550464</v>
       </c>
       <c r="R51" t="n">
-        <v>6994090</v>
+        <v>6993901</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6011,11 +6021,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6040,13 +6045,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004450</v>
+        <v>126099630</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6080,14 +6085,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550379</v>
+        <v>550494</v>
       </c>
       <c r="R52" t="n">
-        <v>6994086</v>
+        <v>6994148</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,12 +6119,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6146,16 +6156,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004511</v>
+        <v>134246394</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6181,22 +6191,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550470</v>
+        <v>550512</v>
       </c>
       <c r="R53" t="n">
-        <v>6993852</v>
+        <v>6994236</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6220,17 +6227,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,34 +6241,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121004515</v>
+        <v>134246395</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6292,22 +6293,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550464</v>
+        <v>550292</v>
       </c>
       <c r="R54" t="n">
-        <v>6993901</v>
+        <v>6994150</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6331,12 +6329,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6345,72 +6343,69 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126099630</v>
+        <v>102089806</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550494</v>
+        <v>550469</v>
       </c>
       <c r="R55" t="n">
-        <v>6994148</v>
+        <v>6994094</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6437,17 +6432,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6446,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6474,54 +6463,57 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134246394</v>
+        <v>121004349</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550512</v>
+        <v>550358</v>
       </c>
       <c r="R56" t="n">
-        <v>6994236</v>
+        <v>6994160</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6545,12 +6537,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6559,71 +6551,75 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134246395</v>
+        <v>121004374</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550292</v>
+        <v>550369</v>
       </c>
       <c r="R57" t="n">
-        <v>6994150</v>
+        <v>6994167</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,12 +6643,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6661,30 +6657,31 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102089806</v>
+        <v>121004533</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6713,17 +6710,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550469</v>
+        <v>550456</v>
       </c>
       <c r="R58" t="n">
-        <v>6994094</v>
+        <v>6993982</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6750,12 +6749,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6764,6 +6768,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6781,13 +6786,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004349</v>
+        <v>126099591</v>
       </c>
       <c r="B59" t="n">
         <v>79946</v>
@@ -6821,14 +6826,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550358</v>
+        <v>550464</v>
       </c>
       <c r="R59" t="n">
-        <v>6994160</v>
+        <v>6994104</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6855,12 +6860,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6887,38 +6892,38 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004374</v>
+        <v>126099553</v>
       </c>
       <c r="B60" t="n">
-        <v>79946</v>
+        <v>80336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6927,14 +6932,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550369</v>
+        <v>550465</v>
       </c>
       <c r="R60" t="n">
-        <v>6994167</v>
+        <v>6994163</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6961,12 +6966,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,16 +7003,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004533</v>
+        <v>102088995</v>
       </c>
       <c r="B61" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7010,37 +7020,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550456</v>
+        <v>550570</v>
       </c>
       <c r="R61" t="n">
-        <v>6993982</v>
+        <v>6994156</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7067,17 +7075,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På kolad högstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7086,7 +7094,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7104,16 +7111,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126099591</v>
+        <v>102089929</v>
       </c>
       <c r="B62" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7121,37 +7128,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550464</v>
+        <v>550373</v>
       </c>
       <c r="R62" t="n">
-        <v>6994104</v>
+        <v>6994082</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7178,12 +7183,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7192,7 +7197,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7210,38 +7214,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126099553</v>
+        <v>121004521</v>
       </c>
       <c r="B63" t="n">
-        <v>80336</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,14 +7254,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550465</v>
+        <v>550494</v>
       </c>
       <c r="R63" t="n">
-        <v>6994163</v>
+        <v>6993901</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7284,17 +7288,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7321,38 +7325,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102088995</v>
+        <v>102089008</v>
       </c>
       <c r="B64" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7429,38 +7433,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089929</v>
+        <v>102089938</v>
       </c>
       <c r="B65" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7532,54 +7536,52 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121004521</v>
+        <v>102089013</v>
       </c>
       <c r="B66" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550494</v>
+        <v>550570</v>
       </c>
       <c r="R66" t="n">
-        <v>6993901</v>
+        <v>6994156</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7606,12 +7608,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7625,7 +7627,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7643,16 +7644,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089008</v>
+        <v>102089935</v>
       </c>
       <c r="B67" t="n">
-        <v>80461</v>
+        <v>80467</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7660,21 +7661,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7685,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550570</v>
+        <v>550373</v>
       </c>
       <c r="R67" t="n">
-        <v>6994156</v>
+        <v>6994082</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7723,11 +7724,6 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7751,16 +7747,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102089938</v>
+        <v>121004525</v>
       </c>
       <c r="B68" t="n">
-        <v>80461</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7768,35 +7764,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550373</v>
+        <v>550502</v>
       </c>
       <c r="R68" t="n">
-        <v>6994082</v>
+        <v>6993935</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7823,12 +7826,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7854,16 +7857,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102089013</v>
+        <v>134246389</v>
       </c>
       <c r="B69" t="n">
-        <v>80467</v>
+        <v>58131</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7871,35 +7874,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>103023</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550570</v>
+        <v>550466</v>
       </c>
       <c r="R69" t="n">
-        <v>6994156</v>
+        <v>6994147</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7926,17 +7928,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7951,27 +7948,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102089935</v>
+        <v>134246392</v>
       </c>
       <c r="B70" t="n">
-        <v>80467</v>
+        <v>98219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7979,38 +7976,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>219815</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550373</v>
+        <v>550548</v>
       </c>
       <c r="R70" t="n">
-        <v>6994082</v>
+        <v>6994192</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8034,12 +8030,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8054,27 +8050,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121004525</v>
+        <v>135466568</v>
       </c>
       <c r="B71" t="n">
-        <v>57141</v>
+        <v>99311</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8082,42 +8078,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550502</v>
+        <v>550481</v>
       </c>
       <c r="R71" t="n">
-        <v>6993935</v>
+        <v>6993999</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8144,12 +8140,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8158,6 +8154,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8175,51 +8172,53 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134246389</v>
+        <v>102088784</v>
       </c>
       <c r="B72" t="n">
-        <v>58131</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103023</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550466</v>
+        <v>550571</v>
       </c>
       <c r="R72" t="n">
-        <v>6994147</v>
+        <v>6994155</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8246,12 +8245,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8266,65 +8265,67 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134246392</v>
+        <v>102089119</v>
       </c>
       <c r="B73" t="n">
-        <v>98219</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219815</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550548</v>
+        <v>550567</v>
       </c>
       <c r="R73" t="n">
-        <v>6994192</v>
+        <v>6994155</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8348,12 +8349,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8368,70 +8369,64 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135466568</v>
+        <v>102089419</v>
       </c>
       <c r="B74" t="n">
-        <v>99311</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550481</v>
+        <v>550554</v>
       </c>
       <c r="R74" t="n">
-        <v>6993999</v>
+        <v>6994133</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8458,12 +8453,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8472,7 +8467,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8490,13 +8484,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466568</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102088784</v>
+        <v>102089819</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8529,14 +8523,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550571</v>
+        <v>550446</v>
       </c>
       <c r="R75" t="n">
-        <v>6994155</v>
+        <v>6994089</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8594,13 +8588,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102089119</v>
+        <v>121004332</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8629,18 +8623,20 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550567</v>
+        <v>550310</v>
       </c>
       <c r="R76" t="n">
-        <v>6994155</v>
+        <v>6994126</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8667,12 +8663,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8681,6 +8677,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8698,13 +8695,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102089419</v>
+        <v>121004405</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8733,18 +8730,20 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550554</v>
+        <v>550404</v>
       </c>
       <c r="R77" t="n">
-        <v>6994133</v>
+        <v>6994153</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8771,12 +8770,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8785,6 +8784,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8802,13 +8802,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102089819</v>
+        <v>121004422</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8837,18 +8837,20 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550446</v>
+        <v>550395</v>
       </c>
       <c r="R78" t="n">
-        <v>6994089</v>
+        <v>6994127</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8875,12 +8877,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8889,6 +8891,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8906,13 +8909,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004332</v>
+        <v>121004461</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8951,10 +8954,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550310</v>
+        <v>550389</v>
       </c>
       <c r="R79" t="n">
-        <v>6994126</v>
+        <v>6994063</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9013,13 +9016,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004405</v>
+        <v>121004477</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9058,10 +9061,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550404</v>
+        <v>550370</v>
       </c>
       <c r="R80" t="n">
-        <v>6994153</v>
+        <v>6993853</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9120,13 +9123,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004422</v>
+        <v>121004505</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9165,10 +9168,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550395</v>
+        <v>550496</v>
       </c>
       <c r="R81" t="n">
-        <v>6994127</v>
+        <v>6993835</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9227,13 +9230,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004461</v>
+        <v>121004519</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9272,10 +9275,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550389</v>
+        <v>550494</v>
       </c>
       <c r="R82" t="n">
-        <v>6994063</v>
+        <v>6993901</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9310,6 +9313,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9334,13 +9342,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004477</v>
+        <v>121004558</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9379,10 +9387,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550370</v>
+        <v>550516</v>
       </c>
       <c r="R83" t="n">
-        <v>6993853</v>
+        <v>6994130</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9441,13 +9449,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004505</v>
+        <v>121004562</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9486,10 +9494,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550496</v>
+        <v>550520</v>
       </c>
       <c r="R84" t="n">
-        <v>6993835</v>
+        <v>6994154</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9548,13 +9556,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004519</v>
+        <v>121004565</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9593,10 +9601,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550494</v>
+        <v>550469</v>
       </c>
       <c r="R85" t="n">
-        <v>6993901</v>
+        <v>6994270</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9631,11 +9639,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9660,13 +9663,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121004558</v>
+        <v>126099534</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9701,14 +9704,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550516</v>
+        <v>550463</v>
       </c>
       <c r="R86" t="n">
-        <v>6994130</v>
+        <v>6994172</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9735,12 +9738,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9767,16 +9770,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121004562</v>
+        <v>134246388</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9802,23 +9805,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550520</v>
+        <v>550414</v>
       </c>
       <c r="R87" t="n">
-        <v>6994154</v>
+        <v>6994084</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9842,12 +9841,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9856,56 +9855,55 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/134246388</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121004565</v>
+        <v>135466572</v>
       </c>
       <c r="B88" t="n">
-        <v>99118</v>
+        <v>98144</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9919,10 +9917,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550469</v>
+        <v>550481</v>
       </c>
       <c r="R88" t="n">
-        <v>6994270</v>
+        <v>6993999</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9949,12 +9947,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9981,58 +9979,54 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/135466572</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126099534</v>
+        <v>134246393</v>
       </c>
       <c r="B89" t="n">
-        <v>99118</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550463</v>
+        <v>550548</v>
       </c>
       <c r="R89" t="n">
-        <v>6994172</v>
+        <v>6994192</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10056,12 +10050,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10070,69 +10064,68 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/134246393</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246388</v>
+        <v>134246406</v>
       </c>
       <c r="B90" t="n">
-        <v>99195</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550414</v>
+        <v>550277</v>
       </c>
       <c r="R90" t="n">
-        <v>6994084</v>
+        <v>6994166</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10190,59 +10183,54 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/134246406</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135457589</v>
+        <v>126099623</v>
       </c>
       <c r="B91" t="n">
-        <v>99276</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550445</v>
+        <v>550481</v>
       </c>
       <c r="R91" t="n">
-        <v>6993808</v>
+        <v>6994133</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10269,17 +10257,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönpyrola.</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10306,62 +10289,54 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457589</t>
+          <t>https://artportalen.se/Sighting/126099623</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135457681</v>
+        <v>134246390</v>
       </c>
       <c r="B92" t="n">
-        <v>99276</v>
+        <v>79131</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550350</v>
+        <v>550466</v>
       </c>
       <c r="R92" t="n">
-        <v>6993905</v>
+        <v>6994147</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10385,12 +10360,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10399,77 +10374,69 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457681</t>
+          <t>https://artportalen.se/Sighting/134246390</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135457684</v>
+        <v>102089933</v>
       </c>
       <c r="B93" t="n">
-        <v>99276</v>
+        <v>80392</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550343</v>
+        <v>550373</v>
       </c>
       <c r="R93" t="n">
-        <v>6993884</v>
+        <v>6994082</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10496,12 +10463,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10510,7 +10477,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10527,966 +10493,6 @@
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457684</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>135457690</v>
-      </c>
-      <c r="B94" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>550353</v>
-      </c>
-      <c r="R94" t="n">
-        <v>6993851</v>
-      </c>
-      <c r="S94" t="n">
-        <v>25</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457690</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135457698</v>
-      </c>
-      <c r="B95" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>550455</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6994009</v>
-      </c>
-      <c r="S95" t="n">
-        <v>25</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457698</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>135457602</v>
-      </c>
-      <c r="B96" t="n">
-        <v>106413</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>550445</v>
-      </c>
-      <c r="R96" t="n">
-        <v>6993808</v>
-      </c>
-      <c r="S96" t="n">
-        <v>25</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Tillsammans med knärot.</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135457602</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>135466572</v>
-      </c>
-      <c r="B97" t="n">
-        <v>98144</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>550481</v>
-      </c>
-      <c r="R97" t="n">
-        <v>6993999</v>
-      </c>
-      <c r="S97" t="n">
-        <v>25</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135466572</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>134246393</v>
-      </c>
-      <c r="B98" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>550548</v>
-      </c>
-      <c r="R98" t="n">
-        <v>6994192</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>134246406</v>
-      </c>
-      <c r="B99" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Lapprännbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>550277</v>
-      </c>
-      <c r="R99" t="n">
-        <v>6994166</v>
-      </c>
-      <c r="S99" t="n">
-        <v>10</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>126099623</v>
-      </c>
-      <c r="B100" t="n">
-        <v>79085</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q100" t="n">
-        <v>550481</v>
-      </c>
-      <c r="R100" t="n">
-        <v>6994133</v>
-      </c>
-      <c r="S100" t="n">
-        <v>25</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AD100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="inlineStr"/>
-      <c r="AW100" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>134246390</v>
-      </c>
-      <c r="B101" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Blomkindtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>550466</v>
-      </c>
-      <c r="R101" t="n">
-        <v>6994147</v>
-      </c>
-      <c r="S101" t="n">
-        <v>10</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>102089933</v>
-      </c>
-      <c r="B102" t="n">
-        <v>80392</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Blomkind, Jmt</t>
-        </is>
-      </c>
-      <c r="Q102" t="n">
-        <v>550373</v>
-      </c>
-      <c r="R102" t="n">
-        <v>6994082</v>
-      </c>
-      <c r="S102" t="n">
-        <v>25</v>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AD102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT102" t="inlineStr"/>
-      <c r="AW102" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
-      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102089933</t>
         </is>
@@ -11586,15 +10592,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ93"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,32 +1321,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004536</v>
+        <v>135457711</v>
       </c>
       <c r="B8" t="n">
-        <v>81312</v>
+        <v>92637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550477</v>
+        <v>550504</v>
       </c>
       <c r="R8" t="n">
-        <v>6994042</v>
+        <v>6993854</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,13 +1421,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004536</t>
+          <t>https://artportalen.se/Sighting/135457711</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004550</v>
+        <v>121004536</v>
       </c>
       <c r="B9" t="n">
         <v>81312</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550508</v>
+        <v>550477</v>
       </c>
       <c r="R9" t="n">
-        <v>6994113</v>
+        <v>6994042</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1527,13 +1527,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004550</t>
+          <t>https://artportalen.se/Sighting/121004536</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126099520</v>
+        <v>121004550</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1567,14 +1567,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550419</v>
+        <v>550508</v>
       </c>
       <c r="R10" t="n">
-        <v>6994207</v>
+        <v>6994113</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,16 +1633,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099520</t>
+          <t>https://artportalen.se/Sighting/121004550</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102089224</v>
+        <v>126099520</v>
       </c>
       <c r="B11" t="n">
-        <v>83173</v>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,35 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550562</v>
+        <v>550419</v>
       </c>
       <c r="R11" t="n">
-        <v>6994152</v>
+        <v>6994207</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1705,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,6 +1721,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,54 +1739,52 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089224</t>
+          <t>https://artportalen.se/Sighting/126099520</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004416</v>
+        <v>102089224</v>
       </c>
       <c r="B12" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550398</v>
+        <v>550562</v>
       </c>
       <c r="R12" t="n">
-        <v>6994131</v>
+        <v>6994152</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1810,12 +1811,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1842,13 +1842,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004416</t>
+          <t>https://artportalen.se/Sighting/102089224</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004472</v>
+        <v>121004416</v>
       </c>
       <c r="B13" t="n">
         <v>92083</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550400</v>
+        <v>550398</v>
       </c>
       <c r="R13" t="n">
-        <v>6993983</v>
+        <v>6994131</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,38 +1948,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004472</t>
+          <t>https://artportalen.se/Sighting/121004416</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004362</v>
+        <v>121004472</v>
       </c>
       <c r="B14" t="n">
-        <v>90932</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550364</v>
+        <v>550400</v>
       </c>
       <c r="R14" t="n">
-        <v>6994169</v>
+        <v>6993983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,13 +2054,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004362</t>
+          <t>https://artportalen.se/Sighting/121004472</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004490</v>
+        <v>121004362</v>
       </c>
       <c r="B15" t="n">
         <v>90932</v>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550508</v>
+        <v>550364</v>
       </c>
       <c r="R15" t="n">
-        <v>6993803</v>
+        <v>6994169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004490</t>
+          <t>https://artportalen.se/Sighting/121004362</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004539</v>
+        <v>121004490</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550486</v>
+        <v>550508</v>
       </c>
       <c r="R16" t="n">
-        <v>6994062</v>
+        <v>6993803</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,16 +2266,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004539</t>
+          <t>https://artportalen.se/Sighting/121004490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62025591</v>
+        <v>121004539</v>
       </c>
       <c r="B17" t="n">
-        <v>91962</v>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,37 +2283,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550409</v>
+        <v>550486</v>
       </c>
       <c r="R17" t="n">
-        <v>6994048</v>
+        <v>6994062</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,12 +2340,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,43 +2354,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025591</t>
+          <t>https://artportalen.se/Sighting/121004539</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102089002</v>
+        <v>62025591</v>
       </c>
       <c r="B18" t="n">
-        <v>80433</v>
+        <v>91962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,38 +2389,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550570</v>
+        <v>550409</v>
       </c>
       <c r="R18" t="n">
-        <v>6994156</v>
+        <v>6994048</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2450,17 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2471,69 +2459,80 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089002</t>
+          <t>https://artportalen.se/Sighting/62025591</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103996059</v>
+        <v>102089002</v>
       </c>
       <c r="B19" t="n">
-        <v>96338</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550310</v>
+        <v>550570</v>
       </c>
       <c r="R19" t="n">
-        <v>6994183</v>
+        <v>6994156</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,22 +2556,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,11 +2577,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2597,67 +2586,60 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/102089002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121004351</v>
+        <v>103996059</v>
       </c>
       <c r="B20" t="n">
-        <v>91831</v>
+        <v>96338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3242</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550358</v>
+        <v>550310</v>
       </c>
       <c r="R20" t="n">
-        <v>6994160</v>
+        <v>6994183</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,12 +2663,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2695,9 +2687,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2707,19 +2703,23 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004351</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004470</v>
+        <v>121004351</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550383</v>
+        <v>550358</v>
       </c>
       <c r="R21" t="n">
-        <v>6993994</v>
+        <v>6994160</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2795,11 +2795,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2824,16 +2819,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004470</t>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>62025592</v>
+        <v>121004470</v>
       </c>
       <c r="B22" t="n">
-        <v>93197</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,37 +2836,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550409</v>
+        <v>550383</v>
       </c>
       <c r="R22" t="n">
-        <v>6994048</v>
+        <v>6993994</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2895,12 +2893,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2909,43 +2912,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025592</t>
+          <t>https://artportalen.se/Sighting/121004470</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102089700</v>
+        <v>135457707</v>
       </c>
       <c r="B23" t="n">
-        <v>93197</v>
+        <v>93354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,35 +2947,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550476</v>
+        <v>550510</v>
       </c>
       <c r="R23" t="n">
-        <v>6994117</v>
+        <v>6993821</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3008,12 +3004,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,6 +3018,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3039,13 +3036,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089700</t>
+          <t>https://artportalen.se/Sighting/135457707</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103996072</v>
+        <v>62025592</v>
       </c>
       <c r="B24" t="n">
         <v>93197</v>
@@ -3076,14 +3073,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550481</v>
+        <v>550409</v>
       </c>
       <c r="R24" t="n">
-        <v>6994068</v>
+        <v>6994048</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3110,22 +3107,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,36 +3124,37 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996072</t>
+          <t>https://artportalen.se/Sighting/62025592</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103996080</v>
+        <v>102089700</v>
       </c>
       <c r="B25" t="n">
         <v>93197</v>
@@ -3195,19 +3183,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550485</v>
+        <v>550476</v>
       </c>
       <c r="R25" t="n">
-        <v>6994105</v>
+        <v>6994117</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,22 +3220,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,11 +3236,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3271,23 +3245,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996080</t>
+          <t>https://artportalen.se/Sighting/102089700</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004341</v>
+        <v>103996072</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3316,22 +3286,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550344</v>
+        <v>550481</v>
       </c>
       <c r="R26" t="n">
-        <v>6994160</v>
+        <v>6994068</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3355,12 +3322,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,9 +3346,13 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3381,19 +3362,23 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004341</t>
+          <t>https://artportalen.se/Sighting/103996072</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121004394</v>
+        <v>103996080</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3422,22 +3407,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550381</v>
+        <v>550485</v>
       </c>
       <c r="R27" t="n">
-        <v>6994155</v>
+        <v>6994105</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,12 +3443,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,9 +3467,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3487,19 +3483,23 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004394</t>
+          <t>https://artportalen.se/Sighting/103996080</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004399</v>
+        <v>121004341</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550384</v>
+        <v>550344</v>
       </c>
       <c r="R28" t="n">
-        <v>6994151</v>
+        <v>6994160</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3599,13 +3599,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004399</t>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004430</v>
+        <v>121004394</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550422</v>
+        <v>550381</v>
       </c>
       <c r="R29" t="n">
-        <v>6994093</v>
+        <v>6994155</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3705,13 +3705,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004430</t>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004475</v>
+        <v>121004399</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550385</v>
+        <v>550384</v>
       </c>
       <c r="R30" t="n">
-        <v>6993920</v>
+        <v>6994151</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3811,13 +3811,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004475</t>
+          <t>https://artportalen.se/Sighting/121004399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004484</v>
+        <v>121004430</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550427</v>
+        <v>550422</v>
       </c>
       <c r="R31" t="n">
-        <v>6993867</v>
+        <v>6994093</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,13 +3917,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004484</t>
+          <t>https://artportalen.se/Sighting/121004430</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004500</v>
+        <v>121004475</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550496</v>
+        <v>550385</v>
       </c>
       <c r="R32" t="n">
-        <v>6993817</v>
+        <v>6993920</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4023,13 +4023,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004500</t>
+          <t>https://artportalen.se/Sighting/121004475</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004509</v>
+        <v>121004484</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550476</v>
+        <v>550427</v>
       </c>
       <c r="R33" t="n">
-        <v>6993841</v>
+        <v>6993867</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,13 +4129,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004509</t>
+          <t>https://artportalen.se/Sighting/121004484</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004524</v>
+        <v>121004500</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550502</v>
+        <v>550496</v>
       </c>
       <c r="R34" t="n">
-        <v>6993935</v>
+        <v>6993817</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,13 +4235,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004524</t>
+          <t>https://artportalen.se/Sighting/121004500</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004537</v>
+        <v>121004509</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550477</v>
+        <v>550476</v>
       </c>
       <c r="R35" t="n">
-        <v>6994042</v>
+        <v>6993841</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4341,13 +4341,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004537</t>
+          <t>https://artportalen.se/Sighting/121004509</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004540</v>
+        <v>121004524</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550505</v>
+        <v>550502</v>
       </c>
       <c r="R36" t="n">
-        <v>6994074</v>
+        <v>6993935</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4447,13 +4447,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004540</t>
+          <t>https://artportalen.se/Sighting/121004524</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004541</v>
+        <v>121004537</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550528</v>
+        <v>550477</v>
       </c>
       <c r="R37" t="n">
-        <v>6994067</v>
+        <v>6994042</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4553,13 +4553,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004541</t>
+          <t>https://artportalen.se/Sighting/121004537</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004547</v>
+        <v>121004540</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550493</v>
+        <v>550505</v>
       </c>
       <c r="R38" t="n">
-        <v>6994078</v>
+        <v>6994074</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4659,16 +4659,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004547</t>
+          <t>https://artportalen.se/Sighting/121004540</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134246391</v>
+        <v>121004541</v>
       </c>
       <c r="B39" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4694,19 +4694,22 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550317</v>
+        <v>550528</v>
       </c>
       <c r="R39" t="n">
-        <v>6994117</v>
+        <v>6994067</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4730,12 +4733,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,55 +4747,56 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/121004541</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004494</v>
+        <v>121004547</v>
       </c>
       <c r="B40" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4805,10 +4809,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550515</v>
+        <v>550493</v>
       </c>
       <c r="R40" t="n">
-        <v>6993816</v>
+        <v>6994078</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4867,57 +4871,54 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004494</t>
+          <t>https://artportalen.se/Sighting/121004547</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004545</v>
+        <v>134246391</v>
       </c>
       <c r="B41" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550493</v>
+        <v>550317</v>
       </c>
       <c r="R41" t="n">
-        <v>6994078</v>
+        <v>6994117</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4941,12 +4942,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,34 +4956,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004545</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135457522</v>
+        <v>121004494</v>
       </c>
       <c r="B42" t="n">
-        <v>93351</v>
+        <v>93201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550478</v>
+        <v>550515</v>
       </c>
       <c r="R42" t="n">
-        <v>6993873</v>
+        <v>6993816</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,38 +5079,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457522</t>
+          <t>https://artportalen.se/Sighting/121004494</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004409</v>
+        <v>121004545</v>
       </c>
       <c r="B43" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550413</v>
+        <v>550493</v>
       </c>
       <c r="R43" t="n">
-        <v>6994137</v>
+        <v>6994078</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5185,16 +5185,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/121004545</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102089839</v>
+        <v>135457522</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>93366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5202,38 +5202,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550410</v>
+        <v>550478</v>
       </c>
       <c r="R44" t="n">
-        <v>6994101</v>
+        <v>6993873</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5257,12 +5259,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,6 +5273,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5288,38 +5291,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004337</v>
+        <v>121004409</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5335,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550319</v>
+        <v>550413</v>
       </c>
       <c r="R45" t="n">
-        <v>6994143</v>
+        <v>6994137</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5370,11 +5373,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5399,38 +5397,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121004358</v>
+        <v>135457649</v>
       </c>
       <c r="B46" t="n">
-        <v>79327</v>
+        <v>89294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5443,10 +5441,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550362</v>
+        <v>550447</v>
       </c>
       <c r="R46" t="n">
-        <v>6994156</v>
+        <v>6993828</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5473,12 +5471,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5505,13 +5503,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/135457649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004395</v>
+        <v>102089839</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5540,19 +5538,17 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550381</v>
+        <v>550410</v>
       </c>
       <c r="R47" t="n">
-        <v>6994155</v>
+        <v>6994101</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,12 +5575,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,7 +5589,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5611,13 +5606,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004439</v>
+        <v>121004337</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5655,10 +5650,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550405</v>
+        <v>550319</v>
       </c>
       <c r="R48" t="n">
-        <v>6994090</v>
+        <v>6994143</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5695,7 +5690,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,13 +5717,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004450</v>
+        <v>121004358</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5766,10 +5761,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550379</v>
+        <v>550362</v>
       </c>
       <c r="R49" t="n">
-        <v>6994086</v>
+        <v>6994156</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5828,13 +5823,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004511</v>
+        <v>121004395</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550470</v>
+        <v>550381</v>
       </c>
       <c r="R50" t="n">
-        <v>6993852</v>
+        <v>6994155</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5910,11 +5905,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5939,13 +5929,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004515</v>
+        <v>121004439</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5983,10 +5973,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550464</v>
+        <v>550405</v>
       </c>
       <c r="R51" t="n">
-        <v>6993901</v>
+        <v>6994090</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6021,6 +6011,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6045,13 +6040,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126099630</v>
+        <v>121004450</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -6085,14 +6080,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550494</v>
+        <v>550379</v>
       </c>
       <c r="R52" t="n">
-        <v>6994148</v>
+        <v>6994086</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6119,17 +6114,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6156,16 +6146,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246394</v>
+        <v>121004511</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6191,19 +6181,22 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550512</v>
+        <v>550470</v>
       </c>
       <c r="R53" t="n">
-        <v>6994236</v>
+        <v>6993852</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6227,12 +6220,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6241,33 +6239,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134246395</v>
+        <v>121004515</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6293,19 +6292,22 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550292</v>
+        <v>550464</v>
       </c>
       <c r="R54" t="n">
-        <v>6994150</v>
+        <v>6993901</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6329,12 +6331,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6343,69 +6345,72 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102089806</v>
+        <v>126099630</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R55" t="n">
-        <v>6994094</v>
+        <v>6994148</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6432,12 +6437,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,6 +6456,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6463,57 +6474,54 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121004349</v>
+        <v>134246394</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550358</v>
+        <v>550512</v>
       </c>
       <c r="R56" t="n">
-        <v>6994160</v>
+        <v>6994236</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6537,12 +6545,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6551,75 +6559,71 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121004374</v>
+        <v>134246395</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550369</v>
+        <v>550292</v>
       </c>
       <c r="R57" t="n">
-        <v>6994167</v>
+        <v>6994150</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6643,12 +6647,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6657,31 +6661,30 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004533</v>
+        <v>102089806</v>
       </c>
       <c r="B58" t="n">
         <v>79946</v>
@@ -6710,19 +6713,17 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550456</v>
+        <v>550469</v>
       </c>
       <c r="R58" t="n">
-        <v>6993982</v>
+        <v>6994094</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6749,17 +6750,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,7 +6764,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6786,13 +6781,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126099591</v>
+        <v>121004349</v>
       </c>
       <c r="B59" t="n">
         <v>79946</v>
@@ -6826,14 +6821,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550464</v>
+        <v>550358</v>
       </c>
       <c r="R59" t="n">
-        <v>6994104</v>
+        <v>6994160</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6860,12 +6855,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6892,38 +6887,38 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126099553</v>
+        <v>121004374</v>
       </c>
       <c r="B60" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6932,14 +6927,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550465</v>
+        <v>550369</v>
       </c>
       <c r="R60" t="n">
-        <v>6994163</v>
+        <v>6994167</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6966,17 +6961,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,16 +6993,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102088995</v>
+        <v>121004533</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7020,35 +7010,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550570</v>
+        <v>550456</v>
       </c>
       <c r="R61" t="n">
-        <v>6994156</v>
+        <v>6993982</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7075,17 +7067,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7094,6 +7086,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7111,16 +7104,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102089929</v>
+        <v>126099591</v>
       </c>
       <c r="B62" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,35 +7121,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550373</v>
+        <v>550464</v>
       </c>
       <c r="R62" t="n">
-        <v>6994082</v>
+        <v>6994104</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7183,12 +7178,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7197,6 +7192,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7214,38 +7210,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004521</v>
+        <v>126099553</v>
       </c>
       <c r="B63" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7254,14 +7250,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550494</v>
+        <v>550465</v>
       </c>
       <c r="R63" t="n">
-        <v>6993901</v>
+        <v>6994163</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7288,17 +7284,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7325,38 +7321,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102089008</v>
+        <v>102088995</v>
       </c>
       <c r="B64" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7433,38 +7429,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089938</v>
+        <v>102089929</v>
       </c>
       <c r="B65" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7536,52 +7532,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102089013</v>
+        <v>121004521</v>
       </c>
       <c r="B66" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550570</v>
+        <v>550494</v>
       </c>
       <c r="R66" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7608,12 +7606,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7627,6 +7625,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7644,16 +7643,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089935</v>
+        <v>102089008</v>
       </c>
       <c r="B67" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7661,21 +7660,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7685,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550373</v>
+        <v>550570</v>
       </c>
       <c r="R67" t="n">
-        <v>6994082</v>
+        <v>6994156</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7724,6 +7723,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7747,16 +7751,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121004525</v>
+        <v>102089938</v>
       </c>
       <c r="B68" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7764,42 +7768,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550502</v>
+        <v>550373</v>
       </c>
       <c r="R68" t="n">
-        <v>6993935</v>
+        <v>6994082</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7826,12 +7823,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,16 +7854,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134246389</v>
+        <v>102089013</v>
       </c>
       <c r="B69" t="n">
-        <v>58131</v>
+        <v>80467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7874,34 +7871,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103023</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550466</v>
+        <v>550570</v>
       </c>
       <c r="R69" t="n">
-        <v>6994147</v>
+        <v>6994156</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7928,12 +7926,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,27 +7951,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134246392</v>
+        <v>102089935</v>
       </c>
       <c r="B70" t="n">
-        <v>98219</v>
+        <v>80467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7976,37 +7979,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219815</v>
+        <v>6463</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550548</v>
+        <v>550373</v>
       </c>
       <c r="R70" t="n">
-        <v>6994192</v>
+        <v>6994082</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8030,12 +8034,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8050,27 +8054,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135466568</v>
+        <v>121004525</v>
       </c>
       <c r="B71" t="n">
-        <v>99311</v>
+        <v>57141</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8078,42 +8082,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550481</v>
+        <v>550502</v>
       </c>
       <c r="R71" t="n">
-        <v>6993999</v>
+        <v>6993935</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8140,12 +8144,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8154,7 +8158,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8172,53 +8175,51 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466568</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102088784</v>
+        <v>134246389</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>58131</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550571</v>
+        <v>550466</v>
       </c>
       <c r="R72" t="n">
-        <v>6994155</v>
+        <v>6994147</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8245,12 +8246,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8265,67 +8266,65 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102089119</v>
+        <v>134246392</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550567</v>
+        <v>550548</v>
       </c>
       <c r="R73" t="n">
-        <v>6994155</v>
+        <v>6994192</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8349,12 +8348,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8369,64 +8368,70 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102089419</v>
+        <v>135466568</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>99328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550554</v>
+        <v>550481</v>
       </c>
       <c r="R74" t="n">
-        <v>6994133</v>
+        <v>6993999</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8453,12 +8458,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8467,6 +8472,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8484,13 +8490,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102089819</v>
+        <v>102088784</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8523,14 +8529,14 @@
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550446</v>
+        <v>550571</v>
       </c>
       <c r="R75" t="n">
-        <v>6994089</v>
+        <v>6994155</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8588,13 +8594,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121004332</v>
+        <v>102089119</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8623,20 +8629,18 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550310</v>
+        <v>550567</v>
       </c>
       <c r="R76" t="n">
-        <v>6994126</v>
+        <v>6994155</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8663,12 +8667,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8677,7 +8681,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8695,13 +8698,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004405</v>
+        <v>102089419</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8730,20 +8733,18 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550404</v>
+        <v>550554</v>
       </c>
       <c r="R77" t="n">
-        <v>6994153</v>
+        <v>6994133</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8770,12 +8771,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,7 +8785,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8802,13 +8802,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121004422</v>
+        <v>102089819</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8837,20 +8837,18 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550395</v>
+        <v>550446</v>
       </c>
       <c r="R78" t="n">
-        <v>6994127</v>
+        <v>6994089</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8877,12 +8875,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8891,7 +8889,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8909,13 +8906,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004461</v>
+        <v>121004332</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8954,10 +8951,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550389</v>
+        <v>550310</v>
       </c>
       <c r="R79" t="n">
-        <v>6994063</v>
+        <v>6994126</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9016,13 +9013,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004477</v>
+        <v>121004405</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9061,10 +9058,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550370</v>
+        <v>550404</v>
       </c>
       <c r="R80" t="n">
-        <v>6993853</v>
+        <v>6994153</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9123,13 +9120,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004505</v>
+        <v>121004422</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9168,10 +9165,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550496</v>
+        <v>550395</v>
       </c>
       <c r="R81" t="n">
-        <v>6993835</v>
+        <v>6994127</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9230,13 +9227,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004519</v>
+        <v>121004461</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9275,10 +9272,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550494</v>
+        <v>550389</v>
       </c>
       <c r="R82" t="n">
-        <v>6993901</v>
+        <v>6994063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9313,11 +9310,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9342,13 +9334,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004558</v>
+        <v>121004477</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -9387,10 +9379,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550516</v>
+        <v>550370</v>
       </c>
       <c r="R83" t="n">
-        <v>6994130</v>
+        <v>6993853</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9449,13 +9441,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004562</v>
+        <v>121004505</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -9494,10 +9486,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550520</v>
+        <v>550496</v>
       </c>
       <c r="R84" t="n">
-        <v>6994154</v>
+        <v>6993835</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9556,13 +9548,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004565</v>
+        <v>121004519</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -9601,10 +9593,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R85" t="n">
-        <v>6994270</v>
+        <v>6993901</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9639,6 +9631,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9663,13 +9660,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126099534</v>
+        <v>121004558</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -9704,14 +9701,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550463</v>
+        <v>550516</v>
       </c>
       <c r="R86" t="n">
-        <v>6994172</v>
+        <v>6994130</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9738,12 +9735,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9770,16 +9767,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134246388</v>
+        <v>121004562</v>
       </c>
       <c r="B87" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9805,19 +9802,23 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550414</v>
+        <v>550520</v>
       </c>
       <c r="R87" t="n">
-        <v>6994084</v>
+        <v>6994154</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9841,12 +9842,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9855,55 +9856,56 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135466572</v>
+        <v>121004565</v>
       </c>
       <c r="B88" t="n">
-        <v>98144</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9917,10 +9919,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550481</v>
+        <v>550469</v>
       </c>
       <c r="R88" t="n">
-        <v>6993999</v>
+        <v>6994270</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9947,12 +9949,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9979,54 +9981,58 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466572</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134246393</v>
+        <v>126099534</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550548</v>
+        <v>550463</v>
       </c>
       <c r="R89" t="n">
-        <v>6994192</v>
+        <v>6994172</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10050,12 +10056,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10064,68 +10070,69 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246406</v>
+        <v>134246388</v>
       </c>
       <c r="B90" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550277</v>
+        <v>550414</v>
       </c>
       <c r="R90" t="n">
-        <v>6994166</v>
+        <v>6994084</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10183,54 +10190,59 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
+          <t>https://artportalen.se/Sighting/134246388</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126099623</v>
+        <v>135457589</v>
       </c>
       <c r="B91" t="n">
-        <v>79085</v>
+        <v>99293</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550481</v>
+        <v>550445</v>
       </c>
       <c r="R91" t="n">
-        <v>6994133</v>
+        <v>6993808</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10257,12 +10269,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönpyrola.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10289,54 +10306,62 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
+          <t>https://artportalen.se/Sighting/135457589</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134246390</v>
+        <v>135457681</v>
       </c>
       <c r="B92" t="n">
-        <v>79131</v>
+        <v>99293</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550466</v>
+        <v>550350</v>
       </c>
       <c r="R92" t="n">
-        <v>6994147</v>
+        <v>6993905</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10360,12 +10385,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10374,69 +10399,77 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
+          <t>https://artportalen.se/Sighting/135457681</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>102089933</v>
+        <v>135457684</v>
       </c>
       <c r="B93" t="n">
-        <v>80392</v>
+        <v>99293</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550373</v>
+        <v>550343</v>
       </c>
       <c r="R93" t="n">
-        <v>6994082</v>
+        <v>6993884</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10463,12 +10496,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10477,6 +10510,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10493,6 +10527,966 @@
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457684</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135457690</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>550353</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6993851</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457690</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135457698</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>550455</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6994009</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457698</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135457602</v>
+      </c>
+      <c r="B96" t="n">
+        <v>106433</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>550445</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6993808</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Tillsammans med knärot.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457602</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135466572</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98161</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6993999</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466572</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134246393</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>550548</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6994192</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246393</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099623</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246390</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B102" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102089933</t>
         </is>
@@ -10592,6 +11586,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
